--- a/docs/oc-mensuales/articulos-de-aseo-e-higiene/feb-2026.xlsx
+++ b/docs/oc-mensuales/articulos-de-aseo-e-higiene/feb-2026.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>3826.79</v>
+        <v>3813.16</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>4537.26</v>
+        <v>4521.11</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>5162.87</v>
+        <v>5144.49</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>4790.12</v>
+        <v>4773.07</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>2422.85</v>
+        <v>2414.23</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>5779.37</v>
+        <v>5758.8</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>3116.25</v>
+        <v>3105.16</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>4083.46</v>
+        <v>4068.92</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>6164.94</v>
+        <v>6142.99</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>17623.06</v>
+        <v>17560.32</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>2912.17</v>
+        <v>2901.8</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>3113.29</v>
+        <v>3102.2</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>108363.65</v>
+        <v>107977.85</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>6997.23</v>
+        <v>6972.32</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>6431.41</v>
+        <v>6408.51</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>36781.59</v>
+        <v>36650.64</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>1248.23</v>
+        <v>1243.78</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>865.5599999999999</v>
+        <v>862.48</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>990.49</v>
+        <v>986.97</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>4490.7</v>
+        <v>4474.71</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>2036.26</v>
+        <v>2029.01</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>41935.83</v>
+        <v>41786.53</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>3431.03</v>
+        <v>3418.82</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>5915.35</v>
+        <v>5894.29</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>3832.1</v>
+        <v>3818.45</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>4998.02</v>
+        <v>4980.23</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>7613.61</v>
+        <v>7586.51</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>3190.93</v>
+        <v>3179.57</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>2432.8</v>
+        <v>2424.14</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>16321.64</v>
+        <v>16263.54</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>1010.51</v>
+        <v>1006.91</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>36127.13</v>
+        <v>35998.51</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>3849.1</v>
+        <v>3835.39</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>1792.55</v>
+        <v>1786.17</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>6762.66</v>
+        <v>6738.58</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>4642.11</v>
+        <v>4625.58</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>5496.16</v>
+        <v>5476.6</v>
       </c>
     </row>
     <row r="39">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>876.78</v>
+        <v>873.66</v>
       </c>
     </row>
     <row r="40">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>7581.31</v>
+        <v>7554.32</v>
       </c>
     </row>
     <row r="41">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>1909.5</v>
+        <v>1902.7</v>
       </c>
     </row>
     <row r="42">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>810.51</v>
+        <v>807.63</v>
       </c>
     </row>
     <row r="43">
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>12035</v>
+        <v>11992.15</v>
       </c>
     </row>
     <row r="44">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>9128.34</v>
+        <v>9095.84</v>
       </c>
     </row>
     <row r="45">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>2787.12</v>
+        <v>2777.19</v>
       </c>
     </row>
     <row r="46">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>2557.44</v>
+        <v>2548.33</v>
       </c>
     </row>
     <row r="47">
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>4521.93</v>
+        <v>4505.83</v>
       </c>
     </row>
     <row r="48">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>1775.46</v>
+        <v>1769.14</v>
       </c>
     </row>
     <row r="49">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>4419.57</v>
+        <v>4403.83</v>
       </c>
     </row>
     <row r="50">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>35405.96</v>
+        <v>35140.98</v>
       </c>
     </row>
     <row r="51">
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>5260.78</v>
+        <v>5221.41</v>
       </c>
     </row>
     <row r="52">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>8290.639999999999</v>
+        <v>8228.6</v>
       </c>
     </row>
     <row r="53">
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>11699.83</v>
+        <v>11612.27</v>
       </c>
     </row>
     <row r="54">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>5886.36</v>
+        <v>5842.31</v>
       </c>
     </row>
     <row r="55">
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>4749.4</v>
+        <v>4713.85</v>
       </c>
     </row>
     <row r="56">
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>1329.4</v>
+        <v>1319.45</v>
       </c>
     </row>
     <row r="57">
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>825.0599999999999</v>
+        <v>818.88</v>
       </c>
     </row>
     <row r="58">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>6460.64</v>
+        <v>6412.29</v>
       </c>
     </row>
     <row r="59">
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>1618.25</v>
+        <v>1606.14</v>
       </c>
     </row>
     <row r="60">
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>3004.77</v>
+        <v>2982.28</v>
       </c>
     </row>
     <row r="61">
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>26870.82</v>
+        <v>26669.72</v>
       </c>
     </row>
     <row r="62">
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>1141.55</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="63">
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>12031.92</v>
+        <v>11941.87</v>
       </c>
     </row>
     <row r="64">
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>2479.89</v>
+        <v>2461.33</v>
       </c>
     </row>
     <row r="65">
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>1277.25</v>
+        <v>1267.69</v>
       </c>
     </row>
     <row r="66">
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>2697.87</v>
+        <v>2677.68</v>
       </c>
     </row>
     <row r="67">
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>3455.44</v>
+        <v>3429.58</v>
       </c>
     </row>
     <row r="68">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>4627.92</v>
+        <v>4593.28</v>
       </c>
     </row>
     <row r="69">
@@ -4656,7 +4656,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>1818.58</v>
+        <v>1804.97</v>
       </c>
     </row>
     <row r="70">
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>5553.93</v>
+        <v>5512.37</v>
       </c>
     </row>
     <row r="71">
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>7743.51</v>
+        <v>7685.56</v>
       </c>
     </row>
     <row r="72">
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>1098.47</v>
+        <v>1090.25</v>
       </c>
     </row>
     <row r="73">
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>2353.99</v>
+        <v>2336.37</v>
       </c>
     </row>
     <row r="74">
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>922.55</v>
+        <v>915.65</v>
       </c>
     </row>
     <row r="75">
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>5144.98</v>
+        <v>5106.47</v>
       </c>
     </row>
     <row r="76">
@@ -5083,7 +5083,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>25587.93</v>
+        <v>25396.43</v>
       </c>
     </row>
     <row r="77">
@@ -5144,7 +5144,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>22411.51</v>
+        <v>22243.79</v>
       </c>
     </row>
     <row r="78">
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>3738.89</v>
+        <v>3710.91</v>
       </c>
     </row>
     <row r="79">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>55639.91</v>
+        <v>55223.5</v>
       </c>
     </row>
     <row r="80">
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>1101.62</v>
+        <v>1093.38</v>
       </c>
     </row>
     <row r="81">
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>2454.14</v>
+        <v>2435.78</v>
       </c>
     </row>
     <row r="82">
@@ -5449,7 +5449,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>4749.93</v>
+        <v>4714.38</v>
       </c>
     </row>
     <row r="83">
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>4284.19</v>
+        <v>4252.13</v>
       </c>
     </row>
     <row r="84">
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>4505.49</v>
+        <v>4471.77</v>
       </c>
     </row>
     <row r="85">
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>3105.94</v>
+        <v>3082.7</v>
       </c>
     </row>
     <row r="86">
@@ -5693,7 +5693,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>6958.56</v>
+        <v>6906.49</v>
       </c>
     </row>
     <row r="87">
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>5644.28</v>
+        <v>5602.04</v>
       </c>
     </row>
     <row r="88">
@@ -5815,7 +5815,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>2918.93</v>
+        <v>2897.09</v>
       </c>
     </row>
     <row r="89">
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>3215.03</v>
+        <v>3190.97</v>
       </c>
     </row>
     <row r="90">
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>987.1</v>
+        <v>979.71</v>
       </c>
     </row>
     <row r="91">
@@ -5998,7 +5998,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>31601.43</v>
+        <v>31364.93</v>
       </c>
     </row>
     <row r="92">
@@ -6059,7 +6059,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>3959.19</v>
+        <v>3929.56</v>
       </c>
     </row>
     <row r="93">
@@ -6120,7 +6120,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>4897.65</v>
+        <v>4861</v>
       </c>
     </row>
     <row r="94">
@@ -6181,7 +6181,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>826.62</v>
+        <v>820.4299999999999</v>
       </c>
     </row>
     <row r="95">
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>2003.87</v>
+        <v>1988.88</v>
       </c>
     </row>
     <row r="96">
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>2932.22</v>
+        <v>2910.28</v>
       </c>
     </row>
     <row r="97">
@@ -6364,7 +6364,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>18246.43</v>
+        <v>18109.88</v>
       </c>
     </row>
     <row r="98">
@@ -6425,7 +6425,7 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>2537.73</v>
+        <v>2545.08</v>
       </c>
     </row>
     <row r="99">
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>44984.98</v>
+        <v>45115.3</v>
       </c>
     </row>
     <row r="100">
@@ -6547,7 +6547,7 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>4100.02</v>
+        <v>4111.9</v>
       </c>
     </row>
     <row r="101">
@@ -6608,7 +6608,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>1301</v>
+        <v>1304.76</v>
       </c>
     </row>
     <row r="102">
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>3119.98</v>
+        <v>3129.01</v>
       </c>
     </row>
     <row r="103">
@@ -6730,7 +6730,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>3551</v>
+        <v>3561.29</v>
       </c>
     </row>
     <row r="104">
@@ -6791,7 +6791,7 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>4312.34</v>
+        <v>4324.83</v>
       </c>
     </row>
     <row r="105">
@@ -6852,7 +6852,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>6140.09</v>
+        <v>6157.88</v>
       </c>
     </row>
     <row r="106">
@@ -6913,7 +6913,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>2628.13</v>
+        <v>2635.74</v>
       </c>
     </row>
     <row r="107">
@@ -6974,7 +6974,7 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>8126.81</v>
+        <v>8150.35</v>
       </c>
     </row>
     <row r="108">
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>7421.33</v>
+        <v>7442.83</v>
       </c>
     </row>
     <row r="109">
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>3414.9</v>
+        <v>3424.8</v>
       </c>
     </row>
     <row r="110">
@@ -7157,7 +7157,7 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>4279.48</v>
+        <v>4291.88</v>
       </c>
     </row>
     <row r="111">
@@ -7218,7 +7218,7 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>4751.97</v>
+        <v>4765.73</v>
       </c>
     </row>
     <row r="112">
@@ -7279,7 +7279,7 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>76561.25</v>
+        <v>76783.05</v>
       </c>
     </row>
     <row r="113">
@@ -7340,7 +7340,7 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>14729.64</v>
+        <v>14772.31</v>
       </c>
     </row>
     <row r="114">
@@ -7401,7 +7401,7 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>3096.51</v>
+        <v>3105.48</v>
       </c>
     </row>
     <row r="115">
@@ -7462,7 +7462,7 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>2530.71</v>
+        <v>2538.05</v>
       </c>
     </row>
     <row r="116">
@@ -7523,7 +7523,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>1732.04</v>
+        <v>1737.06</v>
       </c>
     </row>
     <row r="117">
@@ -7584,7 +7584,7 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>13738.9</v>
+        <v>13778.7</v>
       </c>
     </row>
     <row r="118">
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>5350.97</v>
+        <v>5366.47</v>
       </c>
     </row>
     <row r="119">
@@ -7706,7 +7706,7 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>3471.65</v>
+        <v>3481.7</v>
       </c>
     </row>
     <row r="120">
@@ -7767,7 +7767,7 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>3480.19</v>
+        <v>3490.28</v>
       </c>
     </row>
     <row r="121">
@@ -7828,7 +7828,7 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>4472.43</v>
+        <v>4485.38</v>
       </c>
     </row>
     <row r="122">
@@ -7889,7 +7889,7 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>2052.51</v>
+        <v>2058.46</v>
       </c>
     </row>
     <row r="123">
@@ -7950,7 +7950,7 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>21734.66</v>
+        <v>21797.62</v>
       </c>
     </row>
     <row r="124">
@@ -8011,7 +8011,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>3441.43</v>
+        <v>3451.4</v>
       </c>
     </row>
     <row r="125">
@@ -8072,7 +8072,7 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>3373.56</v>
+        <v>3383.33</v>
       </c>
     </row>
     <row r="126">
@@ -8133,7 +8133,7 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>3624.91</v>
+        <v>3635.41</v>
       </c>
     </row>
     <row r="127">
@@ -8194,7 +8194,7 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>13167.11</v>
+        <v>13205.25</v>
       </c>
     </row>
     <row r="128">
@@ -8255,7 +8255,7 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>3792.17</v>
+        <v>3803.16</v>
       </c>
     </row>
     <row r="129">
@@ -8316,7 +8316,7 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>6918.33</v>
+        <v>6938.37</v>
       </c>
     </row>
     <row r="130">
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>23824.46</v>
+        <v>23893.48</v>
       </c>
     </row>
     <row r="131">
@@ -8438,7 +8438,7 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>4296.5</v>
+        <v>4308.95</v>
       </c>
     </row>
     <row r="132">
@@ -8499,7 +8499,7 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>2586.08</v>
+        <v>2593.57</v>
       </c>
     </row>
     <row r="133">
@@ -8560,7 +8560,7 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>5122.54</v>
+        <v>5137.38</v>
       </c>
     </row>
     <row r="134">
@@ -8621,7 +8621,7 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>858.21</v>
+        <v>860.7</v>
       </c>
     </row>
     <row r="135">
@@ -8682,7 +8682,7 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>1528.95</v>
+        <v>1533.38</v>
       </c>
     </row>
     <row r="136">
@@ -8743,7 +8743,7 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>2670.94</v>
+        <v>2678.68</v>
       </c>
     </row>
     <row r="137">
@@ -8804,7 +8804,7 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>1861.69</v>
+        <v>1867.09</v>
       </c>
     </row>
     <row r="138">
@@ -8865,7 +8865,7 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>2129.77</v>
+        <v>2135.94</v>
       </c>
     </row>
     <row r="139">
@@ -8926,7 +8926,7 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>6951.8</v>
+        <v>6971.94</v>
       </c>
     </row>
     <row r="140">
@@ -8987,7 +8987,7 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>3717.45</v>
+        <v>3728.22</v>
       </c>
     </row>
     <row r="141">
@@ -9048,7 +9048,7 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>4688.51</v>
+        <v>4702.09</v>
       </c>
     </row>
     <row r="142">
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>3858.16</v>
+        <v>3869.33</v>
       </c>
     </row>
     <row r="143">
@@ -9170,7 +9170,7 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>4101.55</v>
+        <v>4113.43</v>
       </c>
     </row>
     <row r="144">
@@ -9231,7 +9231,7 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>5265.02</v>
+        <v>5280.27</v>
       </c>
     </row>
     <row r="145">
@@ -9292,7 +9292,7 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>2494.72</v>
+        <v>2501.94</v>
       </c>
     </row>
     <row r="146">
@@ -9353,7 +9353,7 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>2333.56</v>
+        <v>2340.32</v>
       </c>
     </row>
     <row r="147">
@@ -9414,7 +9414,7 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>1668.28</v>
+        <v>1673.11</v>
       </c>
     </row>
     <row r="148">
@@ -9475,7 +9475,7 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>5406.72</v>
+        <v>5434.65</v>
       </c>
     </row>
     <row r="149">
@@ -9536,7 +9536,7 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>2399.55</v>
+        <v>2411.94</v>
       </c>
     </row>
     <row r="150">
@@ -9597,7 +9597,7 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>2436.7</v>
+        <v>2449.28</v>
       </c>
     </row>
     <row r="151">
@@ -9658,7 +9658,7 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>1427.47</v>
+        <v>1434.84</v>
       </c>
     </row>
     <row r="152">
@@ -9719,7 +9719,7 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>3308.59</v>
+        <v>3325.68</v>
       </c>
     </row>
     <row r="153">
@@ -9780,7 +9780,7 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>2994.52</v>
+        <v>3009.99</v>
       </c>
     </row>
     <row r="154">
@@ -9841,7 +9841,7 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>7605.17</v>
+        <v>7644.45</v>
       </c>
     </row>
     <row r="155">
@@ -9902,7 +9902,7 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>3378.67</v>
+        <v>3396.12</v>
       </c>
     </row>
     <row r="156">
@@ -9963,7 +9963,7 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>8159.84</v>
+        <v>8201.99</v>
       </c>
     </row>
     <row r="157">
@@ -10024,7 +10024,7 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>18011.25</v>
+        <v>18104.29</v>
       </c>
     </row>
     <row r="158">
@@ -10085,7 +10085,7 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>1019.36</v>
+        <v>1024.62</v>
       </c>
     </row>
     <row r="159">
@@ -10146,7 +10146,7 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>46851.86</v>
+        <v>47093.88</v>
       </c>
     </row>
     <row r="160">
@@ -10207,7 +10207,7 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>14106.68</v>
+        <v>14179.55</v>
       </c>
     </row>
     <row r="161">
@@ -10268,7 +10268,7 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>7274.79</v>
+        <v>7312.37</v>
       </c>
     </row>
     <row r="162">
@@ -10329,7 +10329,7 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>2129.65</v>
+        <v>2140.65</v>
       </c>
     </row>
     <row r="163">
@@ -10390,7 +10390,7 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>2124.86</v>
+        <v>2135.84</v>
       </c>
     </row>
     <row r="164">
@@ -10451,7 +10451,7 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>1868.82</v>
+        <v>1878.48</v>
       </c>
     </row>
     <row r="165">
@@ -10512,7 +10512,7 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>2683.24</v>
+        <v>2697.1</v>
       </c>
     </row>
     <row r="166">
@@ -10573,7 +10573,7 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>2697.22</v>
+        <v>2711.15</v>
       </c>
     </row>
     <row r="167">
@@ -10634,7 +10634,7 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>868.2</v>
+        <v>872.6900000000001</v>
       </c>
     </row>
     <row r="168">
@@ -10695,7 +10695,7 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>9897.08</v>
+        <v>9948.209999999999</v>
       </c>
     </row>
     <row r="169">
@@ -10756,7 +10756,7 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>828.25</v>
+        <v>832.52</v>
       </c>
     </row>
     <row r="170">
@@ -10817,7 +10817,7 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>80364.24000000001</v>
+        <v>80779.37</v>
       </c>
     </row>
     <row r="171">
@@ -10878,7 +10878,7 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>3454.47</v>
+        <v>3472.32</v>
       </c>
     </row>
     <row r="172">
@@ -10939,7 +10939,7 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>3444.24</v>
+        <v>3462.04</v>
       </c>
     </row>
     <row r="173">
@@ -11000,7 +11000,7 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>75093.94</v>
+        <v>75481.85000000001</v>
       </c>
     </row>
     <row r="174">
@@ -11061,7 +11061,7 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>58875.2</v>
+        <v>59179.32</v>
       </c>
     </row>
     <row r="175">
@@ -11122,7 +11122,7 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>1306.85</v>
+        <v>1313.61</v>
       </c>
     </row>
     <row r="176">
@@ -11183,7 +11183,7 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>4588.71</v>
+        <v>4612.41</v>
       </c>
     </row>
     <row r="177">
@@ -11244,7 +11244,7 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>2650.17</v>
+        <v>2663.85</v>
       </c>
     </row>
     <row r="178">
@@ -11305,7 +11305,7 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>6110.88</v>
+        <v>6142.45</v>
       </c>
     </row>
     <row r="179">
@@ -11366,7 +11366,7 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>4455.23</v>
+        <v>4478.25</v>
       </c>
     </row>
     <row r="180">
@@ -11427,7 +11427,7 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>4099.16</v>
+        <v>4120.34</v>
       </c>
     </row>
     <row r="181">
@@ -11488,7 +11488,7 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>8658.77</v>
+        <v>8703.5</v>
       </c>
     </row>
     <row r="182">
@@ -11549,7 +11549,7 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>2768.03</v>
+        <v>2782.33</v>
       </c>
     </row>
     <row r="183">
@@ -11610,7 +11610,7 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>2188.39</v>
+        <v>2199.69</v>
       </c>
     </row>
     <row r="184">
@@ -11671,7 +11671,7 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>9041.35</v>
+        <v>9088.059999999999</v>
       </c>
     </row>
     <row r="185">
@@ -11732,7 +11732,7 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>5180.21</v>
+        <v>5206.97</v>
       </c>
     </row>
     <row r="186">
@@ -11793,7 +11793,7 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>4843.9</v>
+        <v>4868.92</v>
       </c>
     </row>
     <row r="187">
@@ -11854,7 +11854,7 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>1050.65</v>
+        <v>1056.08</v>
       </c>
     </row>
     <row r="188">
@@ -11915,7 +11915,7 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>50963.55</v>
+        <v>51226.8</v>
       </c>
     </row>
     <row r="189">
@@ -11976,7 +11976,7 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>17673.41</v>
+        <v>17764.7</v>
       </c>
     </row>
     <row r="190">
@@ -12037,7 +12037,7 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>21140.52</v>
+        <v>21249.72</v>
       </c>
     </row>
     <row r="191">
@@ -12098,7 +12098,7 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>2918.33</v>
+        <v>2933.41</v>
       </c>
     </row>
     <row r="192">
@@ -12159,7 +12159,7 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>3268.95</v>
+        <v>3285.84</v>
       </c>
     </row>
     <row r="193">
@@ -12220,7 +12220,7 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>2579.7</v>
+        <v>2593.03</v>
       </c>
     </row>
     <row r="194">
@@ -12281,7 +12281,7 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>4255.57</v>
+        <v>4277.56</v>
       </c>
     </row>
     <row r="195">
@@ -12342,7 +12342,7 @@
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>1937.36</v>
+        <v>1947.37</v>
       </c>
     </row>
     <row r="196">
@@ -12403,7 +12403,7 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>815.71</v>
+        <v>819.92</v>
       </c>
     </row>
     <row r="197">
@@ -12464,7 +12464,7 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>3480.12</v>
+        <v>3498.1</v>
       </c>
     </row>
     <row r="198">
@@ -12525,7 +12525,7 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>2233.39</v>
+        <v>2244.93</v>
       </c>
     </row>
     <row r="199">
@@ -12586,7 +12586,7 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>9287.58</v>
+        <v>9335.559999999999</v>
       </c>
     </row>
     <row r="200">
@@ -12647,7 +12647,7 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>2391.47</v>
+        <v>2403.83</v>
       </c>
     </row>
     <row r="201">
@@ -12708,7 +12708,7 @@
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>1663.57</v>
+        <v>1672.16</v>
       </c>
     </row>
     <row r="202">
@@ -12769,7 +12769,7 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>2545.91</v>
+        <v>2559.06</v>
       </c>
     </row>
     <row r="203">
@@ -12830,7 +12830,7 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>1059.4</v>
+        <v>1064.87</v>
       </c>
     </row>
     <row r="204">
@@ -12891,7 +12891,7 @@
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>2016.09</v>
+        <v>2026.51</v>
       </c>
     </row>
     <row r="205">
@@ -12952,7 +12952,7 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>5286.31</v>
+        <v>5313.62</v>
       </c>
     </row>
     <row r="206">
@@ -13013,7 +13013,7 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>12746.65</v>
+        <v>12812.49</v>
       </c>
     </row>
     <row r="207">
@@ -13074,7 +13074,7 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>68035.98</v>
+        <v>68387.42</v>
       </c>
     </row>
     <row r="208">
@@ -13135,7 +13135,7 @@
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>2549.17</v>
+        <v>2562.34</v>
       </c>
     </row>
     <row r="209">
@@ -13196,7 +13196,7 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>2406.6</v>
+        <v>2419.03</v>
       </c>
     </row>
     <row r="210">
@@ -13257,7 +13257,7 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>3683.8</v>
+        <v>3702.83</v>
       </c>
     </row>
     <row r="211">
@@ -13318,7 +13318,7 @@
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>1159.78</v>
+        <v>1154.89</v>
       </c>
     </row>
     <row r="212">
@@ -13379,7 +13379,7 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>1426.63</v>
+        <v>1420.62</v>
       </c>
     </row>
     <row r="213">
@@ -13440,7 +13440,7 @@
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>8200.040000000001</v>
+        <v>8165.47</v>
       </c>
     </row>
     <row r="214">
@@ -13501,7 +13501,7 @@
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>1732.29</v>
+        <v>1724.99</v>
       </c>
     </row>
     <row r="215">
@@ -13562,7 +13562,7 @@
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>10138.23</v>
+        <v>10095.49</v>
       </c>
     </row>
     <row r="216">
@@ -13623,7 +13623,7 @@
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>2981.34</v>
+        <v>2968.77</v>
       </c>
     </row>
     <row r="217">
@@ -13684,7 +13684,7 @@
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>2803.57</v>
+        <v>2791.75</v>
       </c>
     </row>
     <row r="218">
@@ -13745,7 +13745,7 @@
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>4881.37</v>
+        <v>4860.79</v>
       </c>
     </row>
     <row r="219">
@@ -13806,7 +13806,7 @@
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>2811.01</v>
+        <v>2799.16</v>
       </c>
     </row>
     <row r="220">
@@ -13867,7 +13867,7 @@
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>5397.12</v>
+        <v>5374.36</v>
       </c>
     </row>
     <row r="221">
@@ -13928,7 +13928,7 @@
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>3474.4</v>
+        <v>3459.75</v>
       </c>
     </row>
     <row r="222">
@@ -13989,7 +13989,7 @@
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>13245.77</v>
+        <v>13189.92</v>
       </c>
     </row>
     <row r="223">
@@ -14050,7 +14050,7 @@
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>28393.36</v>
+        <v>28273.64</v>
       </c>
     </row>
     <row r="224">
@@ -14111,7 +14111,7 @@
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>10743.28</v>
+        <v>10697.98</v>
       </c>
     </row>
     <row r="225">
@@ -14172,7 +14172,7 @@
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>27428.45</v>
+        <v>27312.8</v>
       </c>
     </row>
     <row r="226">
@@ -14233,7 +14233,7 @@
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>69040.14999999999</v>
+        <v>68749.05</v>
       </c>
     </row>
     <row r="227">
@@ -14294,7 +14294,7 @@
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>3627.65</v>
+        <v>3612.35</v>
       </c>
     </row>
     <row r="228">
@@ -14355,7 +14355,7 @@
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>2761.52</v>
+        <v>2749.88</v>
       </c>
     </row>
     <row r="229">
@@ -14416,7 +14416,7 @@
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>7603.18</v>
+        <v>7571.12</v>
       </c>
     </row>
     <row r="230">
@@ -14477,7 +14477,7 @@
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>5886.3</v>
+        <v>5861.48</v>
       </c>
     </row>
     <row r="231">
@@ -14538,7 +14538,7 @@
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>933.76</v>
+        <v>929.8200000000001</v>
       </c>
     </row>
     <row r="232">
@@ -14599,7 +14599,7 @@
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>1196.85</v>
+        <v>1191.8</v>
       </c>
     </row>
     <row r="233">
@@ -14660,7 +14660,7 @@
         </is>
       </c>
       <c r="M233" s="2" t="n">
-        <v>3565.78</v>
+        <v>3550.74</v>
       </c>
     </row>
     <row r="234">
@@ -14721,7 +14721,7 @@
         </is>
       </c>
       <c r="M234" s="2" t="n">
-        <v>2029.12</v>
+        <v>2020.56</v>
       </c>
     </row>
     <row r="235">
@@ -14782,7 +14782,7 @@
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>3275.05</v>
+        <v>3261.24</v>
       </c>
     </row>
     <row r="236">
@@ -14843,7 +14843,7 @@
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>5441.37</v>
+        <v>5418.43</v>
       </c>
     </row>
     <row r="237">
@@ -14904,7 +14904,7 @@
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>2755.06</v>
+        <v>2743.45</v>
       </c>
     </row>
     <row r="238">
@@ -14965,7 +14965,7 @@
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>3415.3</v>
+        <v>3400.9</v>
       </c>
     </row>
     <row r="239">
@@ -15026,7 +15026,7 @@
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>921.88</v>
+        <v>918</v>
       </c>
     </row>
     <row r="240">
@@ -15087,7 +15087,7 @@
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>1318.94</v>
+        <v>1313.38</v>
       </c>
     </row>
     <row r="241">
@@ -15148,7 +15148,7 @@
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>12071.44</v>
+        <v>12020.54</v>
       </c>
     </row>
     <row r="242">
@@ -15209,7 +15209,7 @@
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>4016.86</v>
+        <v>3999.92</v>
       </c>
     </row>
     <row r="243">
@@ -15270,7 +15270,7 @@
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>77727.81</v>
+        <v>77400.08</v>
       </c>
     </row>
     <row r="244">
@@ -15331,7 +15331,7 @@
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>73886.84</v>
+        <v>73575.3</v>
       </c>
     </row>
     <row r="245">
@@ -15392,7 +15392,7 @@
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>6758.82</v>
+        <v>6730.32</v>
       </c>
     </row>
     <row r="246">
@@ -15453,7 +15453,7 @@
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>4740.31</v>
+        <v>4720.33</v>
       </c>
     </row>
     <row r="247">
@@ -15514,7 +15514,7 @@
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>8177.2</v>
+        <v>8142.72</v>
       </c>
     </row>
     <row r="248">
@@ -15575,7 +15575,7 @@
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>39028.89</v>
+        <v>38864.32</v>
       </c>
     </row>
     <row r="249">
@@ -15636,7 +15636,7 @@
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>27006.71</v>
+        <v>26892.84</v>
       </c>
     </row>
     <row r="250">
@@ -15697,7 +15697,7 @@
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>5361.37</v>
+        <v>5338.77</v>
       </c>
     </row>
     <row r="251">
@@ -15758,7 +15758,7 @@
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>9212.870000000001</v>
+        <v>9174.030000000001</v>
       </c>
     </row>
     <row r="252">
@@ -15819,7 +15819,7 @@
         </is>
       </c>
       <c r="M252" s="2" t="n">
-        <v>4904.28</v>
+        <v>4883.6</v>
       </c>
     </row>
     <row r="253">
@@ -15880,7 +15880,7 @@
         </is>
       </c>
       <c r="M253" s="2" t="n">
-        <v>19071.93</v>
+        <v>18991.51</v>
       </c>
     </row>
     <row r="254">
@@ -15941,7 +15941,7 @@
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>3604.71</v>
+        <v>3589.51</v>
       </c>
     </row>
     <row r="255">
@@ -16002,7 +16002,7 @@
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>5151.89</v>
+        <v>5130.17</v>
       </c>
     </row>
     <row r="256">
@@ -16063,7 +16063,7 @@
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>13004.31</v>
+        <v>12949.48</v>
       </c>
     </row>
     <row r="257">
@@ -16124,7 +16124,7 @@
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>30063.78</v>
+        <v>29937.02</v>
       </c>
     </row>
     <row r="258">
@@ -16185,7 +16185,7 @@
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>3487.78</v>
+        <v>3473.07</v>
       </c>
     </row>
     <row r="259">
@@ -16246,7 +16246,7 @@
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>2165.51</v>
+        <v>2156.38</v>
       </c>
     </row>
     <row r="260">
@@ -16307,7 +16307,7 @@
         </is>
       </c>
       <c r="M260" s="2" t="n">
-        <v>8978.4</v>
+        <v>8940.540000000001</v>
       </c>
     </row>
     <row r="261">
@@ -16368,7 +16368,7 @@
         </is>
       </c>
       <c r="M261" s="2" t="n">
-        <v>14686.94</v>
+        <v>14625.01</v>
       </c>
     </row>
     <row r="262">
@@ -16429,7 +16429,7 @@
         </is>
       </c>
       <c r="M262" s="2" t="n">
-        <v>19982.7</v>
+        <v>19898.45</v>
       </c>
     </row>
     <row r="263">
@@ -16490,7 +16490,7 @@
         </is>
       </c>
       <c r="M263" s="2" t="n">
-        <v>7237.11</v>
+        <v>7206.6</v>
       </c>
     </row>
     <row r="264">
@@ -16551,7 +16551,7 @@
         </is>
       </c>
       <c r="M264" s="2" t="n">
-        <v>9111.6</v>
+        <v>9073.18</v>
       </c>
     </row>
     <row r="265">
@@ -16612,7 +16612,7 @@
         </is>
       </c>
       <c r="M265" s="2" t="n">
-        <v>15416.89</v>
+        <v>15351.88</v>
       </c>
     </row>
     <row r="266">
@@ -16673,7 +16673,7 @@
         </is>
       </c>
       <c r="M266" s="2" t="n">
-        <v>2534.94</v>
+        <v>2524.25</v>
       </c>
     </row>
     <row r="267">
@@ -16734,7 +16734,7 @@
         </is>
       </c>
       <c r="M267" s="2" t="n">
-        <v>2853.33</v>
+        <v>2841.3</v>
       </c>
     </row>
     <row r="268">
@@ -16795,7 +16795,7 @@
         </is>
       </c>
       <c r="M268" s="2" t="n">
-        <v>4589.49</v>
+        <v>4570.14</v>
       </c>
     </row>
     <row r="269">
@@ -16856,7 +16856,7 @@
         </is>
       </c>
       <c r="M269" s="2" t="n">
-        <v>15075.06</v>
+        <v>15116.44</v>
       </c>
     </row>
     <row r="270">
@@ -16917,7 +16917,7 @@
         </is>
       </c>
       <c r="M270" s="2" t="n">
-        <v>2721.15</v>
+        <v>2728.62</v>
       </c>
     </row>
     <row r="271">
@@ -16978,7 +16978,7 @@
         </is>
       </c>
       <c r="M271" s="2" t="n">
-        <v>1188.45</v>
+        <v>1191.72</v>
       </c>
     </row>
     <row r="272">
@@ -17039,7 +17039,7 @@
         </is>
       </c>
       <c r="M272" s="2" t="n">
-        <v>952.15</v>
+        <v>954.76</v>
       </c>
     </row>
     <row r="273">
@@ -17100,7 +17100,7 @@
         </is>
       </c>
       <c r="M273" s="2" t="n">
-        <v>2896.73</v>
+        <v>2904.68</v>
       </c>
     </row>
     <row r="274">
@@ -17161,7 +17161,7 @@
         </is>
       </c>
       <c r="M274" s="2" t="n">
-        <v>4899.24</v>
+        <v>4912.69</v>
       </c>
     </row>
     <row r="275">
@@ -17222,7 +17222,7 @@
         </is>
       </c>
       <c r="M275" s="2" t="n">
-        <v>3716.54</v>
+        <v>3726.74</v>
       </c>
     </row>
     <row r="276">
@@ -17283,7 +17283,7 @@
         </is>
       </c>
       <c r="M276" s="2" t="n">
-        <v>2998.85</v>
+        <v>3007.09</v>
       </c>
     </row>
     <row r="277">
@@ -17344,7 +17344,7 @@
         </is>
       </c>
       <c r="M277" s="2" t="n">
-        <v>4475.25</v>
+        <v>4487.53</v>
       </c>
     </row>
     <row r="278">
@@ -17405,7 +17405,7 @@
         </is>
       </c>
       <c r="M278" s="2" t="n">
-        <v>2635.08</v>
+        <v>2642.32</v>
       </c>
     </row>
     <row r="279">
@@ -17466,7 +17466,7 @@
         </is>
       </c>
       <c r="M279" s="2" t="n">
-        <v>1853.98</v>
+        <v>1859.07</v>
       </c>
     </row>
     <row r="280">
@@ -17527,7 +17527,7 @@
         </is>
       </c>
       <c r="M280" s="2" t="n">
-        <v>10714.89</v>
+        <v>10744.31</v>
       </c>
     </row>
     <row r="281">
@@ -17588,7 +17588,7 @@
         </is>
       </c>
       <c r="M281" s="2" t="n">
-        <v>1591.55</v>
+        <v>1595.92</v>
       </c>
     </row>
     <row r="282">
@@ -17649,7 +17649,7 @@
         </is>
       </c>
       <c r="M282" s="2" t="n">
-        <v>2868.91</v>
+        <v>2876.79</v>
       </c>
     </row>
     <row r="283">
@@ -17710,7 +17710,7 @@
         </is>
       </c>
       <c r="M283" s="2" t="n">
-        <v>4468.73</v>
+        <v>4481</v>
       </c>
     </row>
     <row r="284">
@@ -17771,7 +17771,7 @@
         </is>
       </c>
       <c r="M284" s="2" t="n">
-        <v>842.04</v>
+        <v>844.36</v>
       </c>
     </row>
     <row r="285">
@@ -17832,7 +17832,7 @@
         </is>
       </c>
       <c r="M285" s="2" t="n">
-        <v>995.88</v>
+        <v>998.61</v>
       </c>
     </row>
     <row r="286">
@@ -17893,7 +17893,7 @@
         </is>
       </c>
       <c r="M286" s="2" t="n">
-        <v>944.9</v>
+        <v>947.49</v>
       </c>
     </row>
     <row r="287">
@@ -17954,7 +17954,7 @@
         </is>
       </c>
       <c r="M287" s="2" t="n">
-        <v>4300.89</v>
+        <v>4312.7</v>
       </c>
     </row>
     <row r="288">
@@ -18015,7 +18015,7 @@
         </is>
       </c>
       <c r="M288" s="2" t="n">
-        <v>1860.86</v>
+        <v>1865.97</v>
       </c>
     </row>
     <row r="289">
@@ -18076,7 +18076,7 @@
         </is>
       </c>
       <c r="M289" s="2" t="n">
-        <v>4823.94</v>
+        <v>4837.19</v>
       </c>
     </row>
     <row r="290">
@@ -18137,7 +18137,7 @@
         </is>
       </c>
       <c r="M290" s="2" t="n">
-        <v>2811.41</v>
+        <v>2819.13</v>
       </c>
     </row>
     <row r="291">
@@ -18198,7 +18198,7 @@
         </is>
       </c>
       <c r="M291" s="2" t="n">
-        <v>6795.24</v>
+        <v>6813.89</v>
       </c>
     </row>
     <row r="292">
@@ -18259,7 +18259,7 @@
         </is>
       </c>
       <c r="M292" s="2" t="n">
-        <v>2829.5</v>
+        <v>2837.26</v>
       </c>
     </row>
     <row r="293">
@@ -18320,7 +18320,7 @@
         </is>
       </c>
       <c r="M293" s="2" t="n">
-        <v>15447.06</v>
+        <v>15489.47</v>
       </c>
     </row>
     <row r="294">
@@ -18381,7 +18381,7 @@
         </is>
       </c>
       <c r="M294" s="2" t="n">
-        <v>6572.85</v>
+        <v>6590.9</v>
       </c>
     </row>
     <row r="295">
@@ -18442,7 +18442,7 @@
         </is>
       </c>
       <c r="M295" s="2" t="n">
-        <v>19548.07</v>
+        <v>19601.74</v>
       </c>
     </row>
     <row r="296">
@@ -18503,7 +18503,7 @@
         </is>
       </c>
       <c r="M296" s="2" t="n">
-        <v>2583.98</v>
+        <v>2591.07</v>
       </c>
     </row>
     <row r="297">
@@ -18564,7 +18564,7 @@
         </is>
       </c>
       <c r="M297" s="2" t="n">
-        <v>21689.34</v>
+        <v>21748.88</v>
       </c>
     </row>
     <row r="298">
@@ -18625,7 +18625,7 @@
         </is>
       </c>
       <c r="M298" s="2" t="n">
-        <v>8659.459999999999</v>
+        <v>8683.24</v>
       </c>
     </row>
     <row r="299">
@@ -18686,7 +18686,7 @@
         </is>
       </c>
       <c r="M299" s="2" t="n">
-        <v>9010.6</v>
+        <v>9035.34</v>
       </c>
     </row>
     <row r="300">
@@ -18747,7 +18747,7 @@
         </is>
       </c>
       <c r="M300" s="2" t="n">
-        <v>5754.22</v>
+        <v>5770.02</v>
       </c>
     </row>
     <row r="301">
@@ -18808,7 +18808,7 @@
         </is>
       </c>
       <c r="M301" s="2" t="n">
-        <v>3984.8</v>
+        <v>3995.73</v>
       </c>
     </row>
     <row r="302">
@@ -18869,7 +18869,7 @@
         </is>
       </c>
       <c r="M302" s="2" t="n">
-        <v>5915.66</v>
+        <v>5931.9</v>
       </c>
     </row>
     <row r="303">
@@ -18930,7 +18930,7 @@
         </is>
       </c>
       <c r="M303" s="2" t="n">
-        <v>5272.08</v>
+        <v>5286.55</v>
       </c>
     </row>
     <row r="304">
@@ -18991,7 +18991,7 @@
         </is>
       </c>
       <c r="M304" s="2" t="n">
-        <v>1598.18</v>
+        <v>1602.57</v>
       </c>
     </row>
     <row r="305">
@@ -19052,7 +19052,7 @@
         </is>
       </c>
       <c r="M305" s="2" t="n">
-        <v>15060.94</v>
+        <v>15102.29</v>
       </c>
     </row>
     <row r="306">
@@ -19113,7 +19113,7 @@
         </is>
       </c>
       <c r="M306" s="2" t="n">
-        <v>1461.62</v>
+        <v>1465.64</v>
       </c>
     </row>
     <row r="307">
@@ -19174,7 +19174,7 @@
         </is>
       </c>
       <c r="M307" s="2" t="n">
-        <v>6819.43</v>
+        <v>6838.15</v>
       </c>
     </row>
     <row r="308">
@@ -19235,7 +19235,7 @@
         </is>
       </c>
       <c r="M308" s="2" t="n">
-        <v>1207.44</v>
+        <v>1218.42</v>
       </c>
     </row>
     <row r="309">
@@ -19296,7 +19296,7 @@
         </is>
       </c>
       <c r="M309" s="2" t="n">
-        <v>5800.89</v>
+        <v>5853.65</v>
       </c>
     </row>
     <row r="310">
@@ -19357,7 +19357,7 @@
         </is>
       </c>
       <c r="M310" s="2" t="n">
-        <v>41866.11</v>
+        <v>42246.91</v>
       </c>
     </row>
     <row r="311">
@@ -19418,7 +19418,7 @@
         </is>
       </c>
       <c r="M311" s="2" t="n">
-        <v>30058.62</v>
+        <v>30332.03</v>
       </c>
     </row>
     <row r="312">
@@ -19479,7 +19479,7 @@
         </is>
       </c>
       <c r="M312" s="2" t="n">
-        <v>1173.68</v>
+        <v>1184.36</v>
       </c>
     </row>
     <row r="313">
@@ -19540,7 +19540,7 @@
         </is>
       </c>
       <c r="M313" s="2" t="n">
-        <v>2529.76</v>
+        <v>2552.77</v>
       </c>
     </row>
     <row r="314">
@@ -19601,7 +19601,7 @@
         </is>
       </c>
       <c r="M314" s="2" t="n">
-        <v>1140.81</v>
+        <v>1151.19</v>
       </c>
     </row>
     <row r="315">
@@ -19662,7 +19662,7 @@
         </is>
       </c>
       <c r="M315" s="2" t="n">
-        <v>1937.39</v>
+        <v>1955.01</v>
       </c>
     </row>
     <row r="316">
@@ -19723,7 +19723,7 @@
         </is>
       </c>
       <c r="M316" s="2" t="n">
-        <v>2422.71</v>
+        <v>2444.74</v>
       </c>
     </row>
     <row r="317">
@@ -19784,7 +19784,7 @@
         </is>
       </c>
       <c r="M317" s="2" t="n">
-        <v>14813.16</v>
+        <v>14947.9</v>
       </c>
     </row>
     <row r="318">
@@ -19845,7 +19845,7 @@
         </is>
       </c>
       <c r="M318" s="2" t="n">
-        <v>2999.95</v>
+        <v>3027.23</v>
       </c>
     </row>
     <row r="319">
@@ -19906,7 +19906,7 @@
         </is>
       </c>
       <c r="M319" s="2" t="n">
-        <v>1846.87</v>
+        <v>1863.67</v>
       </c>
     </row>
     <row r="320">
@@ -19967,7 +19967,7 @@
         </is>
       </c>
       <c r="M320" s="2" t="n">
-        <v>20910.11</v>
+        <v>21100.3</v>
       </c>
     </row>
     <row r="321">
@@ -20028,7 +20028,7 @@
         </is>
       </c>
       <c r="M321" s="2" t="n">
-        <v>9240.77</v>
+        <v>9324.82</v>
       </c>
     </row>
     <row r="322">
@@ -20089,7 +20089,7 @@
         </is>
       </c>
       <c r="M322" s="2" t="n">
-        <v>1360.2</v>
+        <v>1372.57</v>
       </c>
     </row>
     <row r="323">
@@ -20150,7 +20150,7 @@
         </is>
       </c>
       <c r="M323" s="2" t="n">
-        <v>11781.05</v>
+        <v>11888.2</v>
       </c>
     </row>
     <row r="324">
@@ -20211,7 +20211,7 @@
         </is>
       </c>
       <c r="M324" s="2" t="n">
-        <v>25299.08</v>
+        <v>25529.2</v>
       </c>
     </row>
     <row r="325">
@@ -20272,7 +20272,7 @@
         </is>
       </c>
       <c r="M325" s="2" t="n">
-        <v>16891.29</v>
+        <v>17044.93</v>
       </c>
     </row>
     <row r="326">
@@ -20333,7 +20333,7 @@
         </is>
       </c>
       <c r="M326" s="2" t="n">
-        <v>868.71</v>
+        <v>876.61</v>
       </c>
     </row>
     <row r="327">
@@ -20394,7 +20394,7 @@
         </is>
       </c>
       <c r="M327" s="2" t="n">
-        <v>4667.26</v>
+        <v>4709.71</v>
       </c>
     </row>
     <row r="328">
@@ -20455,7 +20455,7 @@
         </is>
       </c>
       <c r="M328" s="2" t="n">
-        <v>6767.39</v>
+        <v>6828.94</v>
       </c>
     </row>
     <row r="329">
@@ -20516,7 +20516,7 @@
         </is>
       </c>
       <c r="M329" s="2" t="n">
-        <v>1958.79</v>
+        <v>1976.6</v>
       </c>
     </row>
     <row r="330">
@@ -20577,7 +20577,7 @@
         </is>
       </c>
       <c r="M330" s="2" t="n">
-        <v>2814.23</v>
+        <v>2839.83</v>
       </c>
     </row>
     <row r="331">
@@ -20638,7 +20638,7 @@
         </is>
       </c>
       <c r="M331" s="2" t="n">
-        <v>1001.54</v>
+        <v>1010.65</v>
       </c>
     </row>
     <row r="332">
@@ -20699,7 +20699,7 @@
         </is>
       </c>
       <c r="M332" s="2" t="n">
-        <v>2508.61</v>
+        <v>2531.42</v>
       </c>
     </row>
     <row r="333">
@@ -20760,7 +20760,7 @@
         </is>
       </c>
       <c r="M333" s="2" t="n">
-        <v>19747.45</v>
+        <v>19927.07</v>
       </c>
     </row>
     <row r="334">
@@ -20821,7 +20821,7 @@
         </is>
       </c>
       <c r="M334" s="2" t="n">
-        <v>3414.14</v>
+        <v>3445.2</v>
       </c>
     </row>
     <row r="335">
@@ -20882,7 +20882,7 @@
         </is>
       </c>
       <c r="M335" s="2" t="n">
-        <v>2375.8</v>
+        <v>2397.41</v>
       </c>
     </row>
     <row r="336">
@@ -20943,7 +20943,7 @@
         </is>
       </c>
       <c r="M336" s="2" t="n">
-        <v>3218.37</v>
+        <v>3247.65</v>
       </c>
     </row>
     <row r="337">
@@ -21004,7 +21004,7 @@
         </is>
       </c>
       <c r="M337" s="2" t="n">
-        <v>2057.74</v>
+        <v>2076.46</v>
       </c>
     </row>
     <row r="338">
@@ -21065,7 +21065,7 @@
         </is>
       </c>
       <c r="M338" s="2" t="n">
-        <v>9277.280000000001</v>
+        <v>9361.67</v>
       </c>
     </row>
     <row r="339">
@@ -21126,7 +21126,7 @@
         </is>
       </c>
       <c r="M339" s="2" t="n">
-        <v>7214.66</v>
+        <v>7280.28</v>
       </c>
     </row>
     <row r="340">
@@ -21187,7 +21187,7 @@
         </is>
       </c>
       <c r="M340" s="2" t="n">
-        <v>9280.530000000001</v>
+        <v>9364.940000000001</v>
       </c>
     </row>
     <row r="341">
@@ -21248,7 +21248,7 @@
         </is>
       </c>
       <c r="M341" s="2" t="n">
-        <v>7247.41</v>
+        <v>7313.33</v>
       </c>
     </row>
     <row r="342">
@@ -21309,7 +21309,7 @@
         </is>
       </c>
       <c r="M342" s="2" t="n">
-        <v>15709.84</v>
+        <v>15852.74</v>
       </c>
     </row>
     <row r="343">
@@ -21370,7 +21370,7 @@
         </is>
       </c>
       <c r="M343" s="2" t="n">
-        <v>5723.84</v>
+        <v>5775.91</v>
       </c>
     </row>
     <row r="344">
@@ -21431,7 +21431,7 @@
         </is>
       </c>
       <c r="M344" s="2" t="n">
-        <v>26861.35</v>
+        <v>27105.67</v>
       </c>
     </row>
     <row r="345">
@@ -21492,7 +21492,7 @@
         </is>
       </c>
       <c r="M345" s="2" t="n">
-        <v>821.05</v>
+        <v>828.52</v>
       </c>
     </row>
     <row r="346">
@@ -21553,7 +21553,7 @@
         </is>
       </c>
       <c r="M346" s="2" t="n">
-        <v>855.39</v>
+        <v>861.34</v>
       </c>
     </row>
     <row r="347">
@@ -21614,7 +21614,7 @@
         </is>
       </c>
       <c r="M347" s="2" t="n">
-        <v>1641.24</v>
+        <v>1652.66</v>
       </c>
     </row>
     <row r="348">
@@ -21675,7 +21675,7 @@
         </is>
       </c>
       <c r="M348" s="2" t="n">
-        <v>3456.86</v>
+        <v>3480.93</v>
       </c>
     </row>
     <row r="349">
@@ -21736,7 +21736,7 @@
         </is>
       </c>
       <c r="M349" s="2" t="n">
-        <v>8961.309999999999</v>
+        <v>9023.700000000001</v>
       </c>
     </row>
     <row r="350">
@@ -21797,7 +21797,7 @@
         </is>
       </c>
       <c r="M350" s="2" t="n">
-        <v>7615.41</v>
+        <v>7668.43</v>
       </c>
     </row>
     <row r="351">
@@ -21858,7 +21858,7 @@
         </is>
       </c>
       <c r="M351" s="2" t="n">
-        <v>1158.59</v>
+        <v>1166.65</v>
       </c>
     </row>
     <row r="352">
@@ -21919,7 +21919,7 @@
         </is>
       </c>
       <c r="M352" s="2" t="n">
-        <v>8144.51</v>
+        <v>8201.209999999999</v>
       </c>
     </row>
     <row r="353">
@@ -21980,7 +21980,7 @@
         </is>
       </c>
       <c r="M353" s="2" t="n">
-        <v>1050.72</v>
+        <v>1058.04</v>
       </c>
     </row>
     <row r="354">
@@ -22041,7 +22041,7 @@
         </is>
       </c>
       <c r="M354" s="2" t="n">
-        <v>3795.35</v>
+        <v>3821.77</v>
       </c>
     </row>
     <row r="355">
@@ -22102,7 +22102,7 @@
         </is>
       </c>
       <c r="M355" s="2" t="n">
-        <v>852.0599999999999</v>
+        <v>857.99</v>
       </c>
     </row>
     <row r="356">
@@ -22163,7 +22163,7 @@
         </is>
       </c>
       <c r="M356" s="2" t="n">
-        <v>19844.61</v>
+        <v>19982.77</v>
       </c>
     </row>
     <row r="357">
@@ -22224,7 +22224,7 @@
         </is>
       </c>
       <c r="M357" s="2" t="n">
-        <v>1304.08</v>
+        <v>1313.16</v>
       </c>
     </row>
     <row r="358">
@@ -22285,7 +22285,7 @@
         </is>
       </c>
       <c r="M358" s="2" t="n">
-        <v>3297.69</v>
+        <v>3320.65</v>
       </c>
     </row>
     <row r="359">
@@ -22346,7 +22346,7 @@
         </is>
       </c>
       <c r="M359" s="2" t="n">
-        <v>3719.01</v>
+        <v>3744.9</v>
       </c>
     </row>
     <row r="360">
@@ -22407,7 +22407,7 @@
         </is>
       </c>
       <c r="M360" s="2" t="n">
-        <v>2093.19</v>
+        <v>2107.76</v>
       </c>
     </row>
     <row r="361">
@@ -22468,7 +22468,7 @@
         </is>
       </c>
       <c r="M361" s="2" t="n">
-        <v>8691.889999999999</v>
+        <v>8752.4</v>
       </c>
     </row>
     <row r="362">
@@ -22529,7 +22529,7 @@
         </is>
       </c>
       <c r="M362" s="2" t="n">
-        <v>12059.04</v>
+        <v>12142.99</v>
       </c>
     </row>
     <row r="363">
@@ -22590,7 +22590,7 @@
         </is>
       </c>
       <c r="M363" s="2" t="n">
-        <v>2981.44</v>
+        <v>3002.19</v>
       </c>
     </row>
     <row r="364">
@@ -22651,7 +22651,7 @@
         </is>
       </c>
       <c r="M364" s="2" t="n">
-        <v>7667.87</v>
+        <v>7721.25</v>
       </c>
     </row>
     <row r="365">
@@ -22712,7 +22712,7 @@
         </is>
       </c>
       <c r="M365" s="2" t="n">
-        <v>3491.48</v>
+        <v>3515.79</v>
       </c>
     </row>
     <row r="366">
@@ -22773,7 +22773,7 @@
         </is>
       </c>
       <c r="M366" s="2" t="n">
-        <v>25923.02</v>
+        <v>26103.5</v>
       </c>
     </row>
     <row r="367">
@@ -22834,7 +22834,7 @@
         </is>
       </c>
       <c r="M367" s="2" t="n">
-        <v>2441.31</v>
+        <v>2458.31</v>
       </c>
     </row>
     <row r="368">
@@ -22895,7 +22895,7 @@
         </is>
       </c>
       <c r="M368" s="2" t="n">
-        <v>13370.62</v>
+        <v>13463.71</v>
       </c>
     </row>
     <row r="369">
@@ -22956,7 +22956,7 @@
         </is>
       </c>
       <c r="M369" s="2" t="n">
-        <v>3607.41</v>
+        <v>3632.53</v>
       </c>
     </row>
     <row r="370">
@@ -23017,7 +23017,7 @@
         </is>
       </c>
       <c r="M370" s="2" t="n">
-        <v>1456.68</v>
+        <v>1466.83</v>
       </c>
     </row>
     <row r="371">
@@ -23078,7 +23078,7 @@
         </is>
       </c>
       <c r="M371" s="2" t="n">
-        <v>8788.129999999999</v>
+        <v>8849.309999999999</v>
       </c>
     </row>
     <row r="372">
@@ -23139,7 +23139,7 @@
         </is>
       </c>
       <c r="M372" s="2" t="n">
-        <v>4431.83</v>
+        <v>4462.69</v>
       </c>
     </row>
     <row r="373">
@@ -23200,7 +23200,7 @@
         </is>
       </c>
       <c r="M373" s="2" t="n">
-        <v>2542.28</v>
+        <v>2559.97</v>
       </c>
     </row>
     <row r="374">
@@ -23261,7 +23261,7 @@
         </is>
       </c>
       <c r="M374" s="2" t="n">
-        <v>2894.45</v>
+        <v>2914.6</v>
       </c>
     </row>
     <row r="375">
@@ -23322,7 +23322,7 @@
         </is>
       </c>
       <c r="M375" s="2" t="n">
-        <v>3097.53</v>
+        <v>3119.1</v>
       </c>
     </row>
     <row r="376">
@@ -23383,7 +23383,7 @@
         </is>
       </c>
       <c r="M376" s="2" t="n">
-        <v>1220.2</v>
+        <v>1228.69</v>
       </c>
     </row>
     <row r="377">
@@ -23444,7 +23444,7 @@
         </is>
       </c>
       <c r="M377" s="2" t="n">
-        <v>1216.99</v>
+        <v>1225.46</v>
       </c>
     </row>
     <row r="378">
@@ -23505,7 +23505,7 @@
         </is>
       </c>
       <c r="M378" s="2" t="n">
-        <v>11957.07</v>
+        <v>12040.32</v>
       </c>
     </row>
     <row r="379">
@@ -23566,7 +23566,7 @@
         </is>
       </c>
       <c r="M379" s="2" t="n">
-        <v>1507.03</v>
+        <v>1517.52</v>
       </c>
     </row>
     <row r="380">
@@ -23627,7 +23627,7 @@
         </is>
       </c>
       <c r="M380" s="2" t="n">
-        <v>9897.98</v>
+        <v>9966.889999999999</v>
       </c>
     </row>
     <row r="381">
@@ -23688,7 +23688,7 @@
         </is>
       </c>
       <c r="M381" s="2" t="n">
-        <v>2922.2</v>
+        <v>2942.54</v>
       </c>
     </row>
     <row r="382">
@@ -23749,7 +23749,7 @@
         </is>
       </c>
       <c r="M382" s="2" t="n">
-        <v>3224.42</v>
+        <v>3246.87</v>
       </c>
     </row>
     <row r="383">
@@ -23810,7 +23810,7 @@
         </is>
       </c>
       <c r="M383" s="2" t="n">
-        <v>5337.96</v>
+        <v>5375.13</v>
       </c>
     </row>
     <row r="384">
@@ -23871,7 +23871,7 @@
         </is>
       </c>
       <c r="M384" s="2" t="n">
-        <v>3360.72</v>
+        <v>3384.12</v>
       </c>
     </row>
     <row r="385">
@@ -23932,7 +23932,7 @@
         </is>
       </c>
       <c r="M385" s="2" t="n">
-        <v>40187.83</v>
+        <v>40467.62</v>
       </c>
     </row>
     <row r="386">
@@ -23993,7 +23993,7 @@
         </is>
       </c>
       <c r="M386" s="2" t="n">
-        <v>24821</v>
+        <v>24993.81</v>
       </c>
     </row>
     <row r="387">
@@ -24054,7 +24054,7 @@
         </is>
       </c>
       <c r="M387" s="2" t="n">
-        <v>65209.42</v>
+        <v>65663.42</v>
       </c>
     </row>
     <row r="388">
@@ -24115,7 +24115,7 @@
         </is>
       </c>
       <c r="M388" s="2" t="n">
-        <v>9226.91</v>
+        <v>9291.15</v>
       </c>
     </row>
     <row r="389">
@@ -24176,7 +24176,7 @@
         </is>
       </c>
       <c r="M389" s="2" t="n">
-        <v>44048.98</v>
+        <v>44355.65</v>
       </c>
     </row>
     <row r="390">
@@ -24237,7 +24237,7 @@
         </is>
       </c>
       <c r="M390" s="2" t="n">
-        <v>4009.97</v>
+        <v>4037.89</v>
       </c>
     </row>
     <row r="391">
@@ -24298,7 +24298,7 @@
         </is>
       </c>
       <c r="M391" s="2" t="n">
-        <v>5500.42</v>
+        <v>5538.71</v>
       </c>
     </row>
     <row r="392">
@@ -24359,7 +24359,7 @@
         </is>
       </c>
       <c r="M392" s="2" t="n">
-        <v>17728.79</v>
+        <v>17852.22</v>
       </c>
     </row>
     <row r="393">
@@ -24420,7 +24420,7 @@
         </is>
       </c>
       <c r="M393" s="2" t="n">
-        <v>30870.31</v>
+        <v>31085.24</v>
       </c>
     </row>
     <row r="394">
@@ -24481,7 +24481,7 @@
         </is>
       </c>
       <c r="M394" s="2" t="n">
-        <v>7390.54</v>
+        <v>7441.99</v>
       </c>
     </row>
     <row r="395">
@@ -24542,7 +24542,7 @@
         </is>
       </c>
       <c r="M395" s="2" t="n">
-        <v>2706.08</v>
+        <v>2724.92</v>
       </c>
     </row>
     <row r="396">
@@ -24603,7 +24603,7 @@
         </is>
       </c>
       <c r="M396" s="2" t="n">
-        <v>2437.92</v>
+        <v>2454.9</v>
       </c>
     </row>
     <row r="397">
@@ -24664,7 +24664,7 @@
         </is>
       </c>
       <c r="M397" s="2" t="n">
-        <v>868.0599999999999</v>
+        <v>874.1</v>
       </c>
     </row>
     <row r="398">
@@ -24725,7 +24725,7 @@
         </is>
       </c>
       <c r="M398" s="2" t="n">
-        <v>2107.3</v>
+        <v>2121.97</v>
       </c>
     </row>
     <row r="399">
@@ -24786,7 +24786,7 @@
         </is>
       </c>
       <c r="M399" s="2" t="n">
-        <v>1783.62</v>
+        <v>1796.04</v>
       </c>
     </row>
     <row r="400">
@@ -24847,7 +24847,7 @@
         </is>
       </c>
       <c r="M400" s="2" t="n">
-        <v>3273.38</v>
+        <v>3296.17</v>
       </c>
     </row>
     <row r="401">
@@ -24908,7 +24908,7 @@
         </is>
       </c>
       <c r="M401" s="2" t="n">
-        <v>16679.74</v>
+        <v>16795.86</v>
       </c>
     </row>
     <row r="402">
@@ -24969,7 +24969,7 @@
         </is>
       </c>
       <c r="M402" s="2" t="n">
-        <v>1330.59</v>
+        <v>1339.85</v>
       </c>
     </row>
     <row r="403">
@@ -25030,7 +25030,7 @@
         </is>
       </c>
       <c r="M403" s="2" t="n">
-        <v>812.49</v>
+        <v>818.14</v>
       </c>
     </row>
     <row r="404">
@@ -25091,7 +25091,7 @@
         </is>
       </c>
       <c r="M404" s="2" t="n">
-        <v>12740.16</v>
+        <v>12828.86</v>
       </c>
     </row>
     <row r="405">
@@ -25152,7 +25152,7 @@
         </is>
       </c>
       <c r="M405" s="2" t="n">
-        <v>4057.85</v>
+        <v>4086.1</v>
       </c>
     </row>
     <row r="406">
@@ -25213,7 +25213,7 @@
         </is>
       </c>
       <c r="M406" s="2" t="n">
-        <v>18498.52</v>
+        <v>18627.31</v>
       </c>
     </row>
     <row r="407">
@@ -25274,7 +25274,7 @@
         </is>
       </c>
       <c r="M407" s="2" t="n">
-        <v>2142.2</v>
+        <v>2157.11</v>
       </c>
     </row>
     <row r="408">
@@ -25335,7 +25335,7 @@
         </is>
       </c>
       <c r="M408" s="2" t="n">
-        <v>2884.79</v>
+        <v>2904.87</v>
       </c>
     </row>
     <row r="409">
@@ -25396,7 +25396,7 @@
         </is>
       </c>
       <c r="M409" s="2" t="n">
-        <v>6850.5</v>
+        <v>6898.19</v>
       </c>
     </row>
     <row r="410">
@@ -25457,7 +25457,7 @@
         </is>
       </c>
       <c r="M410" s="2" t="n">
-        <v>816.17</v>
+        <v>821.85</v>
       </c>
     </row>
     <row r="411">
@@ -25518,7 +25518,7 @@
         </is>
       </c>
       <c r="M411" s="2" t="n">
-        <v>4440.2</v>
+        <v>4469.44</v>
       </c>
     </row>
     <row r="412">
@@ -25579,7 +25579,7 @@
         </is>
       </c>
       <c r="M412" s="2" t="n">
-        <v>74463.00999999999</v>
+        <v>74953.41</v>
       </c>
     </row>
     <row r="413">
@@ -25640,7 +25640,7 @@
         </is>
       </c>
       <c r="M413" s="2" t="n">
-        <v>2331.15</v>
+        <v>2346.51</v>
       </c>
     </row>
     <row r="414">
@@ -25701,7 +25701,7 @@
         </is>
       </c>
       <c r="M414" s="2" t="n">
-        <v>2062.43</v>
+        <v>2076.02</v>
       </c>
     </row>
     <row r="415">
@@ -25762,7 +25762,7 @@
         </is>
       </c>
       <c r="M415" s="2" t="n">
-        <v>3243.77</v>
+        <v>3265.13</v>
       </c>
     </row>
     <row r="416">
@@ -25823,7 +25823,7 @@
         </is>
       </c>
       <c r="M416" s="2" t="n">
-        <v>1327.91</v>
+        <v>1336.66</v>
       </c>
     </row>
     <row r="417">
@@ -25884,7 +25884,7 @@
         </is>
       </c>
       <c r="M417" s="2" t="n">
-        <v>2064.99</v>
+        <v>2078.59</v>
       </c>
     </row>
     <row r="418">
@@ -25945,7 +25945,7 @@
         </is>
       </c>
       <c r="M418" s="2" t="n">
-        <v>7475.35</v>
+        <v>7524.58</v>
       </c>
     </row>
     <row r="419">
@@ -26006,7 +26006,7 @@
         </is>
       </c>
       <c r="M419" s="2" t="n">
-        <v>2030.57</v>
+        <v>2043.94</v>
       </c>
     </row>
     <row r="420">
@@ -26067,7 +26067,7 @@
         </is>
       </c>
       <c r="M420" s="2" t="n">
-        <v>2834.84</v>
+        <v>2853.51</v>
       </c>
     </row>
     <row r="421">
@@ -26128,7 +26128,7 @@
         </is>
       </c>
       <c r="M421" s="2" t="n">
-        <v>3411.85</v>
+        <v>3434.32</v>
       </c>
     </row>
     <row r="422">
@@ -26189,7 +26189,7 @@
         </is>
       </c>
       <c r="M422" s="2" t="n">
-        <v>2461.27</v>
+        <v>2477.48</v>
       </c>
     </row>
     <row r="423">
@@ -26250,7 +26250,7 @@
         </is>
       </c>
       <c r="M423" s="2" t="n">
-        <v>2884.59</v>
+        <v>2903.59</v>
       </c>
     </row>
     <row r="424">
@@ -26311,7 +26311,7 @@
         </is>
       </c>
       <c r="M424" s="2" t="n">
-        <v>1702.13</v>
+        <v>1713.34</v>
       </c>
     </row>
     <row r="425">
@@ -26372,7 +26372,7 @@
         </is>
       </c>
       <c r="M425" s="2" t="n">
-        <v>6773.08</v>
+        <v>6817.68</v>
       </c>
     </row>
     <row r="426">
@@ -26433,7 +26433,7 @@
         </is>
       </c>
       <c r="M426" s="2" t="n">
-        <v>3018.46</v>
+        <v>3038.34</v>
       </c>
     </row>
     <row r="427">
@@ -26494,7 +26494,7 @@
         </is>
       </c>
       <c r="M427" s="2" t="n">
-        <v>1739.63</v>
+        <v>1751.09</v>
       </c>
     </row>
     <row r="428">
@@ -26555,7 +26555,7 @@
         </is>
       </c>
       <c r="M428" s="2" t="n">
-        <v>4180.09</v>
+        <v>4207.62</v>
       </c>
     </row>
     <row r="429">
@@ -26616,7 +26616,7 @@
         </is>
       </c>
       <c r="M429" s="2" t="n">
-        <v>10313.28</v>
+        <v>10381.2</v>
       </c>
     </row>
     <row r="430">
@@ -26677,7 +26677,7 @@
         </is>
       </c>
       <c r="M430" s="2" t="n">
-        <v>1395.46</v>
+        <v>1404.65</v>
       </c>
     </row>
     <row r="431">
@@ -26738,7 +26738,7 @@
         </is>
       </c>
       <c r="M431" s="2" t="n">
-        <v>2870.01</v>
+        <v>2888.92</v>
       </c>
     </row>
     <row r="432">
@@ -26799,7 +26799,7 @@
         </is>
       </c>
       <c r="M432" s="2" t="n">
-        <v>2040.66</v>
+        <v>2054.1</v>
       </c>
     </row>
     <row r="433">
@@ -26860,7 +26860,7 @@
         </is>
       </c>
       <c r="M433" s="2" t="n">
-        <v>5578.81</v>
+        <v>5615.55</v>
       </c>
     </row>
     <row r="434">
@@ -26921,7 +26921,7 @@
         </is>
       </c>
       <c r="M434" s="2" t="n">
-        <v>1122.34</v>
+        <v>1129.73</v>
       </c>
     </row>
     <row r="435">
@@ -26982,7 +26982,7 @@
         </is>
       </c>
       <c r="M435" s="2" t="n">
-        <v>12374.61</v>
+        <v>12456.11</v>
       </c>
     </row>
     <row r="436">
@@ -27043,7 +27043,7 @@
         </is>
       </c>
       <c r="M436" s="2" t="n">
-        <v>6046.85</v>
+        <v>6086.68</v>
       </c>
     </row>
     <row r="437">
@@ -27104,7 +27104,7 @@
         </is>
       </c>
       <c r="M437" s="2" t="n">
-        <v>1065.13</v>
+        <v>1072.14</v>
       </c>
     </row>
     <row r="438">
@@ -27165,7 +27165,7 @@
         </is>
       </c>
       <c r="M438" s="2" t="n">
-        <v>970.08</v>
+        <v>976.47</v>
       </c>
     </row>
     <row r="439">
@@ -27226,7 +27226,7 @@
         </is>
       </c>
       <c r="M439" s="2" t="n">
-        <v>3151.89</v>
+        <v>3172.65</v>
       </c>
     </row>
     <row r="440">
@@ -27287,7 +27287,7 @@
         </is>
       </c>
       <c r="M440" s="2" t="n">
-        <v>5440.88</v>
+        <v>5476.72</v>
       </c>
     </row>
     <row r="441">
@@ -27348,7 +27348,7 @@
         </is>
       </c>
       <c r="M441" s="2" t="n">
-        <v>2706.08</v>
+        <v>2723.9</v>
       </c>
     </row>
     <row r="442">
@@ -27409,7 +27409,7 @@
         </is>
       </c>
       <c r="M442" s="2" t="n">
-        <v>8859.08</v>
+        <v>8917.43</v>
       </c>
     </row>
     <row r="443">
@@ -27470,7 +27470,7 @@
         </is>
       </c>
       <c r="M443" s="2" t="n">
-        <v>7936.21</v>
+        <v>7988.48</v>
       </c>
     </row>
     <row r="444">
@@ -27531,7 +27531,7 @@
         </is>
       </c>
       <c r="M444" s="2" t="n">
-        <v>1189.68</v>
+        <v>1197.51</v>
       </c>
     </row>
     <row r="445">
@@ -27592,7 +27592,7 @@
         </is>
       </c>
       <c r="M445" s="2" t="n">
-        <v>20530.4</v>
+        <v>20665.61</v>
       </c>
     </row>
     <row r="446">
@@ -27653,7 +27653,7 @@
         </is>
       </c>
       <c r="M446" s="2" t="n">
-        <v>2200.48</v>
+        <v>2214.97</v>
       </c>
     </row>
     <row r="447">
@@ -27714,7 +27714,7 @@
         </is>
       </c>
       <c r="M447" s="2" t="n">
-        <v>2453.61</v>
+        <v>2469.77</v>
       </c>
     </row>
     <row r="448">
@@ -27775,7 +27775,7 @@
         </is>
       </c>
       <c r="M448" s="2" t="n">
-        <v>2328.29</v>
+        <v>2343.62</v>
       </c>
     </row>
     <row r="449">
@@ -27836,7 +27836,7 @@
         </is>
       </c>
       <c r="M449" s="2" t="n">
-        <v>2775.55</v>
+        <v>2793.83</v>
       </c>
     </row>
     <row r="450">
@@ -27897,7 +27897,7 @@
         </is>
       </c>
       <c r="M450" s="2" t="n">
-        <v>2422.59</v>
+        <v>2438.55</v>
       </c>
     </row>
     <row r="451">
@@ -27958,7 +27958,7 @@
         </is>
       </c>
       <c r="M451" s="2" t="n">
-        <v>2498.48</v>
+        <v>2514.94</v>
       </c>
     </row>
     <row r="452">
@@ -28019,7 +28019,7 @@
         </is>
       </c>
       <c r="M452" s="2" t="n">
-        <v>1647.21</v>
+        <v>1658.06</v>
       </c>
     </row>
     <row r="453">
@@ -28080,7 +28080,7 @@
         </is>
       </c>
       <c r="M453" s="2" t="n">
-        <v>2345.77</v>
+        <v>2361.22</v>
       </c>
     </row>
     <row r="454">
@@ -28141,7 +28141,7 @@
         </is>
       </c>
       <c r="M454" s="2" t="n">
-        <v>2207.88</v>
+        <v>2222.42</v>
       </c>
     </row>
     <row r="455">
@@ -28202,7 +28202,7 @@
         </is>
       </c>
       <c r="M455" s="2" t="n">
-        <v>2185.54</v>
+        <v>2199.93</v>
       </c>
     </row>
     <row r="456">
@@ -28263,7 +28263,7 @@
         </is>
       </c>
       <c r="M456" s="2" t="n">
-        <v>1077.63</v>
+        <v>1084.72</v>
       </c>
     </row>
     <row r="457">
@@ -28324,7 +28324,7 @@
         </is>
       </c>
       <c r="M457" s="2" t="n">
-        <v>4055.29</v>
+        <v>4082</v>
       </c>
     </row>
     <row r="458">
@@ -28385,7 +28385,7 @@
         </is>
       </c>
       <c r="M458" s="2" t="n">
-        <v>1925.91</v>
+        <v>1938.59</v>
       </c>
     </row>
     <row r="459">
@@ -28446,7 +28446,7 @@
         </is>
       </c>
       <c r="M459" s="2" t="n">
-        <v>3304.04</v>
+        <v>3325.8</v>
       </c>
     </row>
     <row r="460">
@@ -28507,7 +28507,7 @@
         </is>
       </c>
       <c r="M460" s="2" t="n">
-        <v>3480.13</v>
+        <v>3503.05</v>
       </c>
     </row>
     <row r="461">
@@ -28568,7 +28568,7 @@
         </is>
       </c>
       <c r="M461" s="2" t="n">
-        <v>8086.29</v>
+        <v>8139.55</v>
       </c>
     </row>
     <row r="462">
@@ -28629,7 +28629,7 @@
         </is>
       </c>
       <c r="M462" s="2" t="n">
-        <v>2780.41</v>
+        <v>2798.72</v>
       </c>
     </row>
     <row r="463">
@@ -28690,7 +28690,7 @@
         </is>
       </c>
       <c r="M463" s="2" t="n">
-        <v>12086.36</v>
+        <v>12194.01</v>
       </c>
     </row>
     <row r="464">
@@ -28751,7 +28751,7 @@
         </is>
       </c>
       <c r="M464" s="2" t="n">
-        <v>4876.13</v>
+        <v>4919.56</v>
       </c>
     </row>
     <row r="465">
@@ -28812,7 +28812,7 @@
         </is>
       </c>
       <c r="M465" s="2" t="n">
-        <v>904.49</v>
+        <v>912.55</v>
       </c>
     </row>
     <row r="466">
@@ -28873,7 +28873,7 @@
         </is>
       </c>
       <c r="M466" s="2" t="n">
-        <v>5394.91</v>
+        <v>5442.96</v>
       </c>
     </row>
     <row r="467">
@@ -28934,7 +28934,7 @@
         </is>
       </c>
       <c r="M467" s="2" t="n">
-        <v>1325.54</v>
+        <v>1337.34</v>
       </c>
     </row>
     <row r="468">
@@ -28995,7 +28995,7 @@
         </is>
       </c>
       <c r="M468" s="2" t="n">
-        <v>831.4</v>
+        <v>838.8</v>
       </c>
     </row>
     <row r="469">
@@ -29056,7 +29056,7 @@
         </is>
       </c>
       <c r="M469" s="2" t="n">
-        <v>76541.83</v>
+        <v>77223.56</v>
       </c>
     </row>
     <row r="470">
@@ -29117,7 +29117,7 @@
         </is>
       </c>
       <c r="M470" s="2" t="n">
-        <v>1008.67</v>
+        <v>1017.66</v>
       </c>
     </row>
     <row r="471">
@@ -29178,7 +29178,7 @@
         </is>
       </c>
       <c r="M471" s="2" t="n">
-        <v>809.67</v>
+        <v>816.88</v>
       </c>
     </row>
     <row r="472">
@@ -29239,7 +29239,7 @@
         </is>
       </c>
       <c r="M472" s="2" t="n">
-        <v>1762.5</v>
+        <v>1778.2</v>
       </c>
     </row>
     <row r="473">
@@ -29300,7 +29300,7 @@
         </is>
       </c>
       <c r="M473" s="2" t="n">
-        <v>947.4299999999999</v>
+        <v>955.86</v>
       </c>
     </row>
     <row r="474">
@@ -29361,7 +29361,7 @@
         </is>
       </c>
       <c r="M474" s="2" t="n">
-        <v>8340.02</v>
+        <v>8414.299999999999</v>
       </c>
     </row>
     <row r="475">
@@ -29422,7 +29422,7 @@
         </is>
       </c>
       <c r="M475" s="2" t="n">
-        <v>2499.06</v>
+        <v>2521.32</v>
       </c>
     </row>
     <row r="476">
@@ -29483,7 +29483,7 @@
         </is>
       </c>
       <c r="M476" s="2" t="n">
-        <v>2725.15</v>
+        <v>2749.42</v>
       </c>
     </row>
     <row r="477">
@@ -29544,7 +29544,7 @@
         </is>
       </c>
       <c r="M477" s="2" t="n">
-        <v>1719.21</v>
+        <v>1734.53</v>
       </c>
     </row>
     <row r="478">
@@ -29605,7 +29605,7 @@
         </is>
       </c>
       <c r="M478" s="2" t="n">
-        <v>1445.36</v>
+        <v>1458.23</v>
       </c>
     </row>
     <row r="479">
@@ -29666,7 +29666,7 @@
         </is>
       </c>
       <c r="M479" s="2" t="n">
-        <v>4065.61</v>
+        <v>4101.82</v>
       </c>
     </row>
     <row r="480">
@@ -29727,7 +29727,7 @@
         </is>
       </c>
       <c r="M480" s="2" t="n">
-        <v>2113.98</v>
+        <v>2132.81</v>
       </c>
     </row>
     <row r="481">
@@ -29788,7 +29788,7 @@
         </is>
       </c>
       <c r="M481" s="2" t="n">
-        <v>2505.58</v>
+        <v>2527.89</v>
       </c>
     </row>
     <row r="482">
@@ -29849,7 +29849,7 @@
         </is>
       </c>
       <c r="M482" s="2" t="n">
-        <v>9512.66</v>
+        <v>9597.389999999999</v>
       </c>
     </row>
     <row r="483">
@@ -29910,7 +29910,7 @@
         </is>
       </c>
       <c r="M483" s="2" t="n">
-        <v>2843.35</v>
+        <v>2868.68</v>
       </c>
     </row>
     <row r="484">
@@ -29971,7 +29971,7 @@
         </is>
       </c>
       <c r="M484" s="2" t="n">
-        <v>4300.81</v>
+        <v>4339.12</v>
       </c>
     </row>
     <row r="485">
@@ -30032,7 +30032,7 @@
         </is>
       </c>
       <c r="M485" s="2" t="n">
-        <v>7150.33</v>
+        <v>7214.01</v>
       </c>
     </row>
     <row r="486">
@@ -30093,7 +30093,7 @@
         </is>
       </c>
       <c r="M486" s="2" t="n">
-        <v>2566.72</v>
+        <v>2589.58</v>
       </c>
     </row>
     <row r="487">
@@ -30154,7 +30154,7 @@
         </is>
       </c>
       <c r="M487" s="2" t="n">
-        <v>20449.98</v>
+        <v>20632.12</v>
       </c>
     </row>
     <row r="488">
@@ -30215,7 +30215,7 @@
         </is>
       </c>
       <c r="M488" s="2" t="n">
-        <v>1150.25</v>
+        <v>1160.5</v>
       </c>
     </row>
     <row r="489">
@@ -30276,7 +30276,7 @@
         </is>
       </c>
       <c r="M489" s="2" t="n">
-        <v>1839.16</v>
+        <v>1855.54</v>
       </c>
     </row>
     <row r="490">
@@ -30337,7 +30337,7 @@
         </is>
       </c>
       <c r="M490" s="2" t="n">
-        <v>1905.06</v>
+        <v>1922.03</v>
       </c>
     </row>
     <row r="491">
@@ -30398,7 +30398,7 @@
         </is>
       </c>
       <c r="M491" s="2" t="n">
-        <v>2695.15</v>
+        <v>2719.16</v>
       </c>
     </row>
     <row r="492">
@@ -30459,7 +30459,7 @@
         </is>
       </c>
       <c r="M492" s="2" t="n">
-        <v>2036.27</v>
+        <v>2054.41</v>
       </c>
     </row>
     <row r="493">
@@ -30520,7 +30520,7 @@
         </is>
       </c>
       <c r="M493" s="2" t="n">
-        <v>1203.4</v>
+        <v>1214.12</v>
       </c>
     </row>
     <row r="494">
@@ -30581,7 +30581,7 @@
         </is>
       </c>
       <c r="M494" s="2" t="n">
-        <v>1001.94</v>
+        <v>1010.86</v>
       </c>
     </row>
     <row r="495">
@@ -30642,7 +30642,7 @@
         </is>
       </c>
       <c r="M495" s="2" t="n">
-        <v>9776.43</v>
+        <v>9863.5</v>
       </c>
     </row>
     <row r="496">
@@ -30703,7 +30703,7 @@
         </is>
       </c>
       <c r="M496" s="2" t="n">
-        <v>2911.51</v>
+        <v>2937.44</v>
       </c>
     </row>
     <row r="497">
@@ -30764,7 +30764,7 @@
         </is>
       </c>
       <c r="M497" s="2" t="n">
-        <v>2434.12</v>
+        <v>2455.8</v>
       </c>
     </row>
     <row r="498">
@@ -30825,7 +30825,7 @@
         </is>
       </c>
       <c r="M498" s="2" t="n">
-        <v>6164.25</v>
+        <v>6219.15</v>
       </c>
     </row>
     <row r="499">
@@ -30886,7 +30886,7 @@
         </is>
       </c>
       <c r="M499" s="2" t="n">
-        <v>6421.16</v>
+        <v>6478.36</v>
       </c>
     </row>
     <row r="500">
@@ -30947,7 +30947,7 @@
         </is>
       </c>
       <c r="M500" s="2" t="n">
-        <v>3665.87</v>
+        <v>3698.53</v>
       </c>
     </row>
     <row r="501">
@@ -31008,7 +31008,7 @@
         </is>
       </c>
       <c r="M501" s="2" t="n">
-        <v>4886.24</v>
+        <v>4929.77</v>
       </c>
     </row>
     <row r="502">
@@ -31069,7 +31069,7 @@
         </is>
       </c>
       <c r="M502" s="2" t="n">
-        <v>2064.05</v>
+        <v>2082.43</v>
       </c>
     </row>
     <row r="503">
@@ -31130,7 +31130,7 @@
         </is>
       </c>
       <c r="M503" s="2" t="n">
-        <v>5218.32</v>
+        <v>5264.8</v>
       </c>
     </row>
     <row r="504">
@@ -31191,7 +31191,7 @@
         </is>
       </c>
       <c r="M504" s="2" t="n">
-        <v>6929.61</v>
+        <v>6991.33</v>
       </c>
     </row>
     <row r="505">
@@ -31252,7 +31252,7 @@
         </is>
       </c>
       <c r="M505" s="2" t="n">
-        <v>6518.62</v>
+        <v>6576.68</v>
       </c>
     </row>
     <row r="506">
@@ -31313,7 +31313,7 @@
         </is>
       </c>
       <c r="M506" s="2" t="n">
-        <v>10279.04</v>
+        <v>10370.59</v>
       </c>
     </row>
     <row r="507">
@@ -31374,7 +31374,7 @@
         </is>
       </c>
       <c r="M507" s="2" t="n">
-        <v>14310.66</v>
+        <v>14438.12</v>
       </c>
     </row>
     <row r="508">
@@ -31435,7 +31435,7 @@
         </is>
       </c>
       <c r="M508" s="2" t="n">
-        <v>4492.97</v>
+        <v>4532.99</v>
       </c>
     </row>
     <row r="509">
@@ -31496,7 +31496,7 @@
         </is>
       </c>
       <c r="M509" s="2" t="n">
-        <v>3826.13</v>
+        <v>3860.21</v>
       </c>
     </row>
     <row r="510">
@@ -31557,7 +31557,7 @@
         </is>
       </c>
       <c r="M510" s="2" t="n">
-        <v>6958.11</v>
+        <v>7020.08</v>
       </c>
     </row>
     <row r="511">
@@ -31618,7 +31618,7 @@
         </is>
       </c>
       <c r="M511" s="2" t="n">
-        <v>19509.34</v>
+        <v>19683.1</v>
       </c>
     </row>
     <row r="512">
@@ -31679,7 +31679,7 @@
         </is>
       </c>
       <c r="M512" s="2" t="n">
-        <v>4268.09</v>
+        <v>4306.11</v>
       </c>
     </row>
     <row r="513">
@@ -31740,7 +31740,7 @@
         </is>
       </c>
       <c r="M513" s="2" t="n">
-        <v>1308.69</v>
+        <v>1320.35</v>
       </c>
     </row>
     <row r="514">
@@ -31801,7 +31801,7 @@
         </is>
       </c>
       <c r="M514" s="2" t="n">
-        <v>4345.62</v>
+        <v>4384.32</v>
       </c>
     </row>
     <row r="515">
@@ -31862,7 +31862,7 @@
         </is>
       </c>
       <c r="M515" s="2" t="n">
-        <v>2205.32</v>
+        <v>2224.96</v>
       </c>
     </row>
     <row r="516">
@@ -31923,7 +31923,7 @@
         </is>
       </c>
       <c r="M516" s="2" t="n">
-        <v>1011.34</v>
+        <v>1020.35</v>
       </c>
     </row>
     <row r="517">
@@ -31984,7 +31984,7 @@
         </is>
       </c>
       <c r="M517" s="2" t="n">
-        <v>49864.44</v>
+        <v>50308.57</v>
       </c>
     </row>
     <row r="518">
@@ -32045,7 +32045,7 @@
         </is>
       </c>
       <c r="M518" s="2" t="n">
-        <v>2347.47</v>
+        <v>2368.38</v>
       </c>
     </row>
     <row r="519">
@@ -32106,7 +32106,7 @@
         </is>
       </c>
       <c r="M519" s="2" t="n">
-        <v>19873.87</v>
+        <v>20050.88</v>
       </c>
     </row>
     <row r="520">
@@ -32167,7 +32167,7 @@
         </is>
       </c>
       <c r="M520" s="2" t="n">
-        <v>7653.37</v>
+        <v>7721.54</v>
       </c>
     </row>
     <row r="521">
@@ -32228,7 +32228,7 @@
         </is>
       </c>
       <c r="M521" s="2" t="n">
-        <v>2883.69</v>
+        <v>2909.38</v>
       </c>
     </row>
     <row r="522">
@@ -32289,7 +32289,7 @@
         </is>
       </c>
       <c r="M522" s="2" t="n">
-        <v>2654.05</v>
+        <v>2677.69</v>
       </c>
     </row>
     <row r="523">
@@ -32350,7 +32350,7 @@
         </is>
       </c>
       <c r="M523" s="2" t="n">
-        <v>48396.72</v>
+        <v>48827.78</v>
       </c>
     </row>
     <row r="524">
@@ -32411,7 +32411,7 @@
         </is>
       </c>
       <c r="M524" s="2" t="n">
-        <v>7880.83</v>
+        <v>7951.03</v>
       </c>
     </row>
     <row r="525">
@@ -32472,7 +32472,7 @@
         </is>
       </c>
       <c r="M525" s="2" t="n">
-        <v>1778.75</v>
+        <v>1794.59</v>
       </c>
     </row>
     <row r="526">
@@ -32533,7 +32533,7 @@
         </is>
       </c>
       <c r="M526" s="2" t="n">
-        <v>3307.05</v>
+        <v>3336.51</v>
       </c>
     </row>
     <row r="527">
@@ -32594,7 +32594,7 @@
         </is>
       </c>
       <c r="M527" s="2" t="n">
-        <v>3950.09</v>
+        <v>3943.32</v>
       </c>
     </row>
     <row r="528">
@@ -32655,7 +32655,7 @@
         </is>
       </c>
       <c r="M528" s="2" t="n">
-        <v>1747.69</v>
+        <v>1744.69</v>
       </c>
     </row>
     <row r="529">
@@ -32716,7 +32716,7 @@
         </is>
       </c>
       <c r="M529" s="2" t="n">
-        <v>5802.95</v>
+        <v>5793.01</v>
       </c>
     </row>
     <row r="530">
@@ -32777,7 +32777,7 @@
         </is>
       </c>
       <c r="M530" s="2" t="n">
-        <v>2244.89</v>
+        <v>2241.04</v>
       </c>
     </row>
     <row r="531">
@@ -32838,7 +32838,7 @@
         </is>
       </c>
       <c r="M531" s="2" t="n">
-        <v>14405.29</v>
+        <v>14380.6</v>
       </c>
     </row>
     <row r="532">
@@ -32899,7 +32899,7 @@
         </is>
       </c>
       <c r="M532" s="2" t="n">
-        <v>19223.97</v>
+        <v>19191.02</v>
       </c>
     </row>
     <row r="533">
@@ -32960,7 +32960,7 @@
         </is>
       </c>
       <c r="M533" s="2" t="n">
-        <v>1107.6</v>
+        <v>1105.7</v>
       </c>
     </row>
     <row r="534">
@@ -33021,7 +33021,7 @@
         </is>
       </c>
       <c r="M534" s="2" t="n">
-        <v>10116.56</v>
+        <v>10099.22</v>
       </c>
     </row>
     <row r="535">
@@ -33082,7 +33082,7 @@
         </is>
       </c>
       <c r="M535" s="2" t="n">
-        <v>1670.4</v>
+        <v>1667.53</v>
       </c>
     </row>
     <row r="536">
@@ -33143,7 +33143,7 @@
         </is>
       </c>
       <c r="M536" s="2" t="n">
-        <v>1832.75</v>
+        <v>1829.61</v>
       </c>
     </row>
     <row r="537">
@@ -33204,7 +33204,7 @@
         </is>
       </c>
       <c r="M537" s="2" t="n">
-        <v>35399.26</v>
+        <v>35338.59</v>
       </c>
     </row>
     <row r="538">
@@ -33265,7 +33265,7 @@
         </is>
       </c>
       <c r="M538" s="2" t="n">
-        <v>8144.67</v>
+        <v>8130.71</v>
       </c>
     </row>
     <row r="539">
@@ -33326,7 +33326,7 @@
         </is>
       </c>
       <c r="M539" s="2" t="n">
-        <v>7567.54</v>
+        <v>7554.57</v>
       </c>
     </row>
     <row r="540">
@@ -33387,7 +33387,7 @@
         </is>
       </c>
       <c r="M540" s="2" t="n">
-        <v>4593.59</v>
+        <v>4585.72</v>
       </c>
     </row>
     <row r="541">
@@ -33448,7 +33448,7 @@
         </is>
       </c>
       <c r="M541" s="2" t="n">
-        <v>6576.34</v>
+        <v>6565.07</v>
       </c>
     </row>
     <row r="542">
@@ -33509,7 +33509,7 @@
         </is>
       </c>
       <c r="M542" s="2" t="n">
-        <v>2490.13</v>
+        <v>2485.86</v>
       </c>
     </row>
     <row r="543">
@@ -33570,7 +33570,7 @@
         </is>
       </c>
       <c r="M543" s="2" t="n">
-        <v>812.59</v>
+        <v>811.2</v>
       </c>
     </row>
     <row r="544">
@@ -33631,7 +33631,7 @@
         </is>
       </c>
       <c r="M544" s="2" t="n">
-        <v>6145.89</v>
+        <v>6135.36</v>
       </c>
     </row>
     <row r="545">
@@ -33692,7 +33692,7 @@
         </is>
       </c>
       <c r="M545" s="2" t="n">
-        <v>39018.12</v>
+        <v>38951.24</v>
       </c>
     </row>
     <row r="546">
@@ -33753,7 +33753,7 @@
         </is>
       </c>
       <c r="M546" s="2" t="n">
-        <v>30774.59</v>
+        <v>30721.84</v>
       </c>
     </row>
     <row r="547">
@@ -33814,7 +33814,7 @@
         </is>
       </c>
       <c r="M547" s="2" t="n">
-        <v>1736.94</v>
+        <v>1733.96</v>
       </c>
     </row>
     <row r="548">
@@ -33875,7 +33875,7 @@
         </is>
       </c>
       <c r="M548" s="2" t="n">
-        <v>1533.71</v>
+        <v>1531.08</v>
       </c>
     </row>
     <row r="549">
@@ -33936,7 +33936,7 @@
         </is>
       </c>
       <c r="M549" s="2" t="n">
-        <v>3554.18</v>
+        <v>3548.09</v>
       </c>
     </row>
     <row r="550">
@@ -33997,7 +33997,7 @@
         </is>
       </c>
       <c r="M550" s="2" t="n">
-        <v>3783.92</v>
+        <v>3777.43</v>
       </c>
     </row>
     <row r="551">
@@ -34058,7 +34058,7 @@
         </is>
       </c>
       <c r="M551" s="2" t="n">
-        <v>3187.39</v>
+        <v>3181.92</v>
       </c>
     </row>
     <row r="552">
@@ -34119,7 +34119,7 @@
         </is>
       </c>
       <c r="M552" s="2" t="n">
-        <v>9723.52</v>
+        <v>9706.860000000001</v>
       </c>
     </row>
     <row r="553">
@@ -34180,7 +34180,7 @@
         </is>
       </c>
       <c r="M553" s="2" t="n">
-        <v>47725.64</v>
+        <v>47643.84</v>
       </c>
     </row>
     <row r="554">
@@ -34241,7 +34241,7 @@
         </is>
       </c>
       <c r="M554" s="2" t="n">
-        <v>3382.25</v>
+        <v>3376.45</v>
       </c>
     </row>
     <row r="555">
@@ -34302,7 +34302,7 @@
         </is>
       </c>
       <c r="M555" s="2" t="n">
-        <v>834.98</v>
+        <v>833.55</v>
       </c>
     </row>
     <row r="556">
@@ -34363,7 +34363,7 @@
         </is>
       </c>
       <c r="M556" s="2" t="n">
-        <v>3871.87</v>
+        <v>3865.23</v>
       </c>
     </row>
     <row r="557">
@@ -34424,7 +34424,7 @@
         </is>
       </c>
       <c r="M557" s="2" t="n">
-        <v>4110.46</v>
+        <v>4103.41</v>
       </c>
     </row>
     <row r="558">
@@ -34485,7 +34485,7 @@
         </is>
       </c>
       <c r="M558" s="2" t="n">
-        <v>2434.26</v>
+        <v>2430.09</v>
       </c>
     </row>
     <row r="559">
@@ -34546,7 +34546,7 @@
         </is>
       </c>
       <c r="M559" s="2" t="n">
-        <v>2617.85</v>
+        <v>2613.37</v>
       </c>
     </row>
     <row r="560">
@@ -34607,7 +34607,7 @@
         </is>
       </c>
       <c r="M560" s="2" t="n">
-        <v>3497.54</v>
+        <v>3491.54</v>
       </c>
     </row>
     <row r="561">
@@ -34668,7 +34668,7 @@
         </is>
       </c>
       <c r="M561" s="2" t="n">
-        <v>5257.55</v>
+        <v>5248.54</v>
       </c>
     </row>
     <row r="562">
@@ -34729,7 +34729,7 @@
         </is>
       </c>
       <c r="M562" s="2" t="n">
-        <v>1652.23</v>
+        <v>1649.39</v>
       </c>
     </row>
     <row r="563">
@@ -34790,7 +34790,7 @@
         </is>
       </c>
       <c r="M563" s="2" t="n">
-        <v>905.0700000000001</v>
+        <v>903.52</v>
       </c>
     </row>
     <row r="564">
@@ -34851,7 +34851,7 @@
         </is>
       </c>
       <c r="M564" s="2" t="n">
-        <v>34041.21</v>
+        <v>33982.87</v>
       </c>
     </row>
     <row r="565">
@@ -34912,7 +34912,7 @@
         </is>
       </c>
       <c r="M565" s="2" t="n">
-        <v>812.97</v>
+        <v>811.5700000000001</v>
       </c>
     </row>
     <row r="566">
@@ -34973,7 +34973,7 @@
         </is>
       </c>
       <c r="M566" s="2" t="n">
-        <v>1366.26</v>
+        <v>1363.92</v>
       </c>
     </row>
     <row r="567">
@@ -35034,7 +35034,7 @@
         </is>
       </c>
       <c r="M567" s="2" t="n">
-        <v>5136.9</v>
+        <v>5128.09</v>
       </c>
     </row>
     <row r="568">
@@ -35095,7 +35095,7 @@
         </is>
       </c>
       <c r="M568" s="2" t="n">
-        <v>3597.11</v>
+        <v>3590.95</v>
       </c>
     </row>
     <row r="569">
@@ -35156,7 +35156,7 @@
         </is>
       </c>
       <c r="M569" s="2" t="n">
-        <v>3111</v>
+        <v>3105.67</v>
       </c>
     </row>
     <row r="570">
@@ -35217,7 +35217,7 @@
         </is>
       </c>
       <c r="M570" s="2" t="n">
-        <v>2015.42</v>
+        <v>2011.96</v>
       </c>
     </row>
     <row r="571">
@@ -35278,7 +35278,7 @@
         </is>
       </c>
       <c r="M571" s="2" t="n">
-        <v>1463.5</v>
+        <v>1460.99</v>
       </c>
     </row>
     <row r="572">
@@ -35339,7 +35339,7 @@
         </is>
       </c>
       <c r="M572" s="2" t="n">
-        <v>4471.37</v>
+        <v>4463.71</v>
       </c>
     </row>
     <row r="573">
@@ -35400,7 +35400,7 @@
         </is>
       </c>
       <c r="M573" s="2" t="n">
-        <v>10413.67</v>
+        <v>10395.82</v>
       </c>
     </row>
     <row r="574">
@@ -35461,7 +35461,7 @@
         </is>
       </c>
       <c r="M574" s="2" t="n">
-        <v>2433.93</v>
+        <v>2431.42</v>
       </c>
     </row>
     <row r="575">
@@ -35522,7 +35522,7 @@
         </is>
       </c>
       <c r="M575" s="2" t="n">
-        <v>1417.72</v>
+        <v>1416.26</v>
       </c>
     </row>
     <row r="576">
@@ -35583,7 +35583,7 @@
         </is>
       </c>
       <c r="M576" s="2" t="n">
-        <v>4016.2</v>
+        <v>4012.06</v>
       </c>
     </row>
     <row r="577">
@@ -35644,7 +35644,7 @@
         </is>
       </c>
       <c r="M577" s="2" t="n">
-        <v>4202.36</v>
+        <v>4198.03</v>
       </c>
     </row>
     <row r="578">
@@ -35705,7 +35705,7 @@
         </is>
       </c>
       <c r="M578" s="2" t="n">
-        <v>6032.69</v>
+        <v>6026.47</v>
       </c>
     </row>
     <row r="579">
@@ -35766,7 +35766,7 @@
         </is>
       </c>
       <c r="M579" s="2" t="n">
-        <v>808.78</v>
+        <v>807.9400000000001</v>
       </c>
     </row>
     <row r="580">
@@ -35827,7 +35827,7 @@
         </is>
       </c>
       <c r="M580" s="2" t="n">
-        <v>8120.3</v>
+        <v>8111.92</v>
       </c>
     </row>
     <row r="581">
@@ -35888,7 +35888,7 @@
         </is>
       </c>
       <c r="M581" s="2" t="n">
-        <v>8498.51</v>
+        <v>8489.74</v>
       </c>
     </row>
     <row r="582">
@@ -35949,7 +35949,7 @@
         </is>
       </c>
       <c r="M582" s="2" t="n">
-        <v>4347.68</v>
+        <v>4343.19</v>
       </c>
     </row>
     <row r="583">
@@ -36010,7 +36010,7 @@
         </is>
       </c>
       <c r="M583" s="2" t="n">
-        <v>2957.85</v>
+        <v>2954.8</v>
       </c>
     </row>
     <row r="584">
@@ -36071,7 +36071,7 @@
         </is>
       </c>
       <c r="M584" s="2" t="n">
-        <v>10265.24</v>
+        <v>10254.65</v>
       </c>
     </row>
     <row r="585">
@@ -36132,7 +36132,7 @@
         </is>
       </c>
       <c r="M585" s="2" t="n">
-        <v>11482.54</v>
+        <v>11470.7</v>
       </c>
     </row>
     <row r="586">
@@ -36193,7 +36193,7 @@
         </is>
       </c>
       <c r="M586" s="2" t="n">
-        <v>8984.139999999999</v>
+        <v>8974.870000000001</v>
       </c>
     </row>
     <row r="587">
@@ -36254,7 +36254,7 @@
         </is>
       </c>
       <c r="M587" s="2" t="n">
-        <v>1160.01</v>
+        <v>1158.82</v>
       </c>
     </row>
     <row r="588">
@@ -36315,7 +36315,7 @@
         </is>
       </c>
       <c r="M588" s="2" t="n">
-        <v>10713.48</v>
+        <v>10702.43</v>
       </c>
     </row>
     <row r="589">
@@ -36376,7 +36376,7 @@
         </is>
       </c>
       <c r="M589" s="2" t="n">
-        <v>71407.2</v>
+        <v>71333.55</v>
       </c>
     </row>
     <row r="590">
@@ -36437,7 +36437,7 @@
         </is>
       </c>
       <c r="M590" s="2" t="n">
-        <v>6930.79</v>
+        <v>6923.64</v>
       </c>
     </row>
     <row r="591">
@@ -36498,7 +36498,7 @@
         </is>
       </c>
       <c r="M591" s="2" t="n">
-        <v>1288.66</v>
+        <v>1287.33</v>
       </c>
     </row>
     <row r="592">
@@ -36559,7 +36559,7 @@
         </is>
       </c>
       <c r="M592" s="2" t="n">
-        <v>12369.44</v>
+        <v>12356.68</v>
       </c>
     </row>
     <row r="593">
@@ -36620,7 +36620,7 @@
         </is>
       </c>
       <c r="M593" s="2" t="n">
-        <v>8226.790000000001</v>
+        <v>8218.309999999999</v>
       </c>
     </row>
     <row r="594">
@@ -36681,7 +36681,7 @@
         </is>
       </c>
       <c r="M594" s="2" t="n">
-        <v>4672.2</v>
+        <v>4667.38</v>
       </c>
     </row>
     <row r="595">
@@ -36742,7 +36742,7 @@
         </is>
       </c>
       <c r="M595" s="2" t="n">
-        <v>5544.9</v>
+        <v>5539.18</v>
       </c>
     </row>
     <row r="596">
@@ -36803,7 +36803,7 @@
         </is>
       </c>
       <c r="M596" s="2" t="n">
-        <v>2475.58</v>
+        <v>2473.03</v>
       </c>
     </row>
     <row r="597">
@@ -36864,7 +36864,7 @@
         </is>
       </c>
       <c r="M597" s="2" t="n">
-        <v>5185.12</v>
+        <v>5179.77</v>
       </c>
     </row>
     <row r="598">
@@ -36925,7 +36925,7 @@
         </is>
       </c>
       <c r="M598" s="2" t="n">
-        <v>3089.29</v>
+        <v>3086.1</v>
       </c>
     </row>
     <row r="599">
@@ -36986,7 +36986,7 @@
         </is>
       </c>
       <c r="M599" s="2" t="n">
-        <v>1303.33</v>
+        <v>1301.98</v>
       </c>
     </row>
     <row r="600">
@@ -37047,7 +37047,7 @@
         </is>
       </c>
       <c r="M600" s="2" t="n">
-        <v>21775.34</v>
+        <v>21752.88</v>
       </c>
     </row>
     <row r="601">
@@ -37108,7 +37108,7 @@
         </is>
       </c>
       <c r="M601" s="2" t="n">
-        <v>7166.75</v>
+        <v>7159.36</v>
       </c>
     </row>
     <row r="602">
@@ -37169,7 +37169,7 @@
         </is>
       </c>
       <c r="M602" s="2" t="n">
-        <v>16658.51</v>
+        <v>16641.33</v>
       </c>
     </row>
     <row r="603">
@@ -37230,7 +37230,7 @@
         </is>
       </c>
       <c r="M603" s="2" t="n">
-        <v>1698.59</v>
+        <v>1696.84</v>
       </c>
     </row>
     <row r="604">
@@ -37291,7 +37291,7 @@
         </is>
       </c>
       <c r="M604" s="2" t="n">
-        <v>13623.13</v>
+        <v>13609.08</v>
       </c>
     </row>
     <row r="605">
@@ -37352,7 +37352,7 @@
         </is>
       </c>
       <c r="M605" s="2" t="n">
-        <v>1253.71</v>
+        <v>1252.42</v>
       </c>
     </row>
     <row r="606">
@@ -37413,7 +37413,7 @@
         </is>
       </c>
       <c r="M606" s="2" t="n">
-        <v>9318.139999999999</v>
+        <v>9308.530000000001</v>
       </c>
     </row>
     <row r="607">
@@ -37474,7 +37474,7 @@
         </is>
       </c>
       <c r="M607" s="2" t="n">
-        <v>76382.7</v>
+        <v>76303.92</v>
       </c>
     </row>
     <row r="608">
@@ -37535,7 +37535,7 @@
         </is>
       </c>
       <c r="M608" s="2" t="n">
-        <v>20632.57</v>
+        <v>20611.29</v>
       </c>
     </row>
     <row r="609">
@@ -37596,7 +37596,7 @@
         </is>
       </c>
       <c r="M609" s="2" t="n">
-        <v>9314.15</v>
+        <v>9304.540000000001</v>
       </c>
     </row>
     <row r="610">
@@ -37657,7 +37657,7 @@
         </is>
       </c>
       <c r="M610" s="2" t="n">
-        <v>2783.1</v>
+        <v>2780.23</v>
       </c>
     </row>
     <row r="611">
@@ -37718,7 +37718,7 @@
         </is>
       </c>
       <c r="M611" s="2" t="n">
-        <v>811.45</v>
+        <v>810.62</v>
       </c>
     </row>
     <row r="612">
@@ -37779,7 +37779,7 @@
         </is>
       </c>
       <c r="M612" s="2" t="n">
-        <v>13908.49</v>
+        <v>13894.14</v>
       </c>
     </row>
     <row r="613">
@@ -37840,7 +37840,7 @@
         </is>
       </c>
       <c r="M613" s="2" t="n">
-        <v>1472.44</v>
+        <v>1470.92</v>
       </c>
     </row>
     <row r="614">
@@ -37901,7 +37901,7 @@
         </is>
       </c>
       <c r="M614" s="2" t="n">
-        <v>3002.27</v>
+        <v>2999.18</v>
       </c>
     </row>
     <row r="615">
@@ -37962,7 +37962,7 @@
         </is>
       </c>
       <c r="M615" s="2" t="n">
-        <v>2585.95</v>
+        <v>2583.28</v>
       </c>
     </row>
     <row r="616">
@@ -38023,7 +38023,7 @@
         </is>
       </c>
       <c r="M616" s="2" t="n">
-        <v>3226.35</v>
+        <v>3223.02</v>
       </c>
     </row>
     <row r="617">
@@ -38084,7 +38084,7 @@
         </is>
       </c>
       <c r="M617" s="2" t="n">
-        <v>815.03</v>
+        <v>814.1900000000001</v>
       </c>
     </row>
     <row r="618">
@@ -38145,7 +38145,7 @@
         </is>
       </c>
       <c r="M618" s="2" t="n">
-        <v>1159.38</v>
+        <v>1158.18</v>
       </c>
     </row>
     <row r="619">
@@ -38206,7 +38206,7 @@
         </is>
       </c>
       <c r="M619" s="2" t="n">
-        <v>15311.12</v>
+        <v>15295.33</v>
       </c>
     </row>
     <row r="620">
@@ -38267,7 +38267,7 @@
         </is>
       </c>
       <c r="M620" s="2" t="n">
-        <v>896.23</v>
+        <v>895.3</v>
       </c>
     </row>
     <row r="621">
@@ -38328,7 +38328,7 @@
         </is>
       </c>
       <c r="M621" s="2" t="n">
-        <v>1935.15</v>
+        <v>1933.16</v>
       </c>
     </row>
     <row r="622">
@@ -38389,7 +38389,7 @@
         </is>
       </c>
       <c r="M622" s="2" t="n">
-        <v>1557.49</v>
+        <v>1555.88</v>
       </c>
     </row>
     <row r="623">
@@ -38450,7 +38450,7 @@
         </is>
       </c>
       <c r="M623" s="2" t="n">
-        <v>4505.88</v>
+        <v>4473.6</v>
       </c>
     </row>
     <row r="624">
@@ -38511,7 +38511,7 @@
         </is>
       </c>
       <c r="M624" s="2" t="n">
-        <v>3352.44</v>
+        <v>3328.43</v>
       </c>
     </row>
     <row r="625">
@@ -38572,7 +38572,7 @@
         </is>
       </c>
       <c r="M625" s="2" t="n">
-        <v>2550.99</v>
+        <v>2532.71</v>
       </c>
     </row>
     <row r="626">
@@ -38633,7 +38633,7 @@
         </is>
       </c>
       <c r="M626" s="2" t="n">
-        <v>16507.24</v>
+        <v>16388.98</v>
       </c>
     </row>
     <row r="627">
@@ -38694,7 +38694,7 @@
         </is>
       </c>
       <c r="M627" s="2" t="n">
-        <v>2772.35</v>
+        <v>2752.48</v>
       </c>
     </row>
     <row r="628">
@@ -38755,7 +38755,7 @@
         </is>
       </c>
       <c r="M628" s="2" t="n">
-        <v>2385.08</v>
+        <v>2367.99</v>
       </c>
     </row>
     <row r="629">
@@ -38816,7 +38816,7 @@
         </is>
       </c>
       <c r="M629" s="2" t="n">
-        <v>1013.96</v>
+        <v>1006.7</v>
       </c>
     </row>
     <row r="630">
@@ -38877,7 +38877,7 @@
         </is>
       </c>
       <c r="M630" s="2" t="n">
-        <v>2292.97</v>
+        <v>2276.55</v>
       </c>
     </row>
     <row r="631">
@@ -38938,7 +38938,7 @@
         </is>
       </c>
       <c r="M631" s="2" t="n">
-        <v>2088.06</v>
+        <v>2073.11</v>
       </c>
     </row>
     <row r="632">
@@ -38999,7 +38999,7 @@
         </is>
       </c>
       <c r="M632" s="2" t="n">
-        <v>2739.85</v>
+        <v>2720.22</v>
       </c>
     </row>
     <row r="633">
@@ -39060,7 +39060,7 @@
         </is>
       </c>
       <c r="M633" s="2" t="n">
-        <v>4831.34</v>
+        <v>4796.73</v>
       </c>
     </row>
     <row r="634">
@@ -39121,7 +39121,7 @@
         </is>
       </c>
       <c r="M634" s="2" t="n">
-        <v>1029.15</v>
+        <v>1021.77</v>
       </c>
     </row>
     <row r="635">
@@ -39182,7 +39182,7 @@
         </is>
       </c>
       <c r="M635" s="2" t="n">
-        <v>12220.42</v>
+        <v>12132.87</v>
       </c>
     </row>
     <row r="636">
@@ -39243,7 +39243,7 @@
         </is>
       </c>
       <c r="M636" s="2" t="n">
-        <v>3248.96</v>
+        <v>3225.68</v>
       </c>
     </row>
     <row r="637">
@@ -39304,7 +39304,7 @@
         </is>
       </c>
       <c r="M637" s="2" t="n">
-        <v>2502.81</v>
+        <v>2484.88</v>
       </c>
     </row>
     <row r="638">
@@ -39365,7 +39365,7 @@
         </is>
       </c>
       <c r="M638" s="2" t="n">
-        <v>3691.32</v>
+        <v>3664.88</v>
       </c>
     </row>
     <row r="639">
@@ -39426,7 +39426,7 @@
         </is>
       </c>
       <c r="M639" s="2" t="n">
-        <v>1657.75</v>
+        <v>1645.87</v>
       </c>
     </row>
     <row r="640">
@@ -39487,7 +39487,7 @@
         </is>
       </c>
       <c r="M640" s="2" t="n">
-        <v>8598.75</v>
+        <v>8537.15</v>
       </c>
     </row>
     <row r="641">
@@ -39548,7 +39548,7 @@
         </is>
       </c>
       <c r="M641" s="2" t="n">
-        <v>1663.37</v>
+        <v>1651.45</v>
       </c>
     </row>
     <row r="642">
@@ -39609,7 +39609,7 @@
         </is>
       </c>
       <c r="M642" s="2" t="n">
-        <v>1676.44</v>
+        <v>1664.43</v>
       </c>
     </row>
     <row r="643">
@@ -39670,7 +39670,7 @@
         </is>
       </c>
       <c r="M643" s="2" t="n">
-        <v>930.03</v>
+        <v>923.37</v>
       </c>
     </row>
     <row r="644">
@@ -39731,7 +39731,7 @@
         </is>
       </c>
       <c r="M644" s="2" t="n">
-        <v>3389.43</v>
+        <v>3365.14</v>
       </c>
     </row>
     <row r="645">
@@ -39792,7 +39792,7 @@
         </is>
       </c>
       <c r="M645" s="2" t="n">
-        <v>4391.08</v>
+        <v>4359.63</v>
       </c>
     </row>
     <row r="646">
@@ -39853,7 +39853,7 @@
         </is>
       </c>
       <c r="M646" s="2" t="n">
-        <v>11062.6</v>
+        <v>10983.35</v>
       </c>
     </row>
     <row r="647">
@@ -39914,7 +39914,7 @@
         </is>
       </c>
       <c r="M647" s="2" t="n">
-        <v>1838.34</v>
+        <v>1825.17</v>
       </c>
     </row>
     <row r="648">
@@ -39975,7 +39975,7 @@
         </is>
       </c>
       <c r="M648" s="2" t="n">
-        <v>5718.96</v>
+        <v>5677.99</v>
       </c>
     </row>
     <row r="649">
@@ -40036,7 +40036,7 @@
         </is>
       </c>
       <c r="M649" s="2" t="n">
-        <v>63618.46</v>
+        <v>63162.7</v>
       </c>
     </row>
     <row r="650">
@@ -40097,7 +40097,7 @@
         </is>
       </c>
       <c r="M650" s="2" t="n">
-        <v>17237.59</v>
+        <v>17114.1</v>
       </c>
     </row>
     <row r="651">
@@ -40158,7 +40158,7 @@
         </is>
       </c>
       <c r="M651" s="2" t="n">
-        <v>857.28</v>
+        <v>851.14</v>
       </c>
     </row>
     <row r="652">
@@ -40219,7 +40219,7 @@
         </is>
       </c>
       <c r="M652" s="2" t="n">
-        <v>2281.71</v>
+        <v>2265.37</v>
       </c>
     </row>
     <row r="653">
@@ -40280,7 +40280,7 @@
         </is>
       </c>
       <c r="M653" s="2" t="n">
-        <v>1982.63</v>
+        <v>1968.43</v>
       </c>
     </row>
     <row r="654">
@@ -40341,7 +40341,7 @@
         </is>
       </c>
       <c r="M654" s="2" t="n">
-        <v>1436.44</v>
+        <v>1426.15</v>
       </c>
     </row>
     <row r="655">
@@ -40402,7 +40402,7 @@
         </is>
       </c>
       <c r="M655" s="2" t="n">
-        <v>2668.6</v>
+        <v>2649.49</v>
       </c>
     </row>
     <row r="656">
@@ -40463,7 +40463,7 @@
         </is>
       </c>
       <c r="M656" s="2" t="n">
-        <v>3803.49</v>
+        <v>3776.25</v>
       </c>
     </row>
     <row r="657">
@@ -40524,7 +40524,7 @@
         </is>
       </c>
       <c r="M657" s="2" t="n">
-        <v>32538.26</v>
+        <v>32305.16</v>
       </c>
     </row>
     <row r="658">
@@ -40585,7 +40585,7 @@
         </is>
       </c>
       <c r="M658" s="2" t="n">
-        <v>7752.77</v>
+        <v>7697.23</v>
       </c>
     </row>
     <row r="659">
@@ -40646,7 +40646,7 @@
         </is>
       </c>
       <c r="M659" s="2" t="n">
-        <v>817.46</v>
+        <v>811.61</v>
       </c>
     </row>
     <row r="660">
@@ -40707,7 +40707,7 @@
         </is>
       </c>
       <c r="M660" s="2" t="n">
-        <v>973.4</v>
+        <v>966.4299999999999</v>
       </c>
     </row>
     <row r="661">
@@ -40768,7 +40768,7 @@
         </is>
       </c>
       <c r="M661" s="2" t="n">
-        <v>11678.85</v>
+        <v>11595.18</v>
       </c>
     </row>
     <row r="662">
@@ -40829,7 +40829,7 @@
         </is>
       </c>
       <c r="M662" s="2" t="n">
-        <v>1782.89</v>
+        <v>1770.12</v>
       </c>
     </row>
     <row r="663">
@@ -40890,7 +40890,7 @@
         </is>
       </c>
       <c r="M663" s="2" t="n">
-        <v>814.95</v>
+        <v>809.11</v>
       </c>
     </row>
     <row r="664">
@@ -40951,7 +40951,7 @@
         </is>
       </c>
       <c r="M664" s="2" t="n">
-        <v>16227.49</v>
+        <v>16111.23</v>
       </c>
     </row>
     <row r="665">
@@ -41012,7 +41012,7 @@
         </is>
       </c>
       <c r="M665" s="2" t="n">
-        <v>14782.85</v>
+        <v>14676.94</v>
       </c>
     </row>
     <row r="666">
@@ -41073,7 +41073,7 @@
         </is>
       </c>
       <c r="M666" s="2" t="n">
-        <v>77778.91</v>
+        <v>77221.71000000001</v>
       </c>
     </row>
     <row r="667">
@@ -41134,7 +41134,7 @@
         </is>
       </c>
       <c r="M667" s="2" t="n">
-        <v>77348.21000000001</v>
+        <v>76794.09</v>
       </c>
     </row>
     <row r="668">
@@ -41195,7 +41195,7 @@
         </is>
       </c>
       <c r="M668" s="2" t="n">
-        <v>33360.62</v>
+        <v>33121.63</v>
       </c>
     </row>
     <row r="669">
@@ -41256,7 +41256,7 @@
         </is>
       </c>
       <c r="M669" s="2" t="n">
-        <v>81061.44</v>
+        <v>80480.72</v>
       </c>
     </row>
     <row r="670">
@@ -41317,7 +41317,7 @@
         </is>
       </c>
       <c r="M670" s="2" t="n">
-        <v>1516.74</v>
+        <v>1505.87</v>
       </c>
     </row>
     <row r="671">
@@ -41378,7 +41378,7 @@
         </is>
       </c>
       <c r="M671" s="2" t="n">
-        <v>840.87</v>
+        <v>834.84</v>
       </c>
     </row>
     <row r="672">
@@ -41439,7 +41439,7 @@
         </is>
       </c>
       <c r="M672" s="2" t="n">
-        <v>3476.79</v>
+        <v>3451.89</v>
       </c>
     </row>
     <row r="673">
@@ -41500,7 +41500,7 @@
         </is>
       </c>
       <c r="M673" s="2" t="n">
-        <v>1314.38</v>
+        <v>1304.97</v>
       </c>
     </row>
     <row r="674">
@@ -41561,7 +41561,7 @@
         </is>
       </c>
       <c r="M674" s="2" t="n">
-        <v>1290.52</v>
+        <v>1281.28</v>
       </c>
     </row>
     <row r="675">
@@ -41622,7 +41622,7 @@
         </is>
       </c>
       <c r="M675" s="2" t="n">
-        <v>5275.01</v>
+        <v>5237.22</v>
       </c>
     </row>
     <row r="676">
@@ -41683,7 +41683,7 @@
         </is>
       </c>
       <c r="M676" s="2" t="n">
-        <v>8827.129999999999</v>
+        <v>8763.889999999999</v>
       </c>
     </row>
     <row r="677">
@@ -41744,7 +41744,7 @@
         </is>
       </c>
       <c r="M677" s="2" t="n">
-        <v>4524.28</v>
+        <v>4491.87</v>
       </c>
     </row>
     <row r="678">
@@ -41805,7 +41805,7 @@
         </is>
       </c>
       <c r="M678" s="2" t="n">
-        <v>5771.09</v>
+        <v>5729.75</v>
       </c>
     </row>
     <row r="679">
@@ -41866,7 +41866,7 @@
         </is>
       </c>
       <c r="M679" s="2" t="n">
-        <v>2864.42</v>
+        <v>2843.9</v>
       </c>
     </row>
     <row r="680">
@@ -41927,7 +41927,7 @@
         </is>
       </c>
       <c r="M680" s="2" t="n">
-        <v>1768.57</v>
+        <v>1755.9</v>
       </c>
     </row>
     <row r="681">
@@ -41988,7 +41988,7 @@
         </is>
       </c>
       <c r="M681" s="2" t="n">
-        <v>3580.83</v>
+        <v>3555.18</v>
       </c>
     </row>
     <row r="682">
@@ -42049,7 +42049,7 @@
         </is>
       </c>
       <c r="M682" s="2" t="n">
-        <v>12351.83</v>
+        <v>12263.34</v>
       </c>
     </row>
     <row r="683">
@@ -42110,7 +42110,7 @@
         </is>
       </c>
       <c r="M683" s="2" t="n">
-        <v>1720.93</v>
+        <v>1718.4</v>
       </c>
     </row>
     <row r="684">
@@ -42171,7 +42171,7 @@
         </is>
       </c>
       <c r="M684" s="2" t="n">
-        <v>6229.82</v>
+        <v>6220.65</v>
       </c>
     </row>
     <row r="685">
@@ -42232,7 +42232,7 @@
         </is>
       </c>
       <c r="M685" s="2" t="n">
-        <v>933.34</v>
+        <v>931.97</v>
       </c>
     </row>
     <row r="686">
@@ -42293,7 +42293,7 @@
         </is>
       </c>
       <c r="M686" s="2" t="n">
-        <v>8317.58</v>
+        <v>8305.35</v>
       </c>
     </row>
     <row r="687">
@@ -42354,7 +42354,7 @@
         </is>
       </c>
       <c r="M687" s="2" t="n">
-        <v>1544.2</v>
+        <v>1541.93</v>
       </c>
     </row>
     <row r="688">
@@ -42415,7 +42415,7 @@
         </is>
       </c>
       <c r="M688" s="2" t="n">
-        <v>6558.79</v>
+        <v>6549.14</v>
       </c>
     </row>
     <row r="689">
@@ -42476,7 +42476,7 @@
         </is>
       </c>
       <c r="M689" s="2" t="n">
-        <v>25135.75</v>
+        <v>25098.77</v>
       </c>
     </row>
     <row r="690">
@@ -42537,7 +42537,7 @@
         </is>
       </c>
       <c r="M690" s="2" t="n">
-        <v>2899.43</v>
+        <v>2895.17</v>
       </c>
     </row>
     <row r="691">
@@ -42598,7 +42598,7 @@
         </is>
       </c>
       <c r="M691" s="2" t="n">
-        <v>44057.93</v>
+        <v>43993.12</v>
       </c>
     </row>
     <row r="692">
@@ -42659,7 +42659,7 @@
         </is>
       </c>
       <c r="M692" s="2" t="n">
-        <v>34135.78</v>
+        <v>34085.56</v>
       </c>
     </row>
     <row r="693">
@@ -42720,7 +42720,7 @@
         </is>
       </c>
       <c r="M693" s="2" t="n">
-        <v>11531.14</v>
+        <v>11514.17</v>
       </c>
     </row>
     <row r="694">
@@ -42781,7 +42781,7 @@
         </is>
       </c>
       <c r="M694" s="2" t="n">
-        <v>1739.45</v>
+        <v>1736.89</v>
       </c>
     </row>
     <row r="695">
@@ -42842,7 +42842,7 @@
         </is>
       </c>
       <c r="M695" s="2" t="n">
-        <v>4135.7</v>
+        <v>4129.62</v>
       </c>
     </row>
     <row r="696">
@@ -42903,7 +42903,7 @@
         </is>
       </c>
       <c r="M696" s="2" t="n">
-        <v>7268.91</v>
+        <v>7258.22</v>
       </c>
     </row>
     <row r="697">
@@ -42964,7 +42964,7 @@
         </is>
       </c>
       <c r="M697" s="2" t="n">
-        <v>1740.54</v>
+        <v>1737.98</v>
       </c>
     </row>
     <row r="698">
@@ -43025,7 +43025,7 @@
         </is>
       </c>
       <c r="M698" s="2" t="n">
-        <v>2438.48</v>
+        <v>2434.89</v>
       </c>
     </row>
     <row r="699">
@@ -43086,7 +43086,7 @@
         </is>
       </c>
       <c r="M699" s="2" t="n">
-        <v>1882.28</v>
+        <v>1879.51</v>
       </c>
     </row>
     <row r="700">
@@ -43147,7 +43147,7 @@
         </is>
       </c>
       <c r="M700" s="2" t="n">
-        <v>2095.33</v>
+        <v>2092.25</v>
       </c>
     </row>
     <row r="701">
@@ -43208,7 +43208,7 @@
         </is>
       </c>
       <c r="M701" s="2" t="n">
-        <v>2033.1</v>
+        <v>2030.11</v>
       </c>
     </row>
     <row r="702">
@@ -43269,7 +43269,7 @@
         </is>
       </c>
       <c r="M702" s="2" t="n">
-        <v>3588.05</v>
+        <v>3582.77</v>
       </c>
     </row>
     <row r="703">
@@ -43330,7 +43330,7 @@
         </is>
       </c>
       <c r="M703" s="2" t="n">
-        <v>4428.85</v>
+        <v>4422.33</v>
       </c>
     </row>
     <row r="704">
@@ -43391,7 +43391,7 @@
         </is>
       </c>
       <c r="M704" s="2" t="n">
-        <v>2550.85</v>
+        <v>2547.1</v>
       </c>
     </row>
     <row r="705">
@@ -43452,7 +43452,7 @@
         </is>
       </c>
       <c r="M705" s="2" t="n">
-        <v>4026.78</v>
+        <v>4020.86</v>
       </c>
     </row>
     <row r="706">
@@ -43513,7 +43513,7 @@
         </is>
       </c>
       <c r="M706" s="2" t="n">
-        <v>2283.75</v>
+        <v>2280.39</v>
       </c>
     </row>
     <row r="707">
@@ -43574,7 +43574,7 @@
         </is>
       </c>
       <c r="M707" s="2" t="n">
-        <v>4860.91</v>
+        <v>4853.76</v>
       </c>
     </row>
     <row r="708">
@@ -43635,7 +43635,7 @@
         </is>
       </c>
       <c r="M708" s="2" t="n">
-        <v>23182.51</v>
+        <v>23148.41</v>
       </c>
     </row>
     <row r="709">
@@ -43696,7 +43696,7 @@
         </is>
       </c>
       <c r="M709" s="2" t="n">
-        <v>4616.06</v>
+        <v>4609.27</v>
       </c>
     </row>
     <row r="710">
@@ -43757,7 +43757,7 @@
         </is>
       </c>
       <c r="M710" s="2" t="n">
-        <v>14578.07</v>
+        <v>14556.62</v>
       </c>
     </row>
     <row r="711">
@@ -43818,7 +43818,7 @@
         </is>
       </c>
       <c r="M711" s="2" t="n">
-        <v>9126.67</v>
+        <v>9113.25</v>
       </c>
     </row>
     <row r="712">
@@ -43879,7 +43879,7 @@
         </is>
       </c>
       <c r="M712" s="2" t="n">
-        <v>4599.97</v>
+        <v>4593.2</v>
       </c>
     </row>
     <row r="713">
@@ -43940,7 +43940,7 @@
         </is>
       </c>
       <c r="M713" s="2" t="n">
-        <v>1685.91</v>
+        <v>1683.43</v>
       </c>
     </row>
     <row r="714">
@@ -44001,7 +44001,7 @@
         </is>
       </c>
       <c r="M714" s="2" t="n">
-        <v>2988.98</v>
+        <v>2984.58</v>
       </c>
     </row>
     <row r="715">
@@ -44062,7 +44062,7 @@
         </is>
       </c>
       <c r="M715" s="2" t="n">
-        <v>17560.16</v>
+        <v>17534.33</v>
       </c>
     </row>
     <row r="716">
@@ -44123,7 +44123,7 @@
         </is>
       </c>
       <c r="M716" s="2" t="n">
-        <v>2136.32</v>
+        <v>2133.18</v>
       </c>
     </row>
     <row r="717">
@@ -44184,7 +44184,7 @@
         </is>
       </c>
       <c r="M717" s="2" t="n">
-        <v>8744.309999999999</v>
+        <v>8731.450000000001</v>
       </c>
     </row>
     <row r="718">
@@ -44245,7 +44245,7 @@
         </is>
       </c>
       <c r="M718" s="2" t="n">
-        <v>6553.87</v>
+        <v>6544.23</v>
       </c>
     </row>
     <row r="719">
@@ -44306,7 +44306,7 @@
         </is>
       </c>
       <c r="M719" s="2" t="n">
-        <v>4518.1</v>
+        <v>4511.45</v>
       </c>
     </row>
     <row r="720">
@@ -44367,7 +44367,7 @@
         </is>
       </c>
       <c r="M720" s="2" t="n">
-        <v>1461.29</v>
+        <v>1453.34</v>
       </c>
     </row>
     <row r="721">
@@ -44428,7 +44428,7 @@
         </is>
       </c>
       <c r="M721" s="2" t="n">
-        <v>1719.03</v>
+        <v>1709.67</v>
       </c>
     </row>
     <row r="722">
@@ -44489,7 +44489,7 @@
         </is>
       </c>
       <c r="M722" s="2" t="n">
-        <v>918.02</v>
+        <v>913.02</v>
       </c>
     </row>
     <row r="723">
@@ -44550,7 +44550,7 @@
         </is>
       </c>
       <c r="M723" s="2" t="n">
-        <v>2187.91</v>
+        <v>2175.99</v>
       </c>
     </row>
     <row r="724">
@@ -44611,7 +44611,7 @@
         </is>
       </c>
       <c r="M724" s="2" t="n">
-        <v>1839.91</v>
+        <v>1829.89</v>
       </c>
     </row>
     <row r="725">
@@ -44672,7 +44672,7 @@
         </is>
       </c>
       <c r="M725" s="2" t="n">
-        <v>6864</v>
+        <v>6826.62</v>
       </c>
     </row>
     <row r="726">
@@ -44733,7 +44733,7 @@
         </is>
       </c>
       <c r="M726" s="2" t="n">
-        <v>987.11</v>
+        <v>981.74</v>
       </c>
     </row>
     <row r="727">
@@ -44794,7 +44794,7 @@
         </is>
       </c>
       <c r="M727" s="2" t="n">
-        <v>1387.08</v>
+        <v>1379.53</v>
       </c>
     </row>
     <row r="728">
@@ -44855,7 +44855,7 @@
         </is>
       </c>
       <c r="M728" s="2" t="n">
-        <v>19199.69</v>
+        <v>19095.14</v>
       </c>
     </row>
     <row r="729">
@@ -44916,7 +44916,7 @@
         </is>
       </c>
       <c r="M729" s="2" t="n">
-        <v>2753.36</v>
+        <v>2738.37</v>
       </c>
     </row>
     <row r="730">
@@ -44977,7 +44977,7 @@
         </is>
       </c>
       <c r="M730" s="2" t="n">
-        <v>38715.91</v>
+        <v>38505.08</v>
       </c>
     </row>
     <row r="731">
@@ -45038,7 +45038,7 @@
         </is>
       </c>
       <c r="M731" s="2" t="n">
-        <v>1228.46</v>
+        <v>1221.77</v>
       </c>
     </row>
     <row r="732">
@@ -45099,7 +45099,7 @@
         </is>
       </c>
       <c r="M732" s="2" t="n">
-        <v>969.09</v>
+        <v>963.8099999999999</v>
       </c>
     </row>
     <row r="733">
@@ -45160,7 +45160,7 @@
         </is>
       </c>
       <c r="M733" s="2" t="n">
-        <v>6743.64</v>
+        <v>6706.91</v>
       </c>
     </row>
     <row r="734">
@@ -45221,7 +45221,7 @@
         </is>
       </c>
       <c r="M734" s="2" t="n">
-        <v>1212.15</v>
+        <v>1205.55</v>
       </c>
     </row>
     <row r="735">
@@ -45282,7 +45282,7 @@
         </is>
       </c>
       <c r="M735" s="2" t="n">
-        <v>1180.52</v>
+        <v>1174.09</v>
       </c>
     </row>
     <row r="736">
@@ -45343,7 +45343,7 @@
         </is>
       </c>
       <c r="M736" s="2" t="n">
-        <v>3310.79</v>
+        <v>3292.76</v>
       </c>
     </row>
     <row r="737">
@@ -45404,7 +45404,7 @@
         </is>
       </c>
       <c r="M737" s="2" t="n">
-        <v>855.21</v>
+        <v>850.55</v>
       </c>
     </row>
     <row r="738">
@@ -45465,7 +45465,7 @@
         </is>
       </c>
       <c r="M738" s="2" t="n">
-        <v>7238.92</v>
+        <v>7199.5</v>
       </c>
     </row>
     <row r="739">
@@ -45526,7 +45526,7 @@
         </is>
       </c>
       <c r="M739" s="2" t="n">
-        <v>829.03</v>
+        <v>824.52</v>
       </c>
     </row>
     <row r="740">
@@ -45587,7 +45587,7 @@
         </is>
       </c>
       <c r="M740" s="2" t="n">
-        <v>1229.18</v>
+        <v>1222.48</v>
       </c>
     </row>
     <row r="741">
@@ -45648,7 +45648,7 @@
         </is>
       </c>
       <c r="M741" s="2" t="n">
-        <v>4303.56</v>
+        <v>4280.12</v>
       </c>
     </row>
     <row r="742">
@@ -45709,7 +45709,7 @@
         </is>
       </c>
       <c r="M742" s="2" t="n">
-        <v>5153.88</v>
+        <v>5125.81</v>
       </c>
     </row>
     <row r="743">
@@ -45770,7 +45770,7 @@
         </is>
       </c>
       <c r="M743" s="2" t="n">
-        <v>3299.54</v>
+        <v>3281.58</v>
       </c>
     </row>
     <row r="744">
@@ -45831,7 +45831,7 @@
         </is>
       </c>
       <c r="M744" s="2" t="n">
-        <v>2620.27</v>
+        <v>2606</v>
       </c>
     </row>
     <row r="745">
@@ -45892,7 +45892,7 @@
         </is>
       </c>
       <c r="M745" s="2" t="n">
-        <v>8881.9</v>
+        <v>8833.530000000001</v>
       </c>
     </row>
     <row r="746">
@@ -45953,7 +45953,7 @@
         </is>
       </c>
       <c r="M746" s="2" t="n">
-        <v>3676.85</v>
+        <v>3656.83</v>
       </c>
     </row>
     <row r="747">
@@ -46014,7 +46014,7 @@
         </is>
       </c>
       <c r="M747" s="2" t="n">
-        <v>6697.76</v>
+        <v>6661.29</v>
       </c>
     </row>
     <row r="748">
@@ -46075,7 +46075,7 @@
         </is>
       </c>
       <c r="M748" s="2" t="n">
-        <v>4363.07</v>
+        <v>4339.31</v>
       </c>
     </row>
     <row r="749">
@@ -46136,7 +46136,7 @@
         </is>
       </c>
       <c r="M749" s="2" t="n">
-        <v>2452.39</v>
+        <v>2439.04</v>
       </c>
     </row>
     <row r="750">
@@ -46197,7 +46197,7 @@
         </is>
       </c>
       <c r="M750" s="2" t="n">
-        <v>3046.32</v>
+        <v>3029.73</v>
       </c>
     </row>
     <row r="751">
@@ -46258,7 +46258,7 @@
         </is>
       </c>
       <c r="M751" s="2" t="n">
-        <v>5401.67</v>
+        <v>5372.26</v>
       </c>
     </row>
     <row r="752">
@@ -46319,7 +46319,7 @@
         </is>
       </c>
       <c r="M752" s="2" t="n">
-        <v>1430.22</v>
+        <v>1422.44</v>
       </c>
     </row>
     <row r="753">
@@ -46380,7 +46380,7 @@
         </is>
       </c>
       <c r="M753" s="2" t="n">
-        <v>1683.77</v>
+        <v>1674.6</v>
       </c>
     </row>
     <row r="754">
@@ -46441,7 +46441,7 @@
         </is>
       </c>
       <c r="M754" s="2" t="n">
-        <v>2651.53</v>
+        <v>2637.09</v>
       </c>
     </row>
     <row r="755">
@@ -46502,7 +46502,7 @@
         </is>
       </c>
       <c r="M755" s="2" t="n">
-        <v>3366.8</v>
+        <v>3348.47</v>
       </c>
     </row>
     <row r="756">
@@ -46563,7 +46563,7 @@
         </is>
       </c>
       <c r="M756" s="2" t="n">
-        <v>3246.25</v>
+        <v>3228.57</v>
       </c>
     </row>
     <row r="757">
@@ -46624,7 +46624,7 @@
         </is>
       </c>
       <c r="M757" s="2" t="n">
-        <v>2720.09</v>
+        <v>2705.28</v>
       </c>
     </row>
     <row r="758">
@@ -46685,7 +46685,7 @@
         </is>
       </c>
       <c r="M758" s="2" t="n">
-        <v>51360.26</v>
+        <v>51080.56</v>
       </c>
     </row>
     <row r="759">
@@ -46746,7 +46746,7 @@
         </is>
       </c>
       <c r="M759" s="2" t="n">
-        <v>5651.09</v>
+        <v>5620.32</v>
       </c>
     </row>
     <row r="760">
@@ -46807,7 +46807,7 @@
         </is>
       </c>
       <c r="M760" s="2" t="n">
-        <v>6027.63</v>
+        <v>5994.81</v>
       </c>
     </row>
     <row r="761">
@@ -46868,7 +46868,7 @@
         </is>
       </c>
       <c r="M761" s="2" t="n">
-        <v>6987.06</v>
+        <v>6949.01</v>
       </c>
     </row>
     <row r="762">
@@ -46929,7 +46929,7 @@
         </is>
       </c>
       <c r="M762" s="2" t="n">
-        <v>30513.16</v>
+        <v>30346.99</v>
       </c>
     </row>
     <row r="763">
@@ -46990,7 +46990,7 @@
         </is>
       </c>
       <c r="M763" s="2" t="n">
-        <v>2876.94</v>
+        <v>2861.27</v>
       </c>
     </row>
     <row r="764">
@@ -47051,7 +47051,7 @@
         </is>
       </c>
       <c r="M764" s="2" t="n">
-        <v>28238.98</v>
+        <v>28085.2</v>
       </c>
     </row>
     <row r="765">
@@ -47112,7 +47112,7 @@
         </is>
       </c>
       <c r="M765" s="2" t="n">
-        <v>3640.21</v>
+        <v>3618.75</v>
       </c>
     </row>
     <row r="766">
@@ -47173,7 +47173,7 @@
         </is>
       </c>
       <c r="M766" s="2" t="n">
-        <v>6160.11</v>
+        <v>6123.81</v>
       </c>
     </row>
     <row r="767">
@@ -47234,7 +47234,7 @@
         </is>
       </c>
       <c r="M767" s="2" t="n">
-        <v>910.99</v>
+        <v>905.62</v>
       </c>
     </row>
     <row r="768">
@@ -47295,7 +47295,7 @@
         </is>
       </c>
       <c r="M768" s="2" t="n">
-        <v>1779.23</v>
+        <v>1768.74</v>
       </c>
     </row>
     <row r="769">
@@ -47356,7 +47356,7 @@
         </is>
       </c>
       <c r="M769" s="2" t="n">
-        <v>12295.65</v>
+        <v>12223.19</v>
       </c>
     </row>
     <row r="770">
@@ -47417,7 +47417,7 @@
         </is>
       </c>
       <c r="M770" s="2" t="n">
-        <v>1107.57</v>
+        <v>1101.04</v>
       </c>
     </row>
     <row r="771">
@@ -47478,7 +47478,7 @@
         </is>
       </c>
       <c r="M771" s="2" t="n">
-        <v>1686.08</v>
+        <v>1676.15</v>
       </c>
     </row>
     <row r="772">
@@ -47539,7 +47539,7 @@
         </is>
       </c>
       <c r="M772" s="2" t="n">
-        <v>6206.35</v>
+        <v>6169.78</v>
       </c>
     </row>
     <row r="773">
@@ -47600,7 +47600,7 @@
         </is>
       </c>
       <c r="M773" s="2" t="n">
-        <v>4444.59</v>
+        <v>4418.4</v>
       </c>
     </row>
     <row r="774">
@@ -47661,7 +47661,7 @@
         </is>
       </c>
       <c r="M774" s="2" t="n">
-        <v>13780.13</v>
+        <v>13698.92</v>
       </c>
     </row>
     <row r="775">
@@ -47722,7 +47722,7 @@
         </is>
       </c>
       <c r="M775" s="2" t="n">
-        <v>4396.13</v>
+        <v>4370.23</v>
       </c>
     </row>
     <row r="776">
@@ -47783,7 +47783,7 @@
         </is>
       </c>
       <c r="M776" s="2" t="n">
-        <v>2371.72</v>
+        <v>2357.74</v>
       </c>
     </row>
     <row r="777">
@@ -47844,7 +47844,7 @@
         </is>
       </c>
       <c r="M777" s="2" t="n">
-        <v>847.89</v>
+        <v>842.89</v>
       </c>
     </row>
     <row r="778">
@@ -47905,7 +47905,7 @@
         </is>
       </c>
       <c r="M778" s="2" t="n">
-        <v>1045.01</v>
+        <v>1038.85</v>
       </c>
     </row>
     <row r="779">
@@ -47966,7 +47966,7 @@
         </is>
       </c>
       <c r="M779" s="2" t="n">
-        <v>1049.55</v>
+        <v>1043.37</v>
       </c>
     </row>
     <row r="780">
@@ -48027,7 +48027,7 @@
         </is>
       </c>
       <c r="M780" s="2" t="n">
-        <v>2474.44</v>
+        <v>2459.86</v>
       </c>
     </row>
     <row r="781">
@@ -48088,7 +48088,7 @@
         </is>
       </c>
       <c r="M781" s="2" t="n">
-        <v>1987.45</v>
+        <v>1975.73</v>
       </c>
     </row>
     <row r="782">
@@ -48149,7 +48149,7 @@
         </is>
       </c>
       <c r="M782" s="2" t="n">
-        <v>2309.64</v>
+        <v>2296.03</v>
       </c>
     </row>
     <row r="783">
@@ -48210,7 +48210,7 @@
         </is>
       </c>
       <c r="M783" s="2" t="n">
-        <v>1414.46</v>
+        <v>1406.12</v>
       </c>
     </row>
     <row r="784">
@@ -48271,7 +48271,7 @@
         </is>
       </c>
       <c r="M784" s="2" t="n">
-        <v>1662.65</v>
+        <v>1652.85</v>
       </c>
     </row>
     <row r="785">
@@ -48332,7 +48332,7 @@
         </is>
       </c>
       <c r="M785" s="2" t="n">
-        <v>4336.84</v>
+        <v>4311.29</v>
       </c>
     </row>
     <row r="786">
@@ -48393,7 +48393,7 @@
         </is>
       </c>
       <c r="M786" s="2" t="n">
-        <v>1149.72</v>
+        <v>1142.94</v>
       </c>
     </row>
     <row r="787">
@@ -48454,7 +48454,7 @@
         </is>
       </c>
       <c r="M787" s="2" t="n">
-        <v>1569.6</v>
+        <v>1560.35</v>
       </c>
     </row>
     <row r="788">
@@ -48515,7 +48515,7 @@
         </is>
       </c>
       <c r="M788" s="2" t="n">
-        <v>812.61</v>
+        <v>807.8200000000001</v>
       </c>
     </row>
     <row r="789">
@@ -48576,7 +48576,7 @@
         </is>
       </c>
       <c r="M789" s="2" t="n">
-        <v>3874.72</v>
+        <v>3851.88</v>
       </c>
     </row>
     <row r="790">
@@ -48637,7 +48637,7 @@
         </is>
       </c>
       <c r="M790" s="2" t="n">
-        <v>1853.31</v>
+        <v>1842.39</v>
       </c>
     </row>
     <row r="791">
@@ -48698,7 +48698,7 @@
         </is>
       </c>
       <c r="M791" s="2" t="n">
-        <v>17604.08</v>
+        <v>17500.34</v>
       </c>
     </row>
     <row r="792">
@@ -48759,7 +48759,7 @@
         </is>
       </c>
       <c r="M792" s="2" t="n">
-        <v>25296.97</v>
+        <v>25147.89</v>
       </c>
     </row>
     <row r="793">
@@ -48820,7 +48820,7 @@
         </is>
       </c>
       <c r="M793" s="2" t="n">
-        <v>2646.53</v>
+        <v>2630.93</v>
       </c>
     </row>
     <row r="794">
@@ -48881,7 +48881,7 @@
         </is>
       </c>
       <c r="M794" s="2" t="n">
-        <v>1065.73</v>
+        <v>1059.45</v>
       </c>
     </row>
     <row r="795">
@@ -48942,7 +48942,7 @@
         </is>
       </c>
       <c r="M795" s="2" t="n">
-        <v>44100.98</v>
+        <v>43841.09</v>
       </c>
     </row>
     <row r="796">
@@ -49003,7 +49003,7 @@
         </is>
       </c>
       <c r="M796" s="2" t="n">
-        <v>2733.35</v>
+        <v>2717.24</v>
       </c>
     </row>
     <row r="797">
@@ -49064,7 +49064,7 @@
         </is>
       </c>
       <c r="M797" s="2" t="n">
-        <v>1523.3</v>
+        <v>1514.33</v>
       </c>
     </row>
     <row r="798">
@@ -49125,7 +49125,7 @@
         </is>
       </c>
       <c r="M798" s="2" t="n">
-        <v>2710.9</v>
+        <v>2694.92</v>
       </c>
     </row>
     <row r="799">
@@ -49186,7 +49186,7 @@
         </is>
       </c>
       <c r="M799" s="2" t="n">
-        <v>2946.27</v>
+        <v>2928.91</v>
       </c>
     </row>
     <row r="800">
@@ -49247,7 +49247,7 @@
         </is>
       </c>
       <c r="M800" s="2" t="n">
-        <v>818.4299999999999</v>
+        <v>813.61</v>
       </c>
     </row>
     <row r="801">
@@ -49308,7 +49308,7 @@
         </is>
       </c>
       <c r="M801" s="2" t="n">
-        <v>1318.73</v>
+        <v>1310.96</v>
       </c>
     </row>
     <row r="802">
@@ -49369,7 +49369,7 @@
         </is>
       </c>
       <c r="M802" s="2" t="n">
-        <v>863.71</v>
+        <v>858.62</v>
       </c>
     </row>
     <row r="803">
@@ -49430,7 +49430,7 @@
         </is>
       </c>
       <c r="M803" s="2" t="n">
-        <v>2793.38</v>
+        <v>2776.92</v>
       </c>
     </row>
     <row r="804">
@@ -49491,7 +49491,7 @@
         </is>
       </c>
       <c r="M804" s="2" t="n">
-        <v>9198.219999999999</v>
+        <v>9144.01</v>
       </c>
     </row>
     <row r="805">
@@ -49552,7 +49552,7 @@
         </is>
       </c>
       <c r="M805" s="2" t="n">
-        <v>11583.55</v>
+        <v>11515.28</v>
       </c>
     </row>
     <row r="806">
@@ -49613,7 +49613,7 @@
         </is>
       </c>
       <c r="M806" s="2" t="n">
-        <v>1700.25</v>
+        <v>1690.23</v>
       </c>
     </row>
     <row r="807">
@@ -49674,7 +49674,7 @@
         </is>
       </c>
       <c r="M807" s="2" t="n">
-        <v>65986.87</v>
+        <v>65598.00999999999</v>
       </c>
     </row>
     <row r="808">
@@ -49735,7 +49735,7 @@
         </is>
       </c>
       <c r="M808" s="2" t="n">
-        <v>3231.6</v>
+        <v>3212.56</v>
       </c>
     </row>
     <row r="809">
@@ -49796,7 +49796,7 @@
         </is>
       </c>
       <c r="M809" s="2" t="n">
-        <v>28512.17</v>
+        <v>28344.15</v>
       </c>
     </row>
     <row r="810">
@@ -49857,7 +49857,7 @@
         </is>
       </c>
       <c r="M810" s="2" t="n">
-        <v>4876.13</v>
+        <v>4847.39</v>
       </c>
     </row>
     <row r="811">
@@ -49918,7 +49918,7 @@
         </is>
       </c>
       <c r="M811" s="2" t="n">
-        <v>5394.91</v>
+        <v>5363.12</v>
       </c>
     </row>
     <row r="812">
@@ -49979,7 +49979,7 @@
         </is>
       </c>
       <c r="M812" s="2" t="n">
-        <v>15438.43</v>
+        <v>15347.45</v>
       </c>
     </row>
     <row r="813">
@@ -50040,7 +50040,7 @@
         </is>
       </c>
       <c r="M813" s="2" t="n">
-        <v>815.09</v>
+        <v>810.28</v>
       </c>
     </row>
     <row r="814">
@@ -50101,7 +50101,7 @@
         </is>
       </c>
       <c r="M814" s="2" t="n">
-        <v>1335.76</v>
+        <v>1327.89</v>
       </c>
     </row>
     <row r="815">
@@ -50162,7 +50162,7 @@
         </is>
       </c>
       <c r="M815" s="2" t="n">
-        <v>1875.55</v>
+        <v>1864.15</v>
       </c>
     </row>
     <row r="816">
@@ -50223,7 +50223,7 @@
         </is>
       </c>
       <c r="M816" s="2" t="n">
-        <v>40887.01</v>
+        <v>40638.56</v>
       </c>
     </row>
     <row r="817">
@@ -50284,7 +50284,7 @@
         </is>
       </c>
       <c r="M817" s="2" t="n">
-        <v>867.38</v>
+        <v>862.1</v>
       </c>
     </row>
     <row r="818">
@@ -50345,7 +50345,7 @@
         </is>
       </c>
       <c r="M818" s="2" t="n">
-        <v>4280.45</v>
+        <v>4254.44</v>
       </c>
     </row>
     <row r="819">
@@ -50406,7 +50406,7 @@
         </is>
       </c>
       <c r="M819" s="2" t="n">
-        <v>827.2</v>
+        <v>822.17</v>
       </c>
     </row>
     <row r="820">
@@ -50467,7 +50467,7 @@
         </is>
       </c>
       <c r="M820" s="2" t="n">
-        <v>1416.06</v>
+        <v>1407.45</v>
       </c>
     </row>
     <row r="821">
@@ -50528,7 +50528,7 @@
         </is>
       </c>
       <c r="M821" s="2" t="n">
-        <v>1226.97</v>
+        <v>1219.51</v>
       </c>
     </row>
     <row r="822">
@@ -50589,7 +50589,7 @@
         </is>
       </c>
       <c r="M822" s="2" t="n">
-        <v>997.83</v>
+        <v>991.77</v>
       </c>
     </row>
     <row r="823">
@@ -50650,7 +50650,7 @@
         </is>
       </c>
       <c r="M823" s="2" t="n">
-        <v>8011.49</v>
+        <v>7962.81</v>
       </c>
     </row>
     <row r="824">
@@ -50711,7 +50711,7 @@
         </is>
       </c>
       <c r="M824" s="2" t="n">
-        <v>2379.13</v>
+        <v>2364.67</v>
       </c>
     </row>
     <row r="825">
@@ -50772,7 +50772,7 @@
         </is>
       </c>
       <c r="M825" s="2" t="n">
-        <v>13448.65</v>
+        <v>13366.93</v>
       </c>
     </row>
     <row r="826">
@@ -50833,7 +50833,7 @@
         </is>
       </c>
       <c r="M826" s="2" t="n">
-        <v>25104.02</v>
+        <v>24951.48</v>
       </c>
     </row>
     <row r="827">
@@ -50894,7 +50894,7 @@
         </is>
       </c>
       <c r="M827" s="2" t="n">
-        <v>3448.71</v>
+        <v>3427.76</v>
       </c>
     </row>
     <row r="828">
@@ -50955,7 +50955,7 @@
         </is>
       </c>
       <c r="M828" s="2" t="n">
-        <v>7024.7</v>
+        <v>6982.02</v>
       </c>
     </row>
     <row r="829">
@@ -51016,7 +51016,7 @@
         </is>
       </c>
       <c r="M829" s="2" t="n">
-        <v>23519.38</v>
+        <v>23376.47</v>
       </c>
     </row>
     <row r="830">
@@ -51077,7 +51077,7 @@
         </is>
       </c>
       <c r="M830" s="2" t="n">
-        <v>44390.5</v>
+        <v>44120.77</v>
       </c>
     </row>
     <row r="831">
@@ -51138,7 +51138,7 @@
         </is>
       </c>
       <c r="M831" s="2" t="n">
-        <v>12341.48</v>
+        <v>12266.49</v>
       </c>
     </row>
     <row r="832">
@@ -51199,7 +51199,7 @@
         </is>
       </c>
       <c r="M832" s="2" t="n">
-        <v>3772.92</v>
+        <v>3749.99</v>
       </c>
     </row>
     <row r="833">
@@ -51260,7 +51260,7 @@
         </is>
       </c>
       <c r="M833" s="2" t="n">
-        <v>4171.82</v>
+        <v>4146.47</v>
       </c>
     </row>
     <row r="834">
@@ -51321,7 +51321,7 @@
         </is>
       </c>
       <c r="M834" s="2" t="n">
-        <v>3702.44</v>
+        <v>3679.95</v>
       </c>
     </row>
     <row r="835">
@@ -51382,7 +51382,7 @@
         </is>
       </c>
       <c r="M835" s="2" t="n">
-        <v>1865.49</v>
+        <v>1854.15</v>
       </c>
     </row>
     <row r="836">
@@ -51443,7 +51443,7 @@
         </is>
       </c>
       <c r="M836" s="2" t="n">
-        <v>2855.32</v>
+        <v>2837.97</v>
       </c>
     </row>
     <row r="837">
@@ -51504,7 +51504,7 @@
         </is>
       </c>
       <c r="M837" s="2" t="n">
-        <v>13778.12</v>
+        <v>13694.4</v>
       </c>
     </row>
     <row r="838">
@@ -51565,7 +51565,7 @@
         </is>
       </c>
       <c r="M838" s="2" t="n">
-        <v>1197.78</v>
+        <v>1190.5</v>
       </c>
     </row>
     <row r="839">
@@ -51626,7 +51626,7 @@
         </is>
       </c>
       <c r="M839" s="2" t="n">
-        <v>2675.64</v>
+        <v>2659.38</v>
       </c>
     </row>
     <row r="840">
@@ -51687,7 +51687,7 @@
         </is>
       </c>
       <c r="M840" s="2" t="n">
-        <v>3594.57</v>
+        <v>3572.72</v>
       </c>
     </row>
     <row r="841">
@@ -51748,7 +51748,7 @@
         </is>
       </c>
       <c r="M841" s="2" t="n">
-        <v>830.98</v>
+        <v>825.9299999999999</v>
       </c>
     </row>
     <row r="842">
@@ -51809,7 +51809,7 @@
         </is>
       </c>
       <c r="M842" s="2" t="n">
-        <v>888.17</v>
+        <v>882.78</v>
       </c>
     </row>
     <row r="843">
@@ -51870,7 +51870,7 @@
         </is>
       </c>
       <c r="M843" s="2" t="n">
-        <v>6767.34</v>
+        <v>6726.22</v>
       </c>
     </row>
     <row r="844">
@@ -51931,7 +51931,7 @@
         </is>
       </c>
       <c r="M844" s="2" t="n">
-        <v>1068.95</v>
+        <v>1062.46</v>
       </c>
     </row>
     <row r="845">
@@ -51992,7 +51992,7 @@
         </is>
       </c>
       <c r="M845" s="2" t="n">
-        <v>1031.55</v>
+        <v>1025.29</v>
       </c>
     </row>
     <row r="846">
@@ -52053,7 +52053,7 @@
         </is>
       </c>
       <c r="M846" s="2" t="n">
-        <v>7453.58</v>
+        <v>7408.28</v>
       </c>
     </row>
     <row r="847">
@@ -52114,7 +52114,7 @@
         </is>
       </c>
       <c r="M847" s="2" t="n">
-        <v>1846.54</v>
+        <v>1835.32</v>
       </c>
     </row>
     <row r="848">
@@ -52175,7 +52175,7 @@
         </is>
       </c>
       <c r="M848" s="2" t="n">
-        <v>49142.27</v>
+        <v>48843.66</v>
       </c>
     </row>
     <row r="849">
@@ -52236,7 +52236,7 @@
         </is>
       </c>
       <c r="M849" s="2" t="n">
-        <v>1103.83</v>
+        <v>1097.12</v>
       </c>
     </row>
     <row r="850">
@@ -52297,7 +52297,7 @@
         </is>
       </c>
       <c r="M850" s="2" t="n">
-        <v>885.27</v>
+        <v>879.89</v>
       </c>
     </row>
     <row r="851">
@@ -52358,7 +52358,7 @@
         </is>
       </c>
       <c r="M851" s="2" t="n">
-        <v>2394.33</v>
+        <v>2379.78</v>
       </c>
     </row>
     <row r="852">
@@ -52419,7 +52419,7 @@
         </is>
       </c>
       <c r="M852" s="2" t="n">
-        <v>903.5599999999999</v>
+        <v>898.0700000000001</v>
       </c>
     </row>
     <row r="853">
@@ -52480,7 +52480,7 @@
         </is>
       </c>
       <c r="M853" s="2" t="n">
-        <v>13255.48</v>
+        <v>13174.93</v>
       </c>
     </row>
     <row r="854">
@@ -52541,7 +52541,7 @@
         </is>
       </c>
       <c r="M854" s="2" t="n">
-        <v>1214.82</v>
+        <v>1207.44</v>
       </c>
     </row>
     <row r="855">
@@ -52602,7 +52602,7 @@
         </is>
       </c>
       <c r="M855" s="2" t="n">
-        <v>7429.87</v>
+        <v>7384.73</v>
       </c>
     </row>
     <row r="856">
@@ -52663,7 +52663,7 @@
         </is>
       </c>
       <c r="M856" s="2" t="n">
-        <v>1545.91</v>
+        <v>1536.52</v>
       </c>
     </row>
     <row r="857">
@@ -52724,7 +52724,7 @@
         </is>
       </c>
       <c r="M857" s="2" t="n">
-        <v>837.99</v>
+        <v>832.9</v>
       </c>
     </row>
     <row r="858">
@@ -52785,7 +52785,7 @@
         </is>
       </c>
       <c r="M858" s="2" t="n">
-        <v>43905.97</v>
+        <v>43639.18</v>
       </c>
     </row>
     <row r="859">
@@ -52846,7 +52846,7 @@
         </is>
       </c>
       <c r="M859" s="2" t="n">
-        <v>809.51</v>
+        <v>804.59</v>
       </c>
     </row>
     <row r="860">
@@ -52907,7 +52907,7 @@
         </is>
       </c>
       <c r="M860" s="2" t="n">
-        <v>1007.2</v>
+        <v>1001.08</v>
       </c>
     </row>
     <row r="861">
@@ -52968,7 +52968,7 @@
         </is>
       </c>
       <c r="M861" s="2" t="n">
-        <v>28075.95</v>
+        <v>27905.35</v>
       </c>
     </row>
     <row r="862">
@@ -53029,7 +53029,7 @@
         </is>
       </c>
       <c r="M862" s="2" t="n">
-        <v>952.39</v>
+        <v>946.6</v>
       </c>
     </row>
     <row r="863">
@@ -53090,7 +53090,7 @@
         </is>
       </c>
       <c r="M863" s="2" t="n">
-        <v>807.75</v>
+        <v>802.84</v>
       </c>
     </row>
     <row r="864">
@@ -53151,7 +53151,7 @@
         </is>
       </c>
       <c r="M864" s="2" t="n">
-        <v>2090.39</v>
+        <v>2077.69</v>
       </c>
     </row>
     <row r="865">
@@ -53212,7 +53212,7 @@
         </is>
       </c>
       <c r="M865" s="2" t="n">
-        <v>55316.65</v>
+        <v>54980.52</v>
       </c>
     </row>
     <row r="866">
@@ -53273,7 +53273,7 @@
         </is>
       </c>
       <c r="M866" s="2" t="n">
-        <v>65647.94</v>
+        <v>65249.04</v>
       </c>
     </row>
     <row r="867">
@@ -53334,7 +53334,7 @@
         </is>
       </c>
       <c r="M867" s="2" t="n">
-        <v>13728.55</v>
+        <v>13645.13</v>
       </c>
     </row>
     <row r="868">
@@ -53395,7 +53395,7 @@
         </is>
       </c>
       <c r="M868" s="2" t="n">
-        <v>6840.27</v>
+        <v>6813.87</v>
       </c>
     </row>
     <row r="869">
@@ -53456,7 +53456,7 @@
         </is>
       </c>
       <c r="M869" s="2" t="n">
-        <v>1682.83</v>
+        <v>1676.34</v>
       </c>
     </row>
     <row r="870">
@@ -53517,7 +53517,7 @@
         </is>
       </c>
       <c r="M870" s="2" t="n">
-        <v>821.85</v>
+        <v>818.6799999999999</v>
       </c>
     </row>
     <row r="871">
@@ -53578,7 +53578,7 @@
         </is>
       </c>
       <c r="M871" s="2" t="n">
-        <v>4458.98</v>
+        <v>4441.77</v>
       </c>
     </row>
     <row r="872">
@@ -53639,7 +53639,7 @@
         </is>
       </c>
       <c r="M872" s="2" t="n">
-        <v>3271.18</v>
+        <v>3258.56</v>
       </c>
     </row>
     <row r="873">
@@ -53700,7 +53700,7 @@
         </is>
       </c>
       <c r="M873" s="2" t="n">
-        <v>3161.03</v>
+        <v>3148.83</v>
       </c>
     </row>
     <row r="874">
@@ -53761,7 +53761,7 @@
         </is>
       </c>
       <c r="M874" s="2" t="n">
-        <v>5402.09</v>
+        <v>5381.24</v>
       </c>
     </row>
     <row r="875">
@@ -53822,7 +53822,7 @@
         </is>
       </c>
       <c r="M875" s="2" t="n">
-        <v>2208.16</v>
+        <v>2199.64</v>
       </c>
     </row>
     <row r="876">
@@ -53883,7 +53883,7 @@
         </is>
       </c>
       <c r="M876" s="2" t="n">
-        <v>1722.21</v>
+        <v>1715.56</v>
       </c>
     </row>
     <row r="877">
@@ -53944,7 +53944,7 @@
         </is>
       </c>
       <c r="M877" s="2" t="n">
-        <v>6024.54</v>
+        <v>6001.29</v>
       </c>
     </row>
     <row r="878">
@@ -54005,7 +54005,7 @@
         </is>
       </c>
       <c r="M878" s="2" t="n">
-        <v>1828.91</v>
+        <v>1821.85</v>
       </c>
     </row>
     <row r="879">
@@ -54066,7 +54066,7 @@
         </is>
       </c>
       <c r="M879" s="2" t="n">
-        <v>1875.86</v>
+        <v>1868.62</v>
       </c>
     </row>
     <row r="880">
@@ -54127,7 +54127,7 @@
         </is>
       </c>
       <c r="M880" s="2" t="n">
-        <v>958.78</v>
+        <v>955.08</v>
       </c>
     </row>
     <row r="881">
@@ -54188,7 +54188,7 @@
         </is>
       </c>
       <c r="M881" s="2" t="n">
-        <v>9519.41</v>
+        <v>9482.67</v>
       </c>
     </row>
     <row r="882">
@@ -54249,7 +54249,7 @@
         </is>
       </c>
       <c r="M882" s="2" t="n">
-        <v>9806.83</v>
+        <v>9768.98</v>
       </c>
     </row>
     <row r="883">
@@ -54310,7 +54310,7 @@
         </is>
       </c>
       <c r="M883" s="2" t="n">
-        <v>11705.08</v>
+        <v>11659.9</v>
       </c>
     </row>
     <row r="884">
@@ -54371,7 +54371,7 @@
         </is>
       </c>
       <c r="M884" s="2" t="n">
-        <v>7340.7</v>
+        <v>7312.37</v>
       </c>
     </row>
     <row r="885">
@@ -54432,7 +54432,7 @@
         </is>
       </c>
       <c r="M885" s="2" t="n">
-        <v>3575.86</v>
+        <v>3562.06</v>
       </c>
     </row>
     <row r="886">
@@ -54493,7 +54493,7 @@
         </is>
       </c>
       <c r="M886" s="2" t="n">
-        <v>1728.36</v>
+        <v>1721.69</v>
       </c>
     </row>
     <row r="887">
@@ -54554,7 +54554,7 @@
         </is>
       </c>
       <c r="M887" s="2" t="n">
-        <v>11292.31</v>
+        <v>11248.73</v>
       </c>
     </row>
     <row r="888">
@@ -54615,7 +54615,7 @@
         </is>
       </c>
       <c r="M888" s="2" t="n">
-        <v>1422.41</v>
+        <v>1416.92</v>
       </c>
     </row>
     <row r="889">
@@ -54676,7 +54676,7 @@
         </is>
       </c>
       <c r="M889" s="2" t="n">
-        <v>1581.94</v>
+        <v>1575.83</v>
       </c>
     </row>
     <row r="890">
@@ -54737,7 +54737,7 @@
         </is>
       </c>
       <c r="M890" s="2" t="n">
-        <v>7271.61</v>
+        <v>7243.55</v>
       </c>
     </row>
     <row r="891">
@@ -54798,7 +54798,7 @@
         </is>
       </c>
       <c r="M891" s="2" t="n">
-        <v>4264.77</v>
+        <v>4248.31</v>
       </c>
     </row>
     <row r="892">
@@ -54859,7 +54859,7 @@
         </is>
       </c>
       <c r="M892" s="2" t="n">
-        <v>1006.01</v>
+        <v>1002.13</v>
       </c>
     </row>
     <row r="893">
@@ -54920,7 +54920,7 @@
         </is>
       </c>
       <c r="M893" s="2" t="n">
-        <v>1422.41</v>
+        <v>1416.92</v>
       </c>
     </row>
     <row r="894">
@@ -54981,7 +54981,7 @@
         </is>
       </c>
       <c r="M894" s="2" t="n">
-        <v>67566.74000000001</v>
+        <v>67305.96000000001</v>
       </c>
     </row>
     <row r="895">
@@ -55042,7 +55042,7 @@
         </is>
       </c>
       <c r="M895" s="2" t="n">
-        <v>2087.76</v>
+        <v>2079.7</v>
       </c>
     </row>
     <row r="896">
@@ -55103,7 +55103,7 @@
         </is>
       </c>
       <c r="M896" s="2" t="n">
-        <v>2464.83</v>
+        <v>2455.31</v>
       </c>
     </row>
     <row r="897">
@@ -55164,7 +55164,7 @@
         </is>
       </c>
       <c r="M897" s="2" t="n">
-        <v>2427.51</v>
+        <v>2418.14</v>
       </c>
     </row>
     <row r="898">
@@ -55225,7 +55225,7 @@
         </is>
       </c>
       <c r="M898" s="2" t="n">
-        <v>1378.6</v>
+        <v>1373.28</v>
       </c>
     </row>
     <row r="899">
@@ -55286,7 +55286,7 @@
         </is>
       </c>
       <c r="M899" s="2" t="n">
-        <v>3832.35</v>
+        <v>3817.56</v>
       </c>
     </row>
     <row r="900">
@@ -55347,7 +55347,7 @@
         </is>
       </c>
       <c r="M900" s="2" t="n">
-        <v>4774.8</v>
+        <v>4756.37</v>
       </c>
     </row>
     <row r="901">
@@ -55408,7 +55408,7 @@
         </is>
       </c>
       <c r="M901" s="2" t="n">
-        <v>3502.26</v>
+        <v>3488.75</v>
       </c>
     </row>
     <row r="902">
@@ -55469,7 +55469,7 @@
         </is>
       </c>
       <c r="M902" s="2" t="n">
-        <v>2434.75</v>
+        <v>2425.35</v>
       </c>
     </row>
     <row r="903">
@@ -55530,7 +55530,7 @@
         </is>
       </c>
       <c r="M903" s="2" t="n">
-        <v>3333.83</v>
+        <v>3320.96</v>
       </c>
     </row>
     <row r="904">
@@ -55591,7 +55591,7 @@
         </is>
       </c>
       <c r="M904" s="2" t="n">
-        <v>1269.54</v>
+        <v>1264.64</v>
       </c>
     </row>
     <row r="905">
@@ -55652,7 +55652,7 @@
         </is>
       </c>
       <c r="M905" s="2" t="n">
-        <v>11388.95</v>
+        <v>11344.99</v>
       </c>
     </row>
     <row r="906">
@@ -55713,7 +55713,7 @@
         </is>
       </c>
       <c r="M906" s="2" t="n">
-        <v>4193.89</v>
+        <v>4177.71</v>
       </c>
     </row>
     <row r="907">
@@ -55774,7 +55774,7 @@
         </is>
       </c>
       <c r="M907" s="2" t="n">
-        <v>5294.62</v>
+        <v>5274.18</v>
       </c>
     </row>
     <row r="908">
@@ -55835,7 +55835,7 @@
         </is>
       </c>
       <c r="M908" s="2" t="n">
-        <v>2822.58</v>
+        <v>2811.69</v>
       </c>
     </row>
     <row r="909">
@@ -55896,7 +55896,7 @@
         </is>
       </c>
       <c r="M909" s="2" t="n">
-        <v>813.5</v>
+        <v>810.36</v>
       </c>
     </row>
     <row r="910">
@@ -55957,7 +55957,7 @@
         </is>
       </c>
       <c r="M910" s="2" t="n">
-        <v>2577.95</v>
+        <v>2568</v>
       </c>
     </row>
     <row r="911">
@@ -56018,7 +56018,7 @@
         </is>
       </c>
       <c r="M911" s="2" t="n">
-        <v>11035.54</v>
+        <v>10992.95</v>
       </c>
     </row>
     <row r="912">
@@ -56079,7 +56079,7 @@
         </is>
       </c>
       <c r="M912" s="2" t="n">
-        <v>4065.07</v>
+        <v>4049.38</v>
       </c>
     </row>
     <row r="913">
@@ -56140,7 +56140,7 @@
         </is>
       </c>
       <c r="M913" s="2" t="n">
-        <v>2656.91</v>
+        <v>2646.66</v>
       </c>
     </row>
     <row r="914">
@@ -56201,7 +56201,7 @@
         </is>
       </c>
       <c r="M914" s="2" t="n">
-        <v>6938.42</v>
+        <v>6911.64</v>
       </c>
     </row>
     <row r="915">
@@ -56262,7 +56262,7 @@
         </is>
       </c>
       <c r="M915" s="2" t="n">
-        <v>5488.05</v>
+        <v>5466.87</v>
       </c>
     </row>
     <row r="916">
@@ -56323,7 +56323,7 @@
         </is>
       </c>
       <c r="M916" s="2" t="n">
-        <v>58566.07</v>
+        <v>58340.02</v>
       </c>
     </row>
     <row r="917">
@@ -56384,7 +56384,7 @@
         </is>
       </c>
       <c r="M917" s="2" t="n">
-        <v>2534.43</v>
+        <v>2524.64</v>
       </c>
     </row>
     <row r="918">
@@ -56445,7 +56445,7 @@
         </is>
       </c>
       <c r="M918" s="2" t="n">
-        <v>2863.89</v>
+        <v>2852.83</v>
       </c>
     </row>
     <row r="919">
@@ -56506,7 +56506,7 @@
         </is>
       </c>
       <c r="M919" s="2" t="n">
-        <v>6032.69</v>
+        <v>6009.41</v>
       </c>
     </row>
     <row r="920">
@@ -56567,7 +56567,7 @@
         </is>
       </c>
       <c r="M920" s="2" t="n">
-        <v>2929.22</v>
+        <v>2917.91</v>
       </c>
     </row>
     <row r="921">
@@ -56628,7 +56628,7 @@
         </is>
       </c>
       <c r="M921" s="2" t="n">
-        <v>36496.61</v>
+        <v>36355.74</v>
       </c>
     </row>
     <row r="922">
@@ -56689,7 +56689,7 @@
         </is>
       </c>
       <c r="M922" s="2" t="n">
-        <v>11160.36</v>
+        <v>11117.29</v>
       </c>
     </row>
     <row r="923">
@@ -56750,7 +56750,7 @@
         </is>
       </c>
       <c r="M923" s="2" t="n">
-        <v>11497.66</v>
+        <v>11453.28</v>
       </c>
     </row>
     <row r="924">
@@ -56811,7 +56811,7 @@
         </is>
       </c>
       <c r="M924" s="2" t="n">
-        <v>2490.21</v>
+        <v>2480.6</v>
       </c>
     </row>
     <row r="925">
@@ -56872,7 +56872,7 @@
         </is>
       </c>
       <c r="M925" s="2" t="n">
-        <v>4654.52</v>
+        <v>4636.55</v>
       </c>
     </row>
     <row r="926">
@@ -56933,7 +56933,7 @@
         </is>
       </c>
       <c r="M926" s="2" t="n">
-        <v>2303.05</v>
+        <v>2294.16</v>
       </c>
     </row>
     <row r="927">
@@ -56994,7 +56994,7 @@
         </is>
       </c>
       <c r="M927" s="2" t="n">
-        <v>2376.15</v>
+        <v>2366.98</v>
       </c>
     </row>
     <row r="928">
@@ -57055,7 +57055,7 @@
         </is>
       </c>
       <c r="M928" s="2" t="n">
-        <v>1683.5</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="929">
@@ -57116,7 +57116,7 @@
         </is>
       </c>
       <c r="M929" s="2" t="n">
-        <v>2293.09</v>
+        <v>2284.23</v>
       </c>
     </row>
     <row r="930">
@@ -57177,7 +57177,7 @@
         </is>
       </c>
       <c r="M930" s="2" t="n">
-        <v>4392.46</v>
+        <v>4375.51</v>
       </c>
     </row>
     <row r="931">
@@ -57238,7 +57238,7 @@
         </is>
       </c>
       <c r="M931" s="2" t="n">
-        <v>814.96</v>
+        <v>811.8200000000001</v>
       </c>
     </row>
     <row r="932">
@@ -57299,7 +57299,7 @@
         </is>
       </c>
       <c r="M932" s="2" t="n">
-        <v>7376.1</v>
+        <v>7347.64</v>
       </c>
     </row>
     <row r="933">
@@ -57360,7 +57360,7 @@
         </is>
       </c>
       <c r="M933" s="2" t="n">
-        <v>2700.28</v>
+        <v>2689.86</v>
       </c>
     </row>
     <row r="934">
@@ -57421,7 +57421,7 @@
         </is>
       </c>
       <c r="M934" s="2" t="n">
-        <v>3531.9</v>
+        <v>3518.27</v>
       </c>
     </row>
     <row r="935">
@@ -57482,7 +57482,7 @@
         </is>
       </c>
       <c r="M935" s="2" t="n">
-        <v>24451.24</v>
+        <v>24356.87</v>
       </c>
     </row>
     <row r="936">
@@ -57543,7 +57543,7 @@
         </is>
       </c>
       <c r="M936" s="2" t="n">
-        <v>1967.25</v>
+        <v>1977.44</v>
       </c>
     </row>
     <row r="937">
@@ -57604,7 +57604,7 @@
         </is>
       </c>
       <c r="M937" s="2" t="n">
-        <v>9831.4</v>
+        <v>9882.299999999999</v>
       </c>
     </row>
     <row r="938">
@@ -57665,7 +57665,7 @@
         </is>
       </c>
       <c r="M938" s="2" t="n">
-        <v>3744.45</v>
+        <v>3763.84</v>
       </c>
     </row>
     <row r="939">
@@ -57726,7 +57726,7 @@
         </is>
       </c>
       <c r="M939" s="2" t="n">
-        <v>2543.84</v>
+        <v>2557.01</v>
       </c>
     </row>
     <row r="940">
@@ -57787,7 +57787,7 @@
         </is>
       </c>
       <c r="M940" s="2" t="n">
-        <v>3285.21</v>
+        <v>3302.22</v>
       </c>
     </row>
     <row r="941">
@@ -57848,7 +57848,7 @@
         </is>
       </c>
       <c r="M941" s="2" t="n">
-        <v>6888.58</v>
+        <v>6924.25</v>
       </c>
     </row>
     <row r="942">
@@ -57909,7 +57909,7 @@
         </is>
       </c>
       <c r="M942" s="2" t="n">
-        <v>954.95</v>
+        <v>959.89</v>
       </c>
     </row>
     <row r="943">
@@ -57970,7 +57970,7 @@
         </is>
       </c>
       <c r="M943" s="2" t="n">
-        <v>836.86</v>
+        <v>841.1900000000001</v>
       </c>
     </row>
     <row r="944">
@@ -58031,7 +58031,7 @@
         </is>
       </c>
       <c r="M944" s="2" t="n">
-        <v>2650.52</v>
+        <v>2664.24</v>
       </c>
     </row>
     <row r="945">
@@ -58092,7 +58092,7 @@
         </is>
       </c>
       <c r="M945" s="2" t="n">
-        <v>3205.97</v>
+        <v>3222.56</v>
       </c>
     </row>
     <row r="946">
@@ -58153,7 +58153,7 @@
         </is>
       </c>
       <c r="M946" s="2" t="n">
-        <v>4517.13</v>
+        <v>4540.51</v>
       </c>
     </row>
     <row r="947">
@@ -58214,7 +58214,7 @@
         </is>
       </c>
       <c r="M947" s="2" t="n">
-        <v>1422.41</v>
+        <v>1429.78</v>
       </c>
     </row>
     <row r="948">
@@ -58275,7 +58275,7 @@
         </is>
       </c>
       <c r="M948" s="2" t="n">
-        <v>10019.53</v>
+        <v>10071.4</v>
       </c>
     </row>
     <row r="949">
@@ -58336,7 +58336,7 @@
         </is>
       </c>
       <c r="M949" s="2" t="n">
-        <v>2503.74</v>
+        <v>2516.7</v>
       </c>
     </row>
     <row r="950">
@@ -58397,7 +58397,7 @@
         </is>
       </c>
       <c r="M950" s="2" t="n">
-        <v>2160.53</v>
+        <v>2171.71</v>
       </c>
     </row>
     <row r="951">
@@ -58458,7 +58458,7 @@
         </is>
       </c>
       <c r="M951" s="2" t="n">
-        <v>1343.23</v>
+        <v>1350.19</v>
       </c>
     </row>
     <row r="952">
@@ -58519,7 +58519,7 @@
         </is>
       </c>
       <c r="M952" s="2" t="n">
-        <v>6752.78</v>
+        <v>6787.74</v>
       </c>
     </row>
     <row r="953">
@@ -58580,7 +58580,7 @@
         </is>
       </c>
       <c r="M953" s="2" t="n">
-        <v>2192.2</v>
+        <v>2203.55</v>
       </c>
     </row>
     <row r="954">
@@ -58641,7 +58641,7 @@
         </is>
       </c>
       <c r="M954" s="2" t="n">
-        <v>1210.44</v>
+        <v>1216.71</v>
       </c>
     </row>
     <row r="955">
@@ -58702,7 +58702,7 @@
         </is>
       </c>
       <c r="M955" s="2" t="n">
-        <v>22830.54</v>
+        <v>22948.74</v>
       </c>
     </row>
     <row r="956">
@@ -58763,7 +58763,7 @@
         </is>
       </c>
       <c r="M956" s="2" t="n">
-        <v>22228.33</v>
+        <v>22343.42</v>
       </c>
     </row>
     <row r="957">
@@ -58824,7 +58824,7 @@
         </is>
       </c>
       <c r="M957" s="2" t="n">
-        <v>22768.84</v>
+        <v>22886.72</v>
       </c>
     </row>
     <row r="958">
@@ -58885,7 +58885,7 @@
         </is>
       </c>
       <c r="M958" s="2" t="n">
-        <v>3441.83</v>
+        <v>3459.65</v>
       </c>
     </row>
     <row r="959">
@@ -58946,7 +58946,7 @@
         </is>
       </c>
       <c r="M959" s="2" t="n">
-        <v>912.66</v>
+        <v>917.39</v>
       </c>
     </row>
     <row r="960">
@@ -59007,7 +59007,7 @@
         </is>
       </c>
       <c r="M960" s="2" t="n">
-        <v>64027</v>
+        <v>64358.49</v>
       </c>
     </row>
     <row r="961">
@@ -59068,7 +59068,7 @@
         </is>
       </c>
       <c r="M961" s="2" t="n">
-        <v>7851.09</v>
+        <v>7891.74</v>
       </c>
     </row>
     <row r="962">
@@ -59129,7 +59129,7 @@
         </is>
       </c>
       <c r="M962" s="2" t="n">
-        <v>856.29</v>
+        <v>860.73</v>
       </c>
     </row>
     <row r="963">
@@ -59190,7 +59190,7 @@
         </is>
       </c>
       <c r="M963" s="2" t="n">
-        <v>28187.41</v>
+        <v>28333.35</v>
       </c>
     </row>
     <row r="964">
@@ -59251,7 +59251,7 @@
         </is>
       </c>
       <c r="M964" s="2" t="n">
-        <v>2589.08</v>
+        <v>2602.48</v>
       </c>
     </row>
     <row r="965">
@@ -59312,7 +59312,7 @@
         </is>
       </c>
       <c r="M965" s="2" t="n">
-        <v>1039.22</v>
+        <v>1044.6</v>
       </c>
     </row>
     <row r="966">
@@ -59373,7 +59373,7 @@
         </is>
       </c>
       <c r="M966" s="2" t="n">
-        <v>10764.28</v>
+        <v>10820.01</v>
       </c>
     </row>
     <row r="967">
@@ -59434,7 +59434,7 @@
         </is>
       </c>
       <c r="M967" s="2" t="n">
-        <v>2640.77</v>
+        <v>2654.44</v>
       </c>
     </row>
     <row r="968">
@@ -59495,7 +59495,7 @@
         </is>
       </c>
       <c r="M968" s="2" t="n">
-        <v>3718.4</v>
+        <v>3737.65</v>
       </c>
     </row>
     <row r="969">
@@ -59556,7 +59556,7 @@
         </is>
       </c>
       <c r="M969" s="2" t="n">
-        <v>8405.469999999999</v>
+        <v>8448.99</v>
       </c>
     </row>
     <row r="970">
@@ -59617,7 +59617,7 @@
         </is>
       </c>
       <c r="M970" s="2" t="n">
-        <v>1020.4</v>
+        <v>1025.68</v>
       </c>
     </row>
     <row r="971">
@@ -59678,7 +59678,7 @@
         </is>
       </c>
       <c r="M971" s="2" t="n">
-        <v>2999.06</v>
+        <v>3014.59</v>
       </c>
     </row>
     <row r="972">
@@ -59739,7 +59739,7 @@
         </is>
       </c>
       <c r="M972" s="2" t="n">
-        <v>870.65</v>
+        <v>875.16</v>
       </c>
     </row>
     <row r="973">
@@ -59800,7 +59800,7 @@
         </is>
       </c>
       <c r="M973" s="2" t="n">
-        <v>4794.11</v>
+        <v>4818.93</v>
       </c>
     </row>
     <row r="974">
@@ -59861,7 +59861,7 @@
         </is>
       </c>
       <c r="M974" s="2" t="n">
-        <v>3439.54</v>
+        <v>3457.35</v>
       </c>
     </row>
     <row r="975">
@@ -59922,7 +59922,7 @@
         </is>
       </c>
       <c r="M975" s="2" t="n">
-        <v>7561.28</v>
+        <v>7600.43</v>
       </c>
     </row>
     <row r="976">
@@ -59983,7 +59983,7 @@
         </is>
       </c>
       <c r="M976" s="2" t="n">
-        <v>10391.29</v>
+        <v>10445.09</v>
       </c>
     </row>
     <row r="977">
@@ -60044,7 +60044,7 @@
         </is>
       </c>
       <c r="M977" s="2" t="n">
-        <v>11320.61</v>
+        <v>11379.22</v>
       </c>
     </row>
     <row r="978">
@@ -60105,7 +60105,7 @@
         </is>
       </c>
       <c r="M978" s="2" t="n">
-        <v>8006.22</v>
+        <v>8047.67</v>
       </c>
     </row>
     <row r="979">
@@ -60166,7 +60166,7 @@
         </is>
       </c>
       <c r="M979" s="2" t="n">
-        <v>9926.92</v>
+        <v>9978.32</v>
       </c>
     </row>
     <row r="980">
@@ -60227,7 +60227,7 @@
         </is>
       </c>
       <c r="M980" s="2" t="n">
-        <v>807.95</v>
+        <v>808.73</v>
       </c>
     </row>
     <row r="981">
@@ -60288,7 +60288,7 @@
         </is>
       </c>
       <c r="M981" s="2" t="n">
-        <v>5643.41</v>
+        <v>5648.85</v>
       </c>
     </row>
     <row r="982">
@@ -60349,7 +60349,7 @@
         </is>
       </c>
       <c r="M982" s="2" t="n">
-        <v>71260.3</v>
+        <v>71328.98</v>
       </c>
     </row>
     <row r="983">
@@ -60410,7 +60410,7 @@
         </is>
       </c>
       <c r="M983" s="2" t="n">
-        <v>2127.64</v>
+        <v>2129.69</v>
       </c>
     </row>
     <row r="984">
@@ -60471,7 +60471,7 @@
         </is>
       </c>
       <c r="M984" s="2" t="n">
-        <v>3563.79</v>
+        <v>3567.23</v>
       </c>
     </row>
     <row r="985">
@@ -60532,7 +60532,7 @@
         </is>
       </c>
       <c r="M985" s="2" t="n">
-        <v>18172.2</v>
+        <v>18189.72</v>
       </c>
     </row>
     <row r="986">
@@ -60593,7 +60593,7 @@
         </is>
       </c>
       <c r="M986" s="2" t="n">
-        <v>3795.35</v>
+        <v>3799.01</v>
       </c>
     </row>
     <row r="987">
@@ -60654,7 +60654,7 @@
         </is>
       </c>
       <c r="M987" s="2" t="n">
-        <v>18367.96</v>
+        <v>18385.66</v>
       </c>
     </row>
     <row r="988">
@@ -60715,7 +60715,7 @@
         </is>
       </c>
       <c r="M988" s="2" t="n">
-        <v>2415.16</v>
+        <v>2417.49</v>
       </c>
     </row>
     <row r="989">
@@ -60776,7 +60776,7 @@
         </is>
       </c>
       <c r="M989" s="2" t="n">
-        <v>6709.13</v>
+        <v>6715.59</v>
       </c>
     </row>
     <row r="990">
@@ -60837,7 +60837,7 @@
         </is>
       </c>
       <c r="M990" s="2" t="n">
-        <v>5090.82</v>
+        <v>5095.73</v>
       </c>
     </row>
     <row r="991">
@@ -60898,7 +60898,7 @@
         </is>
       </c>
       <c r="M991" s="2" t="n">
-        <v>1521.4</v>
+        <v>1522.86</v>
       </c>
     </row>
     <row r="992">
@@ -60959,7 +60959,7 @@
         </is>
       </c>
       <c r="M992" s="2" t="n">
-        <v>2111.39</v>
+        <v>2113.42</v>
       </c>
     </row>
     <row r="993">
@@ -61020,7 +61020,7 @@
         </is>
       </c>
       <c r="M993" s="2" t="n">
-        <v>12169.61</v>
+        <v>12181.34</v>
       </c>
     </row>
     <row r="994">
@@ -61081,7 +61081,7 @@
         </is>
       </c>
       <c r="M994" s="2" t="n">
-        <v>2320.32</v>
+        <v>2322.56</v>
       </c>
     </row>
     <row r="995">
@@ -61142,7 +61142,7 @@
         </is>
       </c>
       <c r="M995" s="2" t="n">
-        <v>1502.91</v>
+        <v>1504.35</v>
       </c>
     </row>
     <row r="996">
@@ -61203,7 +61203,7 @@
         </is>
       </c>
       <c r="M996" s="2" t="n">
-        <v>2088.38</v>
+        <v>2090.39</v>
       </c>
     </row>
     <row r="997">
@@ -61264,7 +61264,7 @@
         </is>
       </c>
       <c r="M997" s="2" t="n">
-        <v>8057.51</v>
+        <v>8065.27</v>
       </c>
     </row>
     <row r="998">
@@ -61325,7 +61325,7 @@
         </is>
       </c>
       <c r="M998" s="2" t="n">
-        <v>2783.32</v>
+        <v>2786</v>
       </c>
     </row>
     <row r="999">
@@ -61386,7 +61386,7 @@
         </is>
       </c>
       <c r="M999" s="2" t="n">
-        <v>4639.19</v>
+        <v>4643.66</v>
       </c>
     </row>
     <row r="1000">
@@ -61447,7 +61447,7 @@
         </is>
       </c>
       <c r="M1000" s="2" t="n">
-        <v>11111.13</v>
+        <v>11121.83</v>
       </c>
     </row>
     <row r="1001">
@@ -61508,7 +61508,7 @@
         </is>
       </c>
       <c r="M1001" s="2" t="n">
-        <v>14188.56</v>
+        <v>14202.23</v>
       </c>
     </row>
     <row r="1002">
@@ -61569,7 +61569,7 @@
         </is>
       </c>
       <c r="M1002" s="2" t="n">
-        <v>15301.14</v>
+        <v>15315.89</v>
       </c>
     </row>
     <row r="1003">
@@ -61630,7 +61630,7 @@
         </is>
       </c>
       <c r="M1003" s="2" t="n">
-        <v>12526.94</v>
+        <v>12539.01</v>
       </c>
     </row>
     <row r="1004">
@@ -61691,7 +61691,7 @@
         </is>
       </c>
       <c r="M1004" s="2" t="n">
-        <v>4201.11</v>
+        <v>4205.16</v>
       </c>
     </row>
     <row r="1005">
@@ -61752,7 +61752,7 @@
         </is>
       </c>
       <c r="M1005" s="2" t="n">
-        <v>9801.4</v>
+        <v>9810.84</v>
       </c>
     </row>
     <row r="1006">
@@ -61813,7 +61813,7 @@
         </is>
       </c>
       <c r="M1006" s="2" t="n">
-        <v>11350.74</v>
+        <v>11361.68</v>
       </c>
     </row>
     <row r="1007">
@@ -61874,7 +61874,7 @@
         </is>
       </c>
       <c r="M1007" s="2" t="n">
-        <v>20003.13</v>
+        <v>20022.41</v>
       </c>
     </row>
     <row r="1008">
@@ -61935,7 +61935,7 @@
         </is>
       </c>
       <c r="M1008" s="2" t="n">
-        <v>2565.23</v>
+        <v>2567.7</v>
       </c>
     </row>
     <row r="1009">
@@ -61996,7 +61996,7 @@
         </is>
       </c>
       <c r="M1009" s="2" t="n">
-        <v>6331.8</v>
+        <v>6337.9</v>
       </c>
     </row>
     <row r="1010">
@@ -62057,7 +62057,7 @@
         </is>
       </c>
       <c r="M1010" s="2" t="n">
-        <v>11599.71</v>
+        <v>11610.89</v>
       </c>
     </row>
     <row r="1011">
@@ -62118,7 +62118,7 @@
         </is>
       </c>
       <c r="M1011" s="2" t="n">
-        <v>1867.51</v>
+        <v>1869.31</v>
       </c>
     </row>
     <row r="1012">
@@ -62179,7 +62179,7 @@
         </is>
       </c>
       <c r="M1012" s="2" t="n">
-        <v>9934.25</v>
+        <v>9943.83</v>
       </c>
     </row>
     <row r="1013">
@@ -62240,7 +62240,7 @@
         </is>
       </c>
       <c r="M1013" s="2" t="n">
-        <v>1554.5</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="1014">
@@ -62301,7 +62301,7 @@
         </is>
       </c>
       <c r="M1014" s="2" t="n">
-        <v>34547.69</v>
+        <v>34580.98</v>
       </c>
     </row>
     <row r="1015">
@@ -62362,7 +62362,7 @@
         </is>
       </c>
       <c r="M1015" s="2" t="n">
-        <v>8069.24</v>
+        <v>8077.02</v>
       </c>
     </row>
     <row r="1016">
@@ -62423,7 +62423,7 @@
         </is>
       </c>
       <c r="M1016" s="2" t="n">
-        <v>4803.1</v>
+        <v>4807.73</v>
       </c>
     </row>
     <row r="1017">
@@ -62484,7 +62484,7 @@
         </is>
       </c>
       <c r="M1017" s="2" t="n">
-        <v>809.84</v>
+        <v>810.62</v>
       </c>
     </row>
     <row r="1018">
@@ -62545,7 +62545,7 @@
         </is>
       </c>
       <c r="M1018" s="2" t="n">
-        <v>2585.91</v>
+        <v>2588.4</v>
       </c>
     </row>
     <row r="1019">
@@ -62606,7 +62606,7 @@
         </is>
       </c>
       <c r="M1019" s="2" t="n">
-        <v>11043.71</v>
+        <v>11054.35</v>
       </c>
     </row>
     <row r="1020">
@@ -62667,7 +62667,7 @@
         </is>
       </c>
       <c r="M1020" s="2" t="n">
-        <v>65758.33</v>
+        <v>65821.71000000001</v>
       </c>
     </row>
     <row r="1021">
@@ -62728,7 +62728,7 @@
         </is>
       </c>
       <c r="M1021" s="2" t="n">
-        <v>46138.81</v>
+        <v>46183.28</v>
       </c>
     </row>
     <row r="1022">
@@ -62789,7 +62789,7 @@
         </is>
       </c>
       <c r="M1022" s="2" t="n">
-        <v>5198.86</v>
+        <v>5203.87</v>
       </c>
     </row>
     <row r="1023">
@@ -62850,7 +62850,7 @@
         </is>
       </c>
       <c r="M1023" s="2" t="n">
-        <v>18869.7</v>
+        <v>18887.89</v>
       </c>
     </row>
     <row r="1024">
@@ -62911,7 +62911,7 @@
         </is>
       </c>
       <c r="M1024" s="2" t="n">
-        <v>4086.33</v>
+        <v>4090.27</v>
       </c>
     </row>
     <row r="1025">
@@ -62972,7 +62972,7 @@
         </is>
       </c>
       <c r="M1025" s="2" t="n">
-        <v>5786.58</v>
+        <v>5792.16</v>
       </c>
     </row>
     <row r="1026">
@@ -63033,7 +63033,7 @@
         </is>
       </c>
       <c r="M1026" s="2" t="n">
-        <v>1717.96</v>
+        <v>1719.62</v>
       </c>
     </row>
     <row r="1027">
@@ -63094,7 +63094,7 @@
         </is>
       </c>
       <c r="M1027" s="2" t="n">
-        <v>1803.57</v>
+        <v>1805.31</v>
       </c>
     </row>
     <row r="1028">
@@ -63155,7 +63155,7 @@
         </is>
       </c>
       <c r="M1028" s="2" t="n">
-        <v>10587.31</v>
+        <v>10597.51</v>
       </c>
     </row>
     <row r="1029">
@@ -63216,7 +63216,7 @@
         </is>
       </c>
       <c r="M1029" s="2" t="n">
-        <v>15131.49</v>
+        <v>15146.08</v>
       </c>
     </row>
     <row r="1030">
@@ -63277,7 +63277,7 @@
         </is>
       </c>
       <c r="M1030" s="2" t="n">
-        <v>10799.29</v>
+        <v>10809.7</v>
       </c>
     </row>
     <row r="1031">
@@ -63338,7 +63338,7 @@
         </is>
       </c>
       <c r="M1031" s="2" t="n">
-        <v>6620.18</v>
+        <v>6626.56</v>
       </c>
     </row>
     <row r="1032">
@@ -63399,7 +63399,7 @@
         </is>
       </c>
       <c r="M1032" s="2" t="n">
-        <v>817.4299999999999</v>
+        <v>818.22</v>
       </c>
     </row>
     <row r="1033">
@@ -63460,7 +63460,7 @@
         </is>
       </c>
       <c r="M1033" s="2" t="n">
-        <v>1919.12</v>
+        <v>1920.97</v>
       </c>
     </row>
     <row r="1034">
@@ -63521,7 +63521,7 @@
         </is>
       </c>
       <c r="M1034" s="2" t="n">
-        <v>1693.36</v>
+        <v>1694.99</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-mensuales/articulos-de-aseo-e-higiene/feb-2026.xlsx
+++ b/docs/oc-mensuales/articulos-de-aseo-e-higiene/feb-2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC feb-2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC feb-2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -671,7 +671,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -3233,7 +3233,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3477,7 +3477,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3782,7 +3782,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -4575,7 +4575,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -4697,7 +4697,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -4758,7 +4758,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -5307,7 +5307,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -5551,7 +5551,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -6039,7 +6039,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -6405,7 +6405,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -7564,7 +7564,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -8235,7 +8235,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -8479,7 +8479,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -10919,7 +10919,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -12078,7 +12078,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -12505,7 +12505,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -12810,7 +12810,7 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -12993,7 +12993,7 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -13054,7 +13054,7 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -13664,7 +13664,7 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
@@ -14579,7 +14579,7 @@
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
@@ -15555,7 +15555,7 @@
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
@@ -16043,7 +16043,7 @@
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
@@ -16897,7 +16897,7 @@
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
@@ -16958,7 +16958,7 @@
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
@@ -18056,7 +18056,7 @@
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
@@ -18300,7 +18300,7 @@
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
@@ -18666,7 +18666,7 @@
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I299" t="inlineStr">
@@ -18910,7 +18910,7 @@
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I303" t="inlineStr">
@@ -19093,7 +19093,7 @@
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I306" t="inlineStr">
@@ -19520,7 +19520,7 @@
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I313" t="inlineStr">
@@ -19703,7 +19703,7 @@
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I316" t="inlineStr">
@@ -19764,7 +19764,7 @@
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I317" t="inlineStr">
@@ -19825,7 +19825,7 @@
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I318" t="inlineStr">
@@ -20008,7 +20008,7 @@
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I321" t="inlineStr">
@@ -21106,7 +21106,7 @@
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I339" t="inlineStr">
@@ -22204,7 +22204,7 @@
       </c>
       <c r="H357" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I357" t="inlineStr">
@@ -22387,7 +22387,7 @@
       </c>
       <c r="H360" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I360" t="inlineStr">
@@ -22509,7 +22509,7 @@
       </c>
       <c r="H362" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I362" t="inlineStr">
@@ -22692,7 +22692,7 @@
       </c>
       <c r="H365" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I365" t="inlineStr">
@@ -22875,7 +22875,7 @@
       </c>
       <c r="H368" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I368" t="inlineStr">
@@ -22936,7 +22936,7 @@
       </c>
       <c r="H369" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I369" t="inlineStr">
@@ -23058,7 +23058,7 @@
       </c>
       <c r="H371" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I371" t="inlineStr">
@@ -23180,7 +23180,7 @@
       </c>
       <c r="H373" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I373" t="inlineStr">
@@ -23607,7 +23607,7 @@
       </c>
       <c r="H380" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I380" t="inlineStr">
@@ -24583,7 +24583,7 @@
       </c>
       <c r="H396" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I396" t="inlineStr">
@@ -25010,7 +25010,7 @@
       </c>
       <c r="H403" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I403" t="inlineStr">
@@ -25315,7 +25315,7 @@
       </c>
       <c r="H408" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I408" t="inlineStr">
@@ -26535,7 +26535,7 @@
       </c>
       <c r="H428" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I428" t="inlineStr">
@@ -26718,7 +26718,7 @@
       </c>
       <c r="H431" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I431" t="inlineStr">
@@ -27084,7 +27084,7 @@
       </c>
       <c r="H437" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I437" t="inlineStr">
@@ -27145,7 +27145,7 @@
       </c>
       <c r="H438" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I438" t="inlineStr">
@@ -27206,7 +27206,7 @@
       </c>
       <c r="H439" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I439" t="inlineStr">
@@ -27389,7 +27389,7 @@
       </c>
       <c r="H442" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I442" t="inlineStr">
@@ -27938,7 +27938,7 @@
       </c>
       <c r="H451" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I451" t="inlineStr">
@@ -28670,7 +28670,7 @@
       </c>
       <c r="H463" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I463" t="inlineStr">
@@ -29341,7 +29341,7 @@
       </c>
       <c r="H474" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I474" t="inlineStr">
@@ -29402,7 +29402,7 @@
       </c>
       <c r="H475" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I475" t="inlineStr">
@@ -29707,7 +29707,7 @@
       </c>
       <c r="H480" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I480" t="inlineStr">
@@ -31964,7 +31964,7 @@
       </c>
       <c r="H517" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I517" t="inlineStr">
@@ -32330,7 +32330,7 @@
       </c>
       <c r="H523" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I523" t="inlineStr">
@@ -33123,7 +33123,7 @@
       </c>
       <c r="H536" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I536" t="inlineStr">
@@ -33611,7 +33611,7 @@
       </c>
       <c r="H544" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I544" t="inlineStr">
@@ -33977,7 +33977,7 @@
       </c>
       <c r="H550" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I550" t="inlineStr">
@@ -34099,7 +34099,7 @@
       </c>
       <c r="H552" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I552" t="inlineStr">
@@ -34160,7 +34160,7 @@
       </c>
       <c r="H553" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I553" t="inlineStr">
@@ -34221,7 +34221,7 @@
       </c>
       <c r="H554" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I554" t="inlineStr">
@@ -34465,7 +34465,7 @@
       </c>
       <c r="H558" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I558" t="inlineStr">
@@ -34709,7 +34709,7 @@
       </c>
       <c r="H562" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I562" t="inlineStr">
@@ -35014,7 +35014,7 @@
       </c>
       <c r="H567" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I567" t="inlineStr">
@@ -35136,7 +35136,7 @@
       </c>
       <c r="H569" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I569" t="inlineStr">
@@ -35624,7 +35624,7 @@
       </c>
       <c r="H577" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I577" t="inlineStr">
@@ -36722,7 +36722,7 @@
       </c>
       <c r="H595" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I595" t="inlineStr">
@@ -37210,7 +37210,7 @@
       </c>
       <c r="H603" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I603" t="inlineStr">
@@ -37576,7 +37576,7 @@
       </c>
       <c r="H609" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I609" t="inlineStr">
@@ -37637,7 +37637,7 @@
       </c>
       <c r="H610" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I610" t="inlineStr">
@@ -37698,7 +37698,7 @@
       </c>
       <c r="H611" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I611" t="inlineStr">
@@ -38003,7 +38003,7 @@
       </c>
       <c r="H616" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I616" t="inlineStr">
@@ -38979,7 +38979,7 @@
       </c>
       <c r="H632" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I632" t="inlineStr">
@@ -39162,7 +39162,7 @@
       </c>
       <c r="H635" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I635" t="inlineStr">
@@ -39467,7 +39467,7 @@
       </c>
       <c r="H640" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I640" t="inlineStr">
@@ -39650,7 +39650,7 @@
       </c>
       <c r="H643" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I643" t="inlineStr">
@@ -39711,7 +39711,7 @@
       </c>
       <c r="H644" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I644" t="inlineStr">
@@ -41419,7 +41419,7 @@
       </c>
       <c r="H672" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I672" t="inlineStr">
@@ -41846,7 +41846,7 @@
       </c>
       <c r="H679" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I679" t="inlineStr">
@@ -41968,7 +41968,7 @@
       </c>
       <c r="H681" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I681" t="inlineStr">
@@ -42334,7 +42334,7 @@
       </c>
       <c r="H687" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I687" t="inlineStr">
@@ -42517,7 +42517,7 @@
       </c>
       <c r="H690" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I690" t="inlineStr">
@@ -42578,7 +42578,7 @@
       </c>
       <c r="H691" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I691" t="inlineStr">
@@ -42639,7 +42639,7 @@
       </c>
       <c r="H692" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I692" t="inlineStr">
@@ -42700,7 +42700,7 @@
       </c>
       <c r="H693" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I693" t="inlineStr">
@@ -42822,7 +42822,7 @@
       </c>
       <c r="H695" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I695" t="inlineStr">
@@ -43615,7 +43615,7 @@
       </c>
       <c r="H708" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I708" t="inlineStr">
@@ -44530,7 +44530,7 @@
       </c>
       <c r="H723" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I723" t="inlineStr">
@@ -44957,7 +44957,7 @@
       </c>
       <c r="H730" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I730" t="inlineStr">
@@ -46665,7 +46665,7 @@
       </c>
       <c r="H758" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I758" t="inlineStr">
@@ -47031,7 +47031,7 @@
       </c>
       <c r="H764" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I764" t="inlineStr">
@@ -47275,7 +47275,7 @@
       </c>
       <c r="H768" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I768" t="inlineStr">
@@ -47519,7 +47519,7 @@
       </c>
       <c r="H772" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I772" t="inlineStr">
@@ -47641,7 +47641,7 @@
       </c>
       <c r="H774" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I774" t="inlineStr">
@@ -47702,7 +47702,7 @@
       </c>
       <c r="H775" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I775" t="inlineStr">
@@ -48007,7 +48007,7 @@
       </c>
       <c r="H780" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I780" t="inlineStr">
@@ -48190,7 +48190,7 @@
       </c>
       <c r="H783" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I783" t="inlineStr">
@@ -48312,7 +48312,7 @@
       </c>
       <c r="H785" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I785" t="inlineStr">
@@ -48373,7 +48373,7 @@
       </c>
       <c r="H786" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I786" t="inlineStr">
@@ -48495,7 +48495,7 @@
       </c>
       <c r="H788" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I788" t="inlineStr">
@@ -48617,7 +48617,7 @@
       </c>
       <c r="H790" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I790" t="inlineStr">
@@ -48739,7 +48739,7 @@
       </c>
       <c r="H792" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I792" t="inlineStr">
@@ -49044,7 +49044,7 @@
       </c>
       <c r="H797" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I797" t="inlineStr">
@@ -49166,7 +49166,7 @@
       </c>
       <c r="H799" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I799" t="inlineStr">
@@ -50142,7 +50142,7 @@
       </c>
       <c r="H815" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I815" t="inlineStr">
@@ -50508,7 +50508,7 @@
       </c>
       <c r="H821" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I821" t="inlineStr">
@@ -50691,7 +50691,7 @@
       </c>
       <c r="H824" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I824" t="inlineStr">
@@ -51301,7 +51301,7 @@
       </c>
       <c r="H834" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I834" t="inlineStr">
@@ -51545,7 +51545,7 @@
       </c>
       <c r="H838" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I838" t="inlineStr">
@@ -51606,7 +51606,7 @@
       </c>
       <c r="H839" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I839" t="inlineStr">
@@ -51728,7 +51728,7 @@
       </c>
       <c r="H841" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I841" t="inlineStr">
@@ -51850,7 +51850,7 @@
       </c>
       <c r="H843" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I843" t="inlineStr">
@@ -51972,7 +51972,7 @@
       </c>
       <c r="H845" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I845" t="inlineStr">
@@ -52094,7 +52094,7 @@
       </c>
       <c r="H847" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I847" t="inlineStr">
@@ -52155,7 +52155,7 @@
       </c>
       <c r="H848" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I848" t="inlineStr">
@@ -52216,7 +52216,7 @@
       </c>
       <c r="H849" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I849" t="inlineStr">
@@ -52338,7 +52338,7 @@
       </c>
       <c r="H851" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I851" t="inlineStr">
@@ -52399,7 +52399,7 @@
       </c>
       <c r="H852" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I852" t="inlineStr">
@@ -52826,7 +52826,7 @@
       </c>
       <c r="H859" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I859" t="inlineStr">
@@ -52887,7 +52887,7 @@
       </c>
       <c r="H860" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I860" t="inlineStr">
@@ -52948,7 +52948,7 @@
       </c>
       <c r="H861" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I861" t="inlineStr">
@@ -53070,7 +53070,7 @@
       </c>
       <c r="H863" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I863" t="inlineStr">
@@ -53436,7 +53436,7 @@
       </c>
       <c r="H869" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I869" t="inlineStr">
@@ -53619,7 +53619,7 @@
       </c>
       <c r="H872" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I872" t="inlineStr">
@@ -54473,7 +54473,7 @@
       </c>
       <c r="H886" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I886" t="inlineStr">
@@ -54534,7 +54534,7 @@
       </c>
       <c r="H887" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I887" t="inlineStr">
@@ -55876,7 +55876,7 @@
       </c>
       <c r="H909" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I909" t="inlineStr">
@@ -56303,7 +56303,7 @@
       </c>
       <c r="H916" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I916" t="inlineStr">
@@ -56364,7 +56364,7 @@
       </c>
       <c r="H917" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I917" t="inlineStr">
@@ -56425,7 +56425,7 @@
       </c>
       <c r="H918" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I918" t="inlineStr">
@@ -56547,7 +56547,7 @@
       </c>
       <c r="H920" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I920" t="inlineStr">
@@ -56730,7 +56730,7 @@
       </c>
       <c r="H923" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I923" t="inlineStr">
@@ -56852,7 +56852,7 @@
       </c>
       <c r="H925" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I925" t="inlineStr">
@@ -57035,7 +57035,7 @@
       </c>
       <c r="H928" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I928" t="inlineStr">
@@ -57096,7 +57096,7 @@
       </c>
       <c r="H929" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I929" t="inlineStr">
@@ -57218,7 +57218,7 @@
       </c>
       <c r="H931" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I931" t="inlineStr">
@@ -57279,7 +57279,7 @@
       </c>
       <c r="H932" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I932" t="inlineStr">
@@ -57401,7 +57401,7 @@
       </c>
       <c r="H934" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I934" t="inlineStr">
@@ -57706,7 +57706,7 @@
       </c>
       <c r="H939" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I939" t="inlineStr">
@@ -58011,7 +58011,7 @@
       </c>
       <c r="H944" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I944" t="inlineStr">
@@ -58072,7 +58072,7 @@
       </c>
       <c r="H945" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I945" t="inlineStr">
@@ -58133,7 +58133,7 @@
       </c>
       <c r="H946" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I946" t="inlineStr">
@@ -58987,7 +58987,7 @@
       </c>
       <c r="H960" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I960" t="inlineStr">
@@ -59109,7 +59109,7 @@
       </c>
       <c r="H962" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I962" t="inlineStr">
@@ -59353,7 +59353,7 @@
       </c>
       <c r="H966" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I966" t="inlineStr">
@@ -59658,7 +59658,7 @@
       </c>
       <c r="H971" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I971" t="inlineStr">
@@ -59780,7 +59780,7 @@
       </c>
       <c r="H973" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I973" t="inlineStr">
@@ -60207,7 +60207,7 @@
       </c>
       <c r="H980" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I980" t="inlineStr">
@@ -61549,7 +61549,7 @@
       </c>
       <c r="H1002" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I1002" t="inlineStr">
@@ -61610,7 +61610,7 @@
       </c>
       <c r="H1003" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I1003" t="inlineStr">
@@ -61854,7 +61854,7 @@
       </c>
       <c r="H1007" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I1007" t="inlineStr">
@@ -62159,7 +62159,7 @@
       </c>
       <c r="H1012" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I1012" t="inlineStr">
@@ -63135,7 +63135,7 @@
       </c>
       <c r="H1028" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I1028" t="inlineStr">
@@ -63318,7 +63318,7 @@
       </c>
       <c r="H1031" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I1031" t="inlineStr">

--- a/docs/oc-mensuales/articulos-de-aseo-e-higiene/feb-2026.xlsx
+++ b/docs/oc-mensuales/articulos-de-aseo-e-higiene/feb-2026.xlsx
@@ -684,7 +684,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +871,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +936,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1001,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1066,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1131,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1318,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1444,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1631,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1879,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1904,7 +1944,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2070,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2087,7 +2135,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2200,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2209,7 +2265,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2270,7 +2330,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2392,7 +2456,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2453,7 +2521,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2514,7 +2586,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2575,7 +2651,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2697,7 +2777,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2758,7 +2842,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2819,7 +2907,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2880,7 +2972,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3002,7 +3098,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3185,7 +3285,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3368,7 +3472,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3429,7 +3537,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3490,7 +3602,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3551,7 +3667,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3612,7 +3732,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3673,7 +3797,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3734,7 +3862,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3795,7 +3927,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3978,7 +4114,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4039,7 +4179,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4100,7 +4244,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4222,7 +4370,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4283,7 +4435,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4344,7 +4500,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4527,7 +4687,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4588,7 +4752,11 @@
           <t>76.817.360-5</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4710,7 +4878,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4771,7 +4943,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4893,7 +5069,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4954,7 +5134,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5015,7 +5199,11 @@
           <t>77.404.653-4</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5076,7 +5264,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5137,7 +5329,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5198,7 +5394,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5259,7 +5459,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5381,7 +5585,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5442,7 +5650,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5564,7 +5776,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5625,7 +5841,11 @@
           <t>78.061.716-0</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5747,7 +5967,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5869,7 +6093,11 @@
           <t>78.061.716-0</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6052,7 +6280,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6113,7 +6345,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6174,7 +6410,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6296,7 +6536,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6479,7 +6723,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6601,7 +6849,11 @@
           <t>78.057.703-7</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L101" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6723,7 +6975,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L103" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6784,7 +7040,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L104" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6845,7 +7105,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L105" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6967,7 +7231,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L107" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7028,7 +7296,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L108" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7150,7 +7422,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7211,7 +7487,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L111" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7272,7 +7552,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L112" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7516,7 +7800,11 @@
           <t>78.057.703-7</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L116" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7577,7 +7865,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L117" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7699,7 +7991,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L119" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7760,7 +8056,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L120" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7821,7 +8121,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L121" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7882,7 +8186,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L122" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7943,7 +8251,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L123" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8065,7 +8377,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L125" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8187,7 +8503,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8309,7 +8629,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L129" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8370,7 +8694,11 @@
           <t>78.209.481-5</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L130" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8431,7 +8759,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L131" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8492,7 +8824,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L132" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8553,7 +8889,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L133" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8614,7 +8954,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L134" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8675,7 +9019,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L135" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8736,7 +9084,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr"/>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L136" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8797,7 +9149,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L137" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8858,7 +9214,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr"/>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L138" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8919,7 +9279,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L139" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9041,7 +9405,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L141" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9102,7 +9470,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr"/>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L142" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9224,7 +9596,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr"/>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L144" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9285,7 +9661,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr"/>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L145" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9407,7 +9787,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr"/>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L147" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9468,7 +9852,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L148" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9590,7 +9978,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L150" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9651,7 +10043,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L151" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9712,7 +10108,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L152" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9895,7 +10295,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L155" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10017,7 +10421,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr"/>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L157" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10078,7 +10486,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr"/>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L158" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10139,7 +10551,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr"/>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L159" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10261,7 +10677,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr"/>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L161" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10322,7 +10742,11 @@
           <t>78.061.716-0</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr"/>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L162" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10383,7 +10807,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr"/>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L163" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10444,7 +10872,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr"/>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L164" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10505,7 +10937,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr"/>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L165" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10566,7 +11002,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr"/>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L166" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10627,7 +11067,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr"/>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L167" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10688,7 +11132,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr"/>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L168" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10810,7 +11258,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L170" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10932,7 +11384,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr"/>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L172" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11054,7 +11510,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr"/>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L174" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11115,7 +11575,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr"/>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L175" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11359,7 +11823,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr"/>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L179" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11420,7 +11888,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr"/>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L180" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11481,7 +11953,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr"/>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L181" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11542,7 +12018,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr"/>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L182" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11603,7 +12083,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr"/>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L183" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11664,7 +12148,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr"/>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L184" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11725,7 +12213,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr"/>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L185" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11786,7 +12278,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K186" t="inlineStr"/>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L186" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11847,7 +12343,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr"/>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L187" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11908,7 +12408,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr"/>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L188" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12030,7 +12534,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr"/>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L190" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12091,7 +12599,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr"/>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L191" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12152,7 +12664,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr"/>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L192" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12274,7 +12790,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K194" t="inlineStr"/>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L194" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12396,7 +12916,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr"/>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L196" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12457,7 +12981,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr"/>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L197" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12518,7 +13046,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr"/>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L198" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12701,7 +13233,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr"/>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L201" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12762,7 +13298,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr"/>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L202" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12823,7 +13363,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr"/>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L203" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12884,7 +13428,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr"/>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L204" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12945,7 +13493,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr"/>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L205" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13006,7 +13558,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K206" t="inlineStr"/>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L206" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13067,7 +13623,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr"/>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L207" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13128,7 +13688,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr"/>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L208" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13189,7 +13753,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr"/>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L209" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13311,7 +13879,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr"/>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L211" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13372,7 +13944,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K212" t="inlineStr"/>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L212" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13433,7 +14009,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr"/>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L213" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13494,7 +14074,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K214" t="inlineStr"/>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L214" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13677,7 +14261,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K217" t="inlineStr"/>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L217" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13738,7 +14326,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr"/>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L218" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13799,7 +14391,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K219" t="inlineStr"/>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L219" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13860,7 +14456,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K220" t="inlineStr"/>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L220" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14043,7 +14643,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K223" t="inlineStr"/>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L223" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14104,7 +14708,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K224" t="inlineStr"/>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L224" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14165,7 +14773,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K225" t="inlineStr"/>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L225" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14287,7 +14899,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K227" t="inlineStr"/>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L227" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14348,7 +14964,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K228" t="inlineStr"/>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L228" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14592,7 +15212,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K232" t="inlineStr"/>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L232" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14653,7 +15277,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K233" t="inlineStr"/>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L233" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14775,7 +15403,11 @@
           <t>78.209.481-5</t>
         </is>
       </c>
-      <c r="K235" t="inlineStr"/>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L235" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14897,7 +15529,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K237" t="inlineStr"/>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L237" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14958,7 +15594,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K238" t="inlineStr"/>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L238" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15019,7 +15659,11 @@
           <t>77.922.408-2</t>
         </is>
       </c>
-      <c r="K239" t="inlineStr"/>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L239" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15080,7 +15724,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K240" t="inlineStr"/>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L240" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15141,7 +15789,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K241" t="inlineStr"/>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L241" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15202,7 +15854,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K242" t="inlineStr"/>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L242" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15263,7 +15919,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K243" t="inlineStr"/>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L243" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15385,7 +16045,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K245" t="inlineStr"/>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L245" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15568,7 +16232,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K248" t="inlineStr"/>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L248" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15629,7 +16297,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K249" t="inlineStr"/>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L249" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15690,7 +16362,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K250" t="inlineStr"/>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L250" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15751,7 +16427,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K251" t="inlineStr"/>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L251" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15812,7 +16492,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K252" t="inlineStr"/>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L252" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15873,7 +16557,11 @@
           <t>8.306.984-8</t>
         </is>
       </c>
-      <c r="K253" t="inlineStr"/>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L253" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15934,7 +16622,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K254" t="inlineStr"/>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L254" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16056,7 +16748,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K256" t="inlineStr"/>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L256" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16178,7 +16874,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K258" t="inlineStr"/>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L258" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16239,7 +16939,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K259" t="inlineStr"/>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L259" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16483,7 +17187,11 @@
           <t>78.057.703-7</t>
         </is>
       </c>
-      <c r="K263" t="inlineStr"/>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L263" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16544,7 +17252,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K264" t="inlineStr"/>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L264" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16605,7 +17317,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K265" t="inlineStr"/>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L265" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16666,7 +17382,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K266" t="inlineStr"/>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L266" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16788,7 +17508,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K268" t="inlineStr"/>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L268" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16910,7 +17634,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K270" t="inlineStr"/>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L270" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17032,7 +17760,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K272" t="inlineStr"/>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L272" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17093,7 +17825,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K273" t="inlineStr"/>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L273" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17215,7 +17951,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K275" t="inlineStr"/>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L275" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17276,7 +18016,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K276" t="inlineStr"/>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L276" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17398,7 +18142,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K278" t="inlineStr"/>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L278" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17459,7 +18207,11 @@
           <t>77.623.039-1</t>
         </is>
       </c>
-      <c r="K279" t="inlineStr"/>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L279" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17520,7 +18272,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K280" t="inlineStr"/>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L280" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17581,7 +18337,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K281" t="inlineStr"/>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L281" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17642,7 +18402,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K282" t="inlineStr"/>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L282" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17703,7 +18467,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K283" t="inlineStr"/>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L283" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18008,7 +18776,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K288" t="inlineStr"/>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L288" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18069,7 +18841,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K289" t="inlineStr"/>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L289" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18130,7 +18906,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K290" t="inlineStr"/>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L290" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18191,7 +18971,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K291" t="inlineStr"/>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L291" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18313,7 +19097,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K293" t="inlineStr"/>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L293" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18374,7 +19162,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K294" t="inlineStr"/>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L294" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18435,7 +19227,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K295" t="inlineStr"/>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L295" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18557,7 +19353,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K297" t="inlineStr"/>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L297" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18618,7 +19418,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K298" t="inlineStr"/>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L298" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18679,7 +19483,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K299" t="inlineStr"/>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L299" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18801,7 +19609,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K301" t="inlineStr"/>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L301" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18862,7 +19674,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K302" t="inlineStr"/>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L302" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18923,7 +19739,11 @@
           <t>76.100.933-8</t>
         </is>
       </c>
-      <c r="K303" t="inlineStr"/>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L303" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19045,7 +19865,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K305" t="inlineStr"/>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L305" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19106,7 +19930,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K306" t="inlineStr"/>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L306" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19167,7 +19995,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K307" t="inlineStr"/>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L307" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19289,7 +20121,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K309" t="inlineStr"/>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L309" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19411,7 +20247,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K311" t="inlineStr"/>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L311" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19472,7 +20312,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K312" t="inlineStr"/>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L312" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19533,7 +20377,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K313" t="inlineStr"/>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L313" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19594,7 +20442,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K314" t="inlineStr"/>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L314" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19655,7 +20507,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K315" t="inlineStr"/>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L315" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19716,7 +20572,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K316" t="inlineStr"/>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L316" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19777,7 +20637,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K317" t="inlineStr"/>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L317" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19838,7 +20702,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K318" t="inlineStr"/>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L318" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19899,7 +20767,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K319" t="inlineStr"/>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L319" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20021,7 +20893,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K321" t="inlineStr"/>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L321" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20143,7 +21019,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K323" t="inlineStr"/>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L323" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20204,7 +21084,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K324" t="inlineStr"/>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L324" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20326,7 +21210,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K326" t="inlineStr"/>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L326" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20387,7 +21275,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K327" t="inlineStr"/>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L327" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20448,7 +21340,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K328" t="inlineStr"/>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L328" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20509,7 +21405,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K329" t="inlineStr"/>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L329" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20692,7 +21592,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K332" t="inlineStr"/>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L332" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20814,7 +21718,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K334" t="inlineStr"/>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L334" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20936,7 +21844,11 @@
           <t>79.722.860-5</t>
         </is>
       </c>
-      <c r="K336" t="inlineStr"/>
+      <c r="K336" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L336" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21058,7 +21970,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K338" t="inlineStr"/>
+      <c r="K338" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L338" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21119,7 +22035,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K339" t="inlineStr"/>
+      <c r="K339" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L339" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21180,7 +22100,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K340" t="inlineStr"/>
+      <c r="K340" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L340" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21363,7 +22287,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K343" t="inlineStr"/>
+      <c r="K343" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L343" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21485,7 +22413,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K345" t="inlineStr"/>
+      <c r="K345" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L345" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21607,7 +22539,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K347" t="inlineStr"/>
+      <c r="K347" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L347" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21668,7 +22604,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K348" t="inlineStr"/>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L348" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21729,7 +22669,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K349" t="inlineStr"/>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L349" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21851,7 +22795,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K351" t="inlineStr"/>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L351" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21912,7 +22860,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K352" t="inlineStr"/>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L352" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21973,7 +22925,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K353" t="inlineStr"/>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L353" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22156,7 +23112,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K356" t="inlineStr"/>
+      <c r="K356" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L356" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22217,7 +23177,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K357" t="inlineStr"/>
+      <c r="K357" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L357" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22278,7 +23242,11 @@
           <t>78.061.716-0</t>
         </is>
       </c>
-      <c r="K358" t="inlineStr"/>
+      <c r="K358" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L358" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22400,7 +23368,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K360" t="inlineStr"/>
+      <c r="K360" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L360" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22461,7 +23433,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K361" t="inlineStr"/>
+      <c r="K361" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L361" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22644,7 +23620,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K364" t="inlineStr"/>
+      <c r="K364" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L364" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22705,7 +23685,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K365" t="inlineStr"/>
+      <c r="K365" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L365" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22766,7 +23750,11 @@
           <t>96.989.530-7</t>
         </is>
       </c>
-      <c r="K366" t="inlineStr"/>
+      <c r="K366" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L366" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22827,7 +23815,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K367" t="inlineStr"/>
+      <c r="K367" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L367" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22888,7 +23880,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K368" t="inlineStr"/>
+      <c r="K368" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L368" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22949,7 +23945,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K369" t="inlineStr"/>
+      <c r="K369" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L369" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23071,7 +24071,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K371" t="inlineStr"/>
+      <c r="K371" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L371" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23132,7 +24136,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K372" t="inlineStr"/>
+      <c r="K372" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L372" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23193,7 +24201,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K373" t="inlineStr"/>
+      <c r="K373" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L373" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23315,7 +24327,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K375" t="inlineStr"/>
+      <c r="K375" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L375" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23437,7 +24453,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K377" t="inlineStr"/>
+      <c r="K377" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L377" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23498,7 +24518,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K378" t="inlineStr"/>
+      <c r="K378" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L378" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23559,7 +24583,11 @@
           <t>76.556.184-1</t>
         </is>
       </c>
-      <c r="K379" t="inlineStr"/>
+      <c r="K379" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L379" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23620,7 +24648,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K380" t="inlineStr"/>
+      <c r="K380" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L380" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23681,7 +24713,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K381" t="inlineStr"/>
+      <c r="K381" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L381" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23803,7 +24839,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K383" t="inlineStr"/>
+      <c r="K383" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L383" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23864,7 +24904,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K384" t="inlineStr"/>
+      <c r="K384" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L384" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23986,7 +25030,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K386" t="inlineStr"/>
+      <c r="K386" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L386" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24108,7 +25156,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K388" t="inlineStr"/>
+      <c r="K388" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L388" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24169,7 +25221,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K389" t="inlineStr"/>
+      <c r="K389" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L389" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24230,7 +25286,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K390" t="inlineStr"/>
+      <c r="K390" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L390" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24291,7 +25351,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K391" t="inlineStr"/>
+      <c r="K391" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L391" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24413,7 +25477,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K393" t="inlineStr"/>
+      <c r="K393" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L393" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24474,7 +25542,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K394" t="inlineStr"/>
+      <c r="K394" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L394" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24535,7 +25607,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K395" t="inlineStr"/>
+      <c r="K395" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L395" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24657,7 +25733,11 @@
           <t>78.209.481-5</t>
         </is>
       </c>
-      <c r="K397" t="inlineStr"/>
+      <c r="K397" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L397" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24718,7 +25798,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K398" t="inlineStr"/>
+      <c r="K398" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L398" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24779,7 +25863,11 @@
           <t>96.989.530-7</t>
         </is>
       </c>
-      <c r="K399" t="inlineStr"/>
+      <c r="K399" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L399" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24840,7 +25928,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K400" t="inlineStr"/>
+      <c r="K400" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L400" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24962,7 +26054,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K402" t="inlineStr"/>
+      <c r="K402" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L402" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25084,7 +26180,11 @@
           <t>76.556.184-1</t>
         </is>
       </c>
-      <c r="K404" t="inlineStr"/>
+      <c r="K404" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L404" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25206,7 +26306,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K406" t="inlineStr"/>
+      <c r="K406" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L406" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25267,7 +26371,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K407" t="inlineStr"/>
+      <c r="K407" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L407" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25328,7 +26436,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K408" t="inlineStr"/>
+      <c r="K408" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L408" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25389,7 +26501,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K409" t="inlineStr"/>
+      <c r="K409" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L409" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25572,7 +26688,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K412" t="inlineStr"/>
+      <c r="K412" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L412" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25633,7 +26753,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K413" t="inlineStr"/>
+      <c r="K413" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L413" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25694,7 +26818,11 @@
           <t>78.209.441-6</t>
         </is>
       </c>
-      <c r="K414" t="inlineStr"/>
+      <c r="K414" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L414" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25816,7 +26944,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K416" t="inlineStr"/>
+      <c r="K416" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L416" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25877,7 +27009,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K417" t="inlineStr"/>
+      <c r="K417" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L417" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26060,7 +27196,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K420" t="inlineStr"/>
+      <c r="K420" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L420" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26182,7 +27322,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K422" t="inlineStr"/>
+      <c r="K422" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L422" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26304,7 +27448,11 @@
           <t>79.722.860-5</t>
         </is>
       </c>
-      <c r="K424" t="inlineStr"/>
+      <c r="K424" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L424" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26365,7 +27513,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K425" t="inlineStr"/>
+      <c r="K425" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L425" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26426,7 +27578,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K426" t="inlineStr"/>
+      <c r="K426" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L426" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26487,7 +27643,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K427" t="inlineStr"/>
+      <c r="K427" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L427" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26548,7 +27708,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K428" t="inlineStr"/>
+      <c r="K428" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L428" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26609,7 +27773,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K429" t="inlineStr"/>
+      <c r="K429" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L429" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26731,7 +27899,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K431" t="inlineStr"/>
+      <c r="K431" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L431" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26792,7 +27964,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K432" t="inlineStr"/>
+      <c r="K432" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L432" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26853,7 +28029,11 @@
           <t>78.057.703-7</t>
         </is>
       </c>
-      <c r="K433" t="inlineStr"/>
+      <c r="K433" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L433" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26914,7 +28094,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K434" t="inlineStr"/>
+      <c r="K434" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L434" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26975,7 +28159,11 @@
           <t>78.209.441-6</t>
         </is>
       </c>
-      <c r="K435" t="inlineStr"/>
+      <c r="K435" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L435" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27097,7 +28285,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K437" t="inlineStr"/>
+      <c r="K437" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L437" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27158,7 +28350,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K438" t="inlineStr"/>
+      <c r="K438" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L438" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27219,7 +28415,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K439" t="inlineStr"/>
+      <c r="K439" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L439" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27280,7 +28480,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K440" t="inlineStr"/>
+      <c r="K440" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L440" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27341,7 +28545,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K441" t="inlineStr"/>
+      <c r="K441" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L441" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27402,7 +28610,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K442" t="inlineStr"/>
+      <c r="K442" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L442" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27463,7 +28675,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K443" t="inlineStr"/>
+      <c r="K443" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L443" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27524,7 +28740,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K444" t="inlineStr"/>
+      <c r="K444" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L444" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27585,7 +28805,11 @@
           <t>77.581.865-4</t>
         </is>
       </c>
-      <c r="K445" t="inlineStr"/>
+      <c r="K445" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L445" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27646,7 +28870,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K446" t="inlineStr"/>
+      <c r="K446" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L446" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27829,7 +29057,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K449" t="inlineStr"/>
+      <c r="K449" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L449" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27951,7 +29183,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K451" t="inlineStr"/>
+      <c r="K451" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L451" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28012,7 +29248,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K452" t="inlineStr"/>
+      <c r="K452" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L452" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28195,7 +29435,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K455" t="inlineStr"/>
+      <c r="K455" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L455" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28256,7 +29500,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K456" t="inlineStr"/>
+      <c r="K456" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L456" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28317,7 +29565,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K457" t="inlineStr"/>
+      <c r="K457" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L457" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28500,7 +29752,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K460" t="inlineStr"/>
+      <c r="K460" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L460" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28561,7 +29817,11 @@
           <t>76.556.184-1</t>
         </is>
       </c>
-      <c r="K461" t="inlineStr"/>
+      <c r="K461" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L461" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28622,7 +29882,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K462" t="inlineStr"/>
+      <c r="K462" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L462" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29049,7 +30313,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K469" t="inlineStr"/>
+      <c r="K469" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L469" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29354,7 +30622,11 @@
           <t>77.860.046-3</t>
         </is>
       </c>
-      <c r="K474" t="inlineStr"/>
+      <c r="K474" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L474" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29415,7 +30687,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K475" t="inlineStr"/>
+      <c r="K475" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L475" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29476,7 +30752,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K476" t="inlineStr"/>
+      <c r="K476" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L476" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29537,7 +30817,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K477" t="inlineStr"/>
+      <c r="K477" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L477" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29659,7 +30943,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K479" t="inlineStr"/>
+      <c r="K479" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L479" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29720,7 +31008,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K480" t="inlineStr"/>
+      <c r="K480" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L480" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29842,7 +31134,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K482" t="inlineStr"/>
+      <c r="K482" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L482" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29903,7 +31199,11 @@
           <t>76.556.184-1</t>
         </is>
       </c>
-      <c r="K483" t="inlineStr"/>
+      <c r="K483" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L483" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29964,7 +31264,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K484" t="inlineStr"/>
+      <c r="K484" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L484" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30086,7 +31390,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K486" t="inlineStr"/>
+      <c r="K486" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L486" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30147,7 +31455,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K487" t="inlineStr"/>
+      <c r="K487" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L487" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30208,7 +31520,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K488" t="inlineStr"/>
+      <c r="K488" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L488" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30269,7 +31585,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K489" t="inlineStr"/>
+      <c r="K489" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L489" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30391,7 +31711,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K491" t="inlineStr"/>
+      <c r="K491" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L491" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30513,7 +31837,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K493" t="inlineStr"/>
+      <c r="K493" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L493" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30635,7 +31963,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K495" t="inlineStr"/>
+      <c r="K495" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L495" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30757,7 +32089,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K497" t="inlineStr"/>
+      <c r="K497" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L497" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30818,7 +32154,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K498" t="inlineStr"/>
+      <c r="K498" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L498" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30879,7 +32219,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K499" t="inlineStr"/>
+      <c r="K499" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L499" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30940,7 +32284,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K500" t="inlineStr"/>
+      <c r="K500" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L500" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31001,7 +32349,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K501" t="inlineStr"/>
+      <c r="K501" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L501" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31062,7 +32414,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K502" t="inlineStr"/>
+      <c r="K502" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L502" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31123,7 +32479,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K503" t="inlineStr"/>
+      <c r="K503" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L503" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31184,7 +32544,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K504" t="inlineStr"/>
+      <c r="K504" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L504" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31367,7 +32731,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K507" t="inlineStr"/>
+      <c r="K507" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L507" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31428,7 +32796,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K508" t="inlineStr"/>
+      <c r="K508" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L508" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31489,7 +32861,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K509" t="inlineStr"/>
+      <c r="K509" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L509" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31611,7 +32987,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K511" t="inlineStr"/>
+      <c r="K511" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L511" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31672,7 +33052,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K512" t="inlineStr"/>
+      <c r="K512" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L512" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31794,7 +33178,11 @@
           <t>78.057.703-7</t>
         </is>
       </c>
-      <c r="K514" t="inlineStr"/>
+      <c r="K514" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L514" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31977,7 +33365,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K517" t="inlineStr"/>
+      <c r="K517" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L517" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32038,7 +33430,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K518" t="inlineStr"/>
+      <c r="K518" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L518" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32099,7 +33495,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K519" t="inlineStr"/>
+      <c r="K519" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L519" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32160,7 +33560,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K520" t="inlineStr"/>
+      <c r="K520" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L520" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32221,7 +33625,11 @@
           <t>76.817.360-5</t>
         </is>
       </c>
-      <c r="K521" t="inlineStr"/>
+      <c r="K521" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L521" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32282,7 +33690,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K522" t="inlineStr"/>
+      <c r="K522" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L522" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32343,7 +33755,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K523" t="inlineStr"/>
+      <c r="K523" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L523" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32404,7 +33820,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K524" t="inlineStr"/>
+      <c r="K524" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L524" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32526,7 +33946,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K526" t="inlineStr"/>
+      <c r="K526" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L526" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32648,7 +34072,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K528" t="inlineStr"/>
+      <c r="K528" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L528" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32770,7 +34198,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K530" t="inlineStr"/>
+      <c r="K530" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L530" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32892,7 +34324,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K532" t="inlineStr"/>
+      <c r="K532" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L532" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32953,7 +34389,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K533" t="inlineStr"/>
+      <c r="K533" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L533" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33014,7 +34454,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K534" t="inlineStr"/>
+      <c r="K534" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L534" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33136,7 +34580,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K536" t="inlineStr"/>
+      <c r="K536" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L536" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33380,7 +34828,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K540" t="inlineStr"/>
+      <c r="K540" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L540" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33441,7 +34893,11 @@
           <t>78.057.703-7</t>
         </is>
       </c>
-      <c r="K541" t="inlineStr"/>
+      <c r="K541" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L541" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33563,7 +35019,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K543" t="inlineStr"/>
+      <c r="K543" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L543" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33624,7 +35084,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K544" t="inlineStr"/>
+      <c r="K544" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L544" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33685,7 +35149,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K545" t="inlineStr"/>
+      <c r="K545" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L545" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33746,7 +35214,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K546" t="inlineStr"/>
+      <c r="K546" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L546" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33807,7 +35279,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K547" t="inlineStr"/>
+      <c r="K547" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L547" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33868,7 +35344,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K548" t="inlineStr"/>
+      <c r="K548" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L548" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33990,7 +35470,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K550" t="inlineStr"/>
+      <c r="K550" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L550" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34051,7 +35535,11 @@
           <t>77.909.208-9</t>
         </is>
       </c>
-      <c r="K551" t="inlineStr"/>
+      <c r="K551" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L551" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34112,7 +35600,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K552" t="inlineStr"/>
+      <c r="K552" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L552" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34173,7 +35665,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K553" t="inlineStr"/>
+      <c r="K553" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L553" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34234,7 +35730,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K554" t="inlineStr"/>
+      <c r="K554" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L554" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34417,7 +35917,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K557" t="inlineStr"/>
+      <c r="K557" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L557" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34478,7 +35982,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K558" t="inlineStr"/>
+      <c r="K558" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L558" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34539,7 +36047,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K559" t="inlineStr"/>
+      <c r="K559" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L559" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34600,7 +36112,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K560" t="inlineStr"/>
+      <c r="K560" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L560" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34661,7 +36177,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K561" t="inlineStr"/>
+      <c r="K561" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L561" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34966,7 +36486,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K566" t="inlineStr"/>
+      <c r="K566" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L566" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35088,7 +36612,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K568" t="inlineStr"/>
+      <c r="K568" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L568" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35271,7 +36799,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K571" t="inlineStr"/>
+      <c r="K571" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L571" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35576,7 +37108,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K576" t="inlineStr"/>
+      <c r="K576" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L576" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35637,7 +37173,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K577" t="inlineStr"/>
+      <c r="K577" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L577" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35881,7 +37421,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K581" t="inlineStr"/>
+      <c r="K581" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L581" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36064,7 +37608,11 @@
           <t>77.404.653-4</t>
         </is>
       </c>
-      <c r="K584" t="inlineStr"/>
+      <c r="K584" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L584" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36125,7 +37673,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K585" t="inlineStr"/>
+      <c r="K585" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L585" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36186,7 +37738,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K586" t="inlineStr"/>
+      <c r="K586" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L586" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36369,7 +37925,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K589" t="inlineStr"/>
+      <c r="K589" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L589" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36430,7 +37990,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K590" t="inlineStr"/>
+      <c r="K590" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L590" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36491,7 +38055,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K591" t="inlineStr"/>
+      <c r="K591" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L591" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36735,7 +38303,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K595" t="inlineStr"/>
+      <c r="K595" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L595" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36857,7 +38429,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K597" t="inlineStr"/>
+      <c r="K597" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L597" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36918,7 +38494,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K598" t="inlineStr"/>
+      <c r="K598" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L598" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37162,7 +38742,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K602" t="inlineStr"/>
+      <c r="K602" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L602" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37223,7 +38807,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K603" t="inlineStr"/>
+      <c r="K603" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L603" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37284,7 +38872,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K604" t="inlineStr"/>
+      <c r="K604" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L604" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37467,7 +39059,11 @@
           <t>79.722.860-5</t>
         </is>
       </c>
-      <c r="K607" t="inlineStr"/>
+      <c r="K607" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L607" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37528,7 +39124,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K608" t="inlineStr"/>
+      <c r="K608" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L608" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37589,7 +39189,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K609" t="inlineStr"/>
+      <c r="K609" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L609" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37650,7 +39254,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K610" t="inlineStr"/>
+      <c r="K610" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L610" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37711,7 +39319,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K611" t="inlineStr"/>
+      <c r="K611" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L611" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37772,7 +39384,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K612" t="inlineStr"/>
+      <c r="K612" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L612" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37894,7 +39510,11 @@
           <t>78.209.481-5</t>
         </is>
       </c>
-      <c r="K614" t="inlineStr"/>
+      <c r="K614" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L614" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38016,7 +39636,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K616" t="inlineStr"/>
+      <c r="K616" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L616" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38138,7 +39762,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K618" t="inlineStr"/>
+      <c r="K618" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L618" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38199,7 +39827,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K619" t="inlineStr"/>
+      <c r="K619" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L619" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38504,7 +40136,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K624" t="inlineStr"/>
+      <c r="K624" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L624" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38748,7 +40384,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K628" t="inlineStr"/>
+      <c r="K628" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L628" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38809,7 +40449,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K629" t="inlineStr"/>
+      <c r="K629" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L629" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38992,7 +40636,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K632" t="inlineStr"/>
+      <c r="K632" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L632" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39053,7 +40701,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K633" t="inlineStr"/>
+      <c r="K633" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L633" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39114,7 +40766,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K634" t="inlineStr"/>
+      <c r="K634" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L634" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39175,7 +40831,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K635" t="inlineStr"/>
+      <c r="K635" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L635" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39297,7 +40957,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K637" t="inlineStr"/>
+      <c r="K637" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L637" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39358,7 +41022,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K638" t="inlineStr"/>
+      <c r="K638" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L638" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39419,7 +41087,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K639" t="inlineStr"/>
+      <c r="K639" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L639" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39480,7 +41152,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K640" t="inlineStr"/>
+      <c r="K640" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L640" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39602,7 +41278,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K642" t="inlineStr"/>
+      <c r="K642" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L642" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39663,7 +41343,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K643" t="inlineStr"/>
+      <c r="K643" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L643" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39724,7 +41408,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K644" t="inlineStr"/>
+      <c r="K644" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L644" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39785,7 +41473,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K645" t="inlineStr"/>
+      <c r="K645" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L645" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40029,7 +41721,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K649" t="inlineStr"/>
+      <c r="K649" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L649" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40090,7 +41786,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K650" t="inlineStr"/>
+      <c r="K650" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L650" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40212,7 +41912,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K652" t="inlineStr"/>
+      <c r="K652" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L652" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40395,7 +42099,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K655" t="inlineStr"/>
+      <c r="K655" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L655" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40517,7 +42225,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K657" t="inlineStr"/>
+      <c r="K657" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L657" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40578,7 +42290,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K658" t="inlineStr"/>
+      <c r="K658" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L658" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40639,7 +42355,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K659" t="inlineStr"/>
+      <c r="K659" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L659" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40700,7 +42420,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K660" t="inlineStr"/>
+      <c r="K660" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L660" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40822,7 +42546,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K662" t="inlineStr"/>
+      <c r="K662" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L662" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40883,7 +42611,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K663" t="inlineStr"/>
+      <c r="K663" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L663" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40944,7 +42676,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K664" t="inlineStr"/>
+      <c r="K664" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L664" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41005,7 +42741,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K665" t="inlineStr"/>
+      <c r="K665" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L665" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41127,7 +42867,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K667" t="inlineStr"/>
+      <c r="K667" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L667" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41188,7 +42932,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K668" t="inlineStr"/>
+      <c r="K668" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L668" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41249,7 +42997,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K669" t="inlineStr"/>
+      <c r="K669" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L669" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41310,7 +43062,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K670" t="inlineStr"/>
+      <c r="K670" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L670" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41554,7 +43310,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K674" t="inlineStr"/>
+      <c r="K674" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L674" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41615,7 +43375,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K675" t="inlineStr"/>
+      <c r="K675" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L675" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41676,7 +43440,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K676" t="inlineStr"/>
+      <c r="K676" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L676" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41737,7 +43505,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K677" t="inlineStr"/>
+      <c r="K677" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L677" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41798,7 +43570,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K678" t="inlineStr"/>
+      <c r="K678" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L678" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41859,7 +43635,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K679" t="inlineStr"/>
+      <c r="K679" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L679" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41981,7 +43761,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K681" t="inlineStr"/>
+      <c r="K681" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L681" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42103,7 +43887,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K683" t="inlineStr"/>
+      <c r="K683" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L683" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42164,7 +43952,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K684" t="inlineStr"/>
+      <c r="K684" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L684" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42225,7 +44017,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K685" t="inlineStr"/>
+      <c r="K685" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L685" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42286,7 +44082,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K686" t="inlineStr"/>
+      <c r="K686" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L686" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42347,7 +44147,11 @@
           <t>78.076.237-3</t>
         </is>
       </c>
-      <c r="K687" t="inlineStr"/>
+      <c r="K687" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L687" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42408,7 +44212,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K688" t="inlineStr"/>
+      <c r="K688" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L688" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42469,7 +44277,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K689" t="inlineStr"/>
+      <c r="K689" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L689" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42530,7 +44342,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K690" t="inlineStr"/>
+      <c r="K690" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L690" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42591,7 +44407,11 @@
           <t>78.209.441-6</t>
         </is>
       </c>
-      <c r="K691" t="inlineStr"/>
+      <c r="K691" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L691" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42652,7 +44472,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K692" t="inlineStr"/>
+      <c r="K692" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L692" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42713,7 +44537,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K693" t="inlineStr"/>
+      <c r="K693" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L693" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42774,7 +44602,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K694" t="inlineStr"/>
+      <c r="K694" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L694" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42835,7 +44667,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K695" t="inlineStr"/>
+      <c r="K695" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L695" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42957,7 +44793,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K697" t="inlineStr"/>
+      <c r="K697" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L697" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43018,7 +44858,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K698" t="inlineStr"/>
+      <c r="K698" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L698" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43079,7 +44923,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K699" t="inlineStr"/>
+      <c r="K699" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L699" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43140,7 +44988,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K700" t="inlineStr"/>
+      <c r="K700" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L700" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43262,7 +45114,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K702" t="inlineStr"/>
+      <c r="K702" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L702" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43323,7 +45179,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K703" t="inlineStr"/>
+      <c r="K703" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L703" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43384,7 +45244,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K704" t="inlineStr"/>
+      <c r="K704" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L704" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43445,7 +45309,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K705" t="inlineStr"/>
+      <c r="K705" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L705" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43506,7 +45374,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K706" t="inlineStr"/>
+      <c r="K706" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L706" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43567,7 +45439,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K707" t="inlineStr"/>
+      <c r="K707" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L707" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43628,7 +45504,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K708" t="inlineStr"/>
+      <c r="K708" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L708" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43689,7 +45569,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K709" t="inlineStr"/>
+      <c r="K709" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L709" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43811,7 +45695,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K711" t="inlineStr"/>
+      <c r="K711" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L711" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43933,7 +45821,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K713" t="inlineStr"/>
+      <c r="K713" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L713" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44055,7 +45947,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K715" t="inlineStr"/>
+      <c r="K715" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L715" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44116,7 +46012,11 @@
           <t>77.860.046-3</t>
         </is>
       </c>
-      <c r="K716" t="inlineStr"/>
+      <c r="K716" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L716" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44238,7 +46138,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K718" t="inlineStr"/>
+      <c r="K718" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L718" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44360,7 +46264,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K720" t="inlineStr"/>
+      <c r="K720" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L720" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44543,7 +46451,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K723" t="inlineStr"/>
+      <c r="K723" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L723" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44665,7 +46577,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K725" t="inlineStr"/>
+      <c r="K725" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L725" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44848,7 +46764,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K728" t="inlineStr"/>
+      <c r="K728" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L728" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44970,7 +46890,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K730" t="inlineStr"/>
+      <c r="K730" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L730" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45092,7 +47016,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K732" t="inlineStr"/>
+      <c r="K732" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L732" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45153,7 +47081,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K733" t="inlineStr"/>
+      <c r="K733" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L733" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45214,7 +47146,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K734" t="inlineStr"/>
+      <c r="K734" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L734" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45275,7 +47211,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K735" t="inlineStr"/>
+      <c r="K735" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L735" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45336,7 +47276,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K736" t="inlineStr"/>
+      <c r="K736" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L736" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45397,7 +47341,11 @@
           <t>79.722.860-5</t>
         </is>
       </c>
-      <c r="K737" t="inlineStr"/>
+      <c r="K737" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L737" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45458,7 +47406,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K738" t="inlineStr"/>
+      <c r="K738" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L738" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45519,7 +47471,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K739" t="inlineStr"/>
+      <c r="K739" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L739" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45580,7 +47536,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K740" t="inlineStr"/>
+      <c r="K740" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L740" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45763,7 +47723,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K743" t="inlineStr"/>
+      <c r="K743" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L743" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45824,7 +47788,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K744" t="inlineStr"/>
+      <c r="K744" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L744" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45885,7 +47853,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K745" t="inlineStr"/>
+      <c r="K745" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L745" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45946,7 +47918,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K746" t="inlineStr"/>
+      <c r="K746" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L746" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46068,7 +48044,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K748" t="inlineStr"/>
+      <c r="K748" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L748" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46251,7 +48231,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K751" t="inlineStr"/>
+      <c r="K751" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L751" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46312,7 +48296,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K752" t="inlineStr"/>
+      <c r="K752" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L752" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46373,7 +48361,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K753" t="inlineStr"/>
+      <c r="K753" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L753" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46434,7 +48426,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K754" t="inlineStr"/>
+      <c r="K754" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L754" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46495,7 +48491,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K755" t="inlineStr"/>
+      <c r="K755" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L755" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46556,7 +48556,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K756" t="inlineStr"/>
+      <c r="K756" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L756" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46617,7 +48621,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K757" t="inlineStr"/>
+      <c r="K757" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L757" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46678,7 +48686,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K758" t="inlineStr"/>
+      <c r="K758" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L758" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46739,7 +48751,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K759" t="inlineStr"/>
+      <c r="K759" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L759" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46800,7 +48816,11 @@
           <t>8.306.984-8</t>
         </is>
       </c>
-      <c r="K760" t="inlineStr"/>
+      <c r="K760" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L760" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46861,7 +48881,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K761" t="inlineStr"/>
+      <c r="K761" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L761" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46922,7 +48946,11 @@
           <t>77.037.031-0</t>
         </is>
       </c>
-      <c r="K762" t="inlineStr"/>
+      <c r="K762" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L762" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46983,7 +49011,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K763" t="inlineStr"/>
+      <c r="K763" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L763" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47044,7 +49076,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K764" t="inlineStr"/>
+      <c r="K764" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L764" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47166,7 +49202,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K766" t="inlineStr"/>
+      <c r="K766" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L766" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47349,7 +49389,11 @@
           <t>77.623.039-1</t>
         </is>
       </c>
-      <c r="K769" t="inlineStr"/>
+      <c r="K769" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L769" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47410,7 +49454,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K770" t="inlineStr"/>
+      <c r="K770" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L770" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47471,7 +49519,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K771" t="inlineStr"/>
+      <c r="K771" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L771" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47715,7 +49767,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K775" t="inlineStr"/>
+      <c r="K775" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L775" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47776,7 +49832,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K776" t="inlineStr"/>
+      <c r="K776" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L776" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47837,7 +49897,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K777" t="inlineStr"/>
+      <c r="K777" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L777" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47898,7 +49962,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K778" t="inlineStr"/>
+      <c r="K778" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L778" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48020,7 +50088,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K780" t="inlineStr"/>
+      <c r="K780" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L780" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48081,7 +50153,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K781" t="inlineStr"/>
+      <c r="K781" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L781" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48142,7 +50218,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K782" t="inlineStr"/>
+      <c r="K782" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L782" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48264,7 +50344,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K784" t="inlineStr"/>
+      <c r="K784" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L784" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48447,7 +50531,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K787" t="inlineStr"/>
+      <c r="K787" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L787" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48508,7 +50596,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K788" t="inlineStr"/>
+      <c r="K788" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L788" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48630,7 +50722,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K790" t="inlineStr"/>
+      <c r="K790" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L790" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48691,7 +50787,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K791" t="inlineStr"/>
+      <c r="K791" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L791" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48752,7 +50852,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K792" t="inlineStr"/>
+      <c r="K792" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L792" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48813,7 +50917,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K793" t="inlineStr"/>
+      <c r="K793" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L793" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48935,7 +51043,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K795" t="inlineStr"/>
+      <c r="K795" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L795" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48996,7 +51108,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K796" t="inlineStr"/>
+      <c r="K796" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L796" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49057,7 +51173,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K797" t="inlineStr"/>
+      <c r="K797" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L797" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49118,7 +51238,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K798" t="inlineStr"/>
+      <c r="K798" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L798" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49179,7 +51303,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K799" t="inlineStr"/>
+      <c r="K799" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L799" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49301,7 +51429,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K801" t="inlineStr"/>
+      <c r="K801" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L801" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49362,7 +51494,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K802" t="inlineStr"/>
+      <c r="K802" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L802" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49423,7 +51559,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K803" t="inlineStr"/>
+      <c r="K803" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L803" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49545,7 +51685,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K805" t="inlineStr"/>
+      <c r="K805" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L805" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49606,7 +51750,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K806" t="inlineStr"/>
+      <c r="K806" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L806" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49789,7 +51937,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K809" t="inlineStr"/>
+      <c r="K809" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L809" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49850,7 +52002,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K810" t="inlineStr"/>
+      <c r="K810" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L810" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49972,7 +52128,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K812" t="inlineStr"/>
+      <c r="K812" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L812" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50033,7 +52193,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K813" t="inlineStr"/>
+      <c r="K813" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L813" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50094,7 +52258,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K814" t="inlineStr"/>
+      <c r="K814" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L814" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50155,7 +52323,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K815" t="inlineStr"/>
+      <c r="K815" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L815" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50216,7 +52388,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K816" t="inlineStr"/>
+      <c r="K816" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L816" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50277,7 +52453,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K817" t="inlineStr"/>
+      <c r="K817" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L817" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50338,7 +52518,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K818" t="inlineStr"/>
+      <c r="K818" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L818" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50399,7 +52583,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K819" t="inlineStr"/>
+      <c r="K819" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L819" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50460,7 +52648,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K820" t="inlineStr"/>
+      <c r="K820" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L820" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50521,7 +52713,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K821" t="inlineStr"/>
+      <c r="K821" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L821" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50582,7 +52778,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K822" t="inlineStr"/>
+      <c r="K822" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L822" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50643,7 +52843,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K823" t="inlineStr"/>
+      <c r="K823" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L823" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50704,7 +52908,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K824" t="inlineStr"/>
+      <c r="K824" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L824" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50765,7 +52973,11 @@
           <t>77.037.031-0</t>
         </is>
       </c>
-      <c r="K825" t="inlineStr"/>
+      <c r="K825" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L825" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50948,7 +53160,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K828" t="inlineStr"/>
+      <c r="K828" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L828" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51131,7 +53347,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K831" t="inlineStr"/>
+      <c r="K831" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L831" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51375,7 +53595,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K835" t="inlineStr"/>
+      <c r="K835" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L835" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51436,7 +53660,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K836" t="inlineStr"/>
+      <c r="K836" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L836" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51558,7 +53786,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K838" t="inlineStr"/>
+      <c r="K838" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L838" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51619,7 +53851,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K839" t="inlineStr"/>
+      <c r="K839" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L839" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51680,7 +53916,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K840" t="inlineStr"/>
+      <c r="K840" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L840" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51741,7 +53981,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K841" t="inlineStr"/>
+      <c r="K841" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L841" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51863,7 +54107,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K843" t="inlineStr"/>
+      <c r="K843" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L843" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52046,7 +54294,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K846" t="inlineStr"/>
+      <c r="K846" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L846" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52107,7 +54359,11 @@
           <t>78.209.441-6</t>
         </is>
       </c>
-      <c r="K847" t="inlineStr"/>
+      <c r="K847" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L847" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52168,7 +54424,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K848" t="inlineStr"/>
+      <c r="K848" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L848" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52229,7 +54489,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K849" t="inlineStr"/>
+      <c r="K849" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L849" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52290,7 +54554,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K850" t="inlineStr"/>
+      <c r="K850" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L850" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52351,7 +54619,11 @@
           <t>77.685.821-8</t>
         </is>
       </c>
-      <c r="K851" t="inlineStr"/>
+      <c r="K851" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L851" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52412,7 +54684,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K852" t="inlineStr"/>
+      <c r="K852" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L852" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52473,7 +54749,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K853" t="inlineStr"/>
+      <c r="K853" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L853" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52534,7 +54814,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K854" t="inlineStr"/>
+      <c r="K854" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L854" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52595,7 +54879,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K855" t="inlineStr"/>
+      <c r="K855" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L855" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52656,7 +54944,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K856" t="inlineStr"/>
+      <c r="K856" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L856" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52717,7 +55009,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K857" t="inlineStr"/>
+      <c r="K857" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L857" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52778,7 +55074,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K858" t="inlineStr"/>
+      <c r="K858" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L858" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52900,7 +55200,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K860" t="inlineStr"/>
+      <c r="K860" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L860" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52961,7 +55265,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K861" t="inlineStr"/>
+      <c r="K861" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L861" t="inlineStr">
         <is>
           <t>USD</t>
@@ -53022,7 +55330,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K862" t="inlineStr"/>
+      <c r="K862" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L862" t="inlineStr">
         <is>
           <t>USD</t>
@@ -53205,7 +55517,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K865" t="inlineStr"/>
+      <c r="K865" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L865" t="inlineStr">
         <is>
           <t>USD</t>
@@ -53266,7 +55582,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K866" t="inlineStr"/>
+      <c r="K866" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L866" t="inlineStr">
         <is>
           <t>USD</t>
@@ -53449,7 +55769,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K869" t="inlineStr"/>
+      <c r="K869" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L869" t="inlineStr">
         <is>
           <t>USD</t>
@@ -53510,7 +55834,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K870" t="inlineStr"/>
+      <c r="K870" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L870" t="inlineStr">
         <is>
           <t>USD</t>
@@ -53632,7 +55960,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K872" t="inlineStr"/>
+      <c r="K872" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L872" t="inlineStr">
         <is>
           <t>USD</t>
@@ -53754,7 +56086,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K874" t="inlineStr"/>
+      <c r="K874" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L874" t="inlineStr">
         <is>
           <t>USD</t>
@@ -53815,7 +56151,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K875" t="inlineStr"/>
+      <c r="K875" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L875" t="inlineStr">
         <is>
           <t>USD</t>
@@ -53876,7 +56216,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K876" t="inlineStr"/>
+      <c r="K876" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L876" t="inlineStr">
         <is>
           <t>USD</t>
@@ -53937,7 +56281,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K877" t="inlineStr"/>
+      <c r="K877" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L877" t="inlineStr">
         <is>
           <t>USD</t>
@@ -54059,7 +56407,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K879" t="inlineStr"/>
+      <c r="K879" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L879" t="inlineStr">
         <is>
           <t>USD</t>
@@ -54120,7 +56472,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K880" t="inlineStr"/>
+      <c r="K880" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L880" t="inlineStr">
         <is>
           <t>USD</t>
@@ -54181,7 +56537,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K881" t="inlineStr"/>
+      <c r="K881" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L881" t="inlineStr">
         <is>
           <t>USD</t>
@@ -54242,7 +56602,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K882" t="inlineStr"/>
+      <c r="K882" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L882" t="inlineStr">
         <is>
           <t>USD</t>
@@ -54303,7 +56667,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K883" t="inlineStr"/>
+      <c r="K883" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L883" t="inlineStr">
         <is>
           <t>USD</t>
@@ -54364,7 +56732,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K884" t="inlineStr"/>
+      <c r="K884" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L884" t="inlineStr">
         <is>
           <t>USD</t>
@@ -54425,7 +56797,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K885" t="inlineStr"/>
+      <c r="K885" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L885" t="inlineStr">
         <is>
           <t>USD</t>
@@ -54486,7 +56862,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K886" t="inlineStr"/>
+      <c r="K886" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L886" t="inlineStr">
         <is>
           <t>USD</t>
@@ -54547,7 +56927,11 @@
           <t>78.209.441-6</t>
         </is>
       </c>
-      <c r="K887" t="inlineStr"/>
+      <c r="K887" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L887" t="inlineStr">
         <is>
           <t>USD</t>
@@ -54669,7 +57053,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K889" t="inlineStr"/>
+      <c r="K889" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L889" t="inlineStr">
         <is>
           <t>USD</t>
@@ -54730,7 +57118,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K890" t="inlineStr"/>
+      <c r="K890" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L890" t="inlineStr">
         <is>
           <t>USD</t>
@@ -54791,7 +57183,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K891" t="inlineStr"/>
+      <c r="K891" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L891" t="inlineStr">
         <is>
           <t>USD</t>
@@ -54852,7 +57248,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K892" t="inlineStr"/>
+      <c r="K892" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L892" t="inlineStr">
         <is>
           <t>USD</t>
@@ -54913,7 +57313,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K893" t="inlineStr"/>
+      <c r="K893" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L893" t="inlineStr">
         <is>
           <t>USD</t>
@@ -54974,7 +57378,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K894" t="inlineStr"/>
+      <c r="K894" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L894" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55035,7 +57443,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K895" t="inlineStr"/>
+      <c r="K895" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L895" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55157,7 +57569,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K897" t="inlineStr"/>
+      <c r="K897" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L897" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55218,7 +57634,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K898" t="inlineStr"/>
+      <c r="K898" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L898" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55279,7 +57699,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K899" t="inlineStr"/>
+      <c r="K899" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L899" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55340,7 +57764,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K900" t="inlineStr"/>
+      <c r="K900" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L900" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55401,7 +57829,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K901" t="inlineStr"/>
+      <c r="K901" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L901" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55462,7 +57894,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K902" t="inlineStr"/>
+      <c r="K902" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L902" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55584,7 +58020,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K904" t="inlineStr"/>
+      <c r="K904" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L904" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55645,7 +58085,11 @@
           <t>96.989.530-7</t>
         </is>
       </c>
-      <c r="K905" t="inlineStr"/>
+      <c r="K905" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L905" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55706,7 +58150,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K906" t="inlineStr"/>
+      <c r="K906" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L906" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55767,7 +58215,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K907" t="inlineStr"/>
+      <c r="K907" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L907" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55828,7 +58280,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K908" t="inlineStr"/>
+      <c r="K908" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L908" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55889,7 +58345,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K909" t="inlineStr"/>
+      <c r="K909" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L909" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55950,7 +58410,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K910" t="inlineStr"/>
+      <c r="K910" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L910" t="inlineStr">
         <is>
           <t>USD</t>
@@ -56011,7 +58475,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K911" t="inlineStr"/>
+      <c r="K911" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L911" t="inlineStr">
         <is>
           <t>USD</t>
@@ -56133,7 +58601,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K913" t="inlineStr"/>
+      <c r="K913" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L913" t="inlineStr">
         <is>
           <t>USD</t>
@@ -56194,7 +58666,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K914" t="inlineStr"/>
+      <c r="K914" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L914" t="inlineStr">
         <is>
           <t>USD</t>
@@ -56255,7 +58731,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K915" t="inlineStr"/>
+      <c r="K915" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L915" t="inlineStr">
         <is>
           <t>USD</t>
@@ -56316,7 +58796,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K916" t="inlineStr"/>
+      <c r="K916" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L916" t="inlineStr">
         <is>
           <t>USD</t>
@@ -56377,7 +58861,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K917" t="inlineStr"/>
+      <c r="K917" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L917" t="inlineStr">
         <is>
           <t>USD</t>
@@ -56621,7 +59109,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K921" t="inlineStr"/>
+      <c r="K921" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L921" t="inlineStr">
         <is>
           <t>USD</t>
@@ -56682,7 +59174,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K922" t="inlineStr"/>
+      <c r="K922" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L922" t="inlineStr">
         <is>
           <t>USD</t>
@@ -56743,7 +59239,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K923" t="inlineStr"/>
+      <c r="K923" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L923" t="inlineStr">
         <is>
           <t>USD</t>
@@ -56804,7 +59304,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K924" t="inlineStr"/>
+      <c r="K924" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L924" t="inlineStr">
         <is>
           <t>USD</t>
@@ -56865,7 +59369,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K925" t="inlineStr"/>
+      <c r="K925" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L925" t="inlineStr">
         <is>
           <t>USD</t>
@@ -56926,7 +59434,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K926" t="inlineStr"/>
+      <c r="K926" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L926" t="inlineStr">
         <is>
           <t>USD</t>
@@ -56987,7 +59499,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K927" t="inlineStr"/>
+      <c r="K927" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L927" t="inlineStr">
         <is>
           <t>USD</t>
@@ -57048,7 +59564,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K928" t="inlineStr"/>
+      <c r="K928" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L928" t="inlineStr">
         <is>
           <t>USD</t>
@@ -57109,7 +59629,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K929" t="inlineStr"/>
+      <c r="K929" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L929" t="inlineStr">
         <is>
           <t>USD</t>
@@ -57231,7 +59755,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K931" t="inlineStr"/>
+      <c r="K931" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L931" t="inlineStr">
         <is>
           <t>USD</t>
@@ -57292,7 +59820,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K932" t="inlineStr"/>
+      <c r="K932" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L932" t="inlineStr">
         <is>
           <t>USD</t>
@@ -57353,7 +59885,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K933" t="inlineStr"/>
+      <c r="K933" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L933" t="inlineStr">
         <is>
           <t>USD</t>
@@ -57475,7 +60011,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K935" t="inlineStr"/>
+      <c r="K935" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L935" t="inlineStr">
         <is>
           <t>USD</t>
@@ -57536,7 +60076,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K936" t="inlineStr"/>
+      <c r="K936" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L936" t="inlineStr">
         <is>
           <t>USD</t>
@@ -57597,7 +60141,11 @@
           <t>77.404.653-4</t>
         </is>
       </c>
-      <c r="K937" t="inlineStr"/>
+      <c r="K937" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L937" t="inlineStr">
         <is>
           <t>USD</t>
@@ -57658,7 +60206,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K938" t="inlineStr"/>
+      <c r="K938" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L938" t="inlineStr">
         <is>
           <t>USD</t>
@@ -57902,7 +60454,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K942" t="inlineStr"/>
+      <c r="K942" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L942" t="inlineStr">
         <is>
           <t>USD</t>
@@ -57963,7 +60519,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K943" t="inlineStr"/>
+      <c r="K943" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L943" t="inlineStr">
         <is>
           <t>USD</t>
@@ -58024,7 +60584,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K944" t="inlineStr"/>
+      <c r="K944" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L944" t="inlineStr">
         <is>
           <t>USD</t>
@@ -58146,7 +60710,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K946" t="inlineStr"/>
+      <c r="K946" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L946" t="inlineStr">
         <is>
           <t>USD</t>
@@ -58268,7 +60836,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K948" t="inlineStr"/>
+      <c r="K948" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L948" t="inlineStr">
         <is>
           <t>USD</t>
@@ -58329,7 +60901,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K949" t="inlineStr"/>
+      <c r="K949" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L949" t="inlineStr">
         <is>
           <t>USD</t>
@@ -58390,7 +60966,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K950" t="inlineStr"/>
+      <c r="K950" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L950" t="inlineStr">
         <is>
           <t>USD</t>
@@ -58451,7 +61031,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K951" t="inlineStr"/>
+      <c r="K951" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L951" t="inlineStr">
         <is>
           <t>USD</t>
@@ -58512,7 +61096,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K952" t="inlineStr"/>
+      <c r="K952" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L952" t="inlineStr">
         <is>
           <t>USD</t>
@@ -58756,7 +61344,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K956" t="inlineStr"/>
+      <c r="K956" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L956" t="inlineStr">
         <is>
           <t>USD</t>
@@ -58878,7 +61470,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K958" t="inlineStr"/>
+      <c r="K958" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L958" t="inlineStr">
         <is>
           <t>USD</t>
@@ -59000,7 +61596,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K960" t="inlineStr"/>
+      <c r="K960" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L960" t="inlineStr">
         <is>
           <t>USD</t>
@@ -59061,7 +61661,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K961" t="inlineStr"/>
+      <c r="K961" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L961" t="inlineStr">
         <is>
           <t>USD</t>
@@ -59122,7 +61726,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K962" t="inlineStr"/>
+      <c r="K962" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L962" t="inlineStr">
         <is>
           <t>USD</t>
@@ -59183,7 +61791,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K963" t="inlineStr"/>
+      <c r="K963" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L963" t="inlineStr">
         <is>
           <t>USD</t>
@@ -59244,7 +61856,11 @@
           <t>77.720.988-4</t>
         </is>
       </c>
-      <c r="K964" t="inlineStr"/>
+      <c r="K964" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L964" t="inlineStr">
         <is>
           <t>USD</t>
@@ -59305,7 +61921,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K965" t="inlineStr"/>
+      <c r="K965" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L965" t="inlineStr">
         <is>
           <t>USD</t>
@@ -59427,7 +62047,11 @@
           <t>78.209.481-5</t>
         </is>
       </c>
-      <c r="K967" t="inlineStr"/>
+      <c r="K967" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L967" t="inlineStr">
         <is>
           <t>USD</t>
@@ -59549,7 +62173,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K969" t="inlineStr"/>
+      <c r="K969" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L969" t="inlineStr">
         <is>
           <t>USD</t>
@@ -59610,7 +62238,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K970" t="inlineStr"/>
+      <c r="K970" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L970" t="inlineStr">
         <is>
           <t>USD</t>
@@ -59671,7 +62303,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K971" t="inlineStr"/>
+      <c r="K971" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L971" t="inlineStr">
         <is>
           <t>USD</t>
@@ -59732,7 +62368,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K972" t="inlineStr"/>
+      <c r="K972" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L972" t="inlineStr">
         <is>
           <t>USD</t>
@@ -59793,7 +62433,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K973" t="inlineStr"/>
+      <c r="K973" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L973" t="inlineStr">
         <is>
           <t>USD</t>
@@ -59915,7 +62559,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K975" t="inlineStr"/>
+      <c r="K975" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L975" t="inlineStr">
         <is>
           <t>USD</t>
@@ -59976,7 +62624,11 @@
           <t>78.209.441-6</t>
         </is>
       </c>
-      <c r="K976" t="inlineStr"/>
+      <c r="K976" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L976" t="inlineStr">
         <is>
           <t>USD</t>
@@ -60098,7 +62750,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K978" t="inlineStr"/>
+      <c r="K978" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L978" t="inlineStr">
         <is>
           <t>USD</t>
@@ -60159,7 +62815,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K979" t="inlineStr"/>
+      <c r="K979" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L979" t="inlineStr">
         <is>
           <t>USD</t>
@@ -60220,7 +62880,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K980" t="inlineStr"/>
+      <c r="K980" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L980" t="inlineStr">
         <is>
           <t>USD</t>
@@ -60281,7 +62945,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K981" t="inlineStr"/>
+      <c r="K981" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L981" t="inlineStr">
         <is>
           <t>USD</t>
@@ -60403,7 +63071,11 @@
           <t>76.715.074-1</t>
         </is>
       </c>
-      <c r="K983" t="inlineStr"/>
+      <c r="K983" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L983" t="inlineStr">
         <is>
           <t>USD</t>
@@ -60525,7 +63197,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K985" t="inlineStr"/>
+      <c r="K985" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L985" t="inlineStr">
         <is>
           <t>USD</t>
@@ -60891,7 +63567,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K991" t="inlineStr"/>
+      <c r="K991" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L991" t="inlineStr">
         <is>
           <t>USD</t>
@@ -60952,7 +63632,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K992" t="inlineStr"/>
+      <c r="K992" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L992" t="inlineStr">
         <is>
           <t>USD</t>
@@ -61074,7 +63758,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K994" t="inlineStr"/>
+      <c r="K994" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L994" t="inlineStr">
         <is>
           <t>USD</t>
@@ -61135,7 +63823,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K995" t="inlineStr"/>
+      <c r="K995" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L995" t="inlineStr">
         <is>
           <t>USD</t>
@@ -61318,7 +64010,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K998" t="inlineStr"/>
+      <c r="K998" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L998" t="inlineStr">
         <is>
           <t>USD</t>
@@ -61379,7 +64075,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K999" t="inlineStr"/>
+      <c r="K999" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L999" t="inlineStr">
         <is>
           <t>USD</t>
@@ -61440,7 +64140,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K1000" t="inlineStr"/>
+      <c r="K1000" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1000" t="inlineStr">
         <is>
           <t>USD</t>
@@ -61501,7 +64205,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K1001" t="inlineStr"/>
+      <c r="K1001" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1001" t="inlineStr">
         <is>
           <t>USD</t>
@@ -61623,7 +64331,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K1003" t="inlineStr"/>
+      <c r="K1003" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L1003" t="inlineStr">
         <is>
           <t>USD</t>
@@ -61684,7 +64396,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K1004" t="inlineStr"/>
+      <c r="K1004" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L1004" t="inlineStr">
         <is>
           <t>USD</t>
@@ -61745,7 +64461,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K1005" t="inlineStr"/>
+      <c r="K1005" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1005" t="inlineStr">
         <is>
           <t>USD</t>
@@ -61867,7 +64587,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K1007" t="inlineStr"/>
+      <c r="K1007" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L1007" t="inlineStr">
         <is>
           <t>USD</t>
@@ -62050,7 +64774,11 @@
           <t>96.989.530-7</t>
         </is>
       </c>
-      <c r="K1010" t="inlineStr"/>
+      <c r="K1010" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1010" t="inlineStr">
         <is>
           <t>USD</t>
@@ -62111,7 +64839,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K1011" t="inlineStr"/>
+      <c r="K1011" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1011" t="inlineStr">
         <is>
           <t>USD</t>
@@ -62233,7 +64965,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K1013" t="inlineStr"/>
+      <c r="K1013" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L1013" t="inlineStr">
         <is>
           <t>USD</t>
@@ -62294,7 +65030,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K1014" t="inlineStr"/>
+      <c r="K1014" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L1014" t="inlineStr">
         <is>
           <t>USD</t>
@@ -62538,7 +65278,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K1018" t="inlineStr"/>
+      <c r="K1018" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1018" t="inlineStr">
         <is>
           <t>USD</t>
@@ -62599,7 +65343,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K1019" t="inlineStr"/>
+      <c r="K1019" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1019" t="inlineStr">
         <is>
           <t>USD</t>
@@ -62660,7 +65408,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K1020" t="inlineStr"/>
+      <c r="K1020" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L1020" t="inlineStr">
         <is>
           <t>USD</t>
@@ -62721,7 +65473,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K1021" t="inlineStr"/>
+      <c r="K1021" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1021" t="inlineStr">
         <is>
           <t>USD</t>
@@ -62782,7 +65538,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K1022" t="inlineStr"/>
+      <c r="K1022" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L1022" t="inlineStr">
         <is>
           <t>USD</t>
@@ -62904,7 +65664,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K1024" t="inlineStr"/>
+      <c r="K1024" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L1024" t="inlineStr">
         <is>
           <t>USD</t>
@@ -62965,7 +65729,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K1025" t="inlineStr"/>
+      <c r="K1025" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L1025" t="inlineStr">
         <is>
           <t>USD</t>
@@ -63087,7 +65855,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K1027" t="inlineStr"/>
+      <c r="K1027" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L1027" t="inlineStr">
         <is>
           <t>USD</t>
@@ -63148,7 +65920,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K1028" t="inlineStr"/>
+      <c r="K1028" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1028" t="inlineStr">
         <is>
           <t>USD</t>
@@ -63331,7 +66107,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K1031" t="inlineStr"/>
+      <c r="K1031" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L1031" t="inlineStr">
         <is>
           <t>USD</t>
@@ -63392,7 +66172,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K1032" t="inlineStr"/>
+      <c r="K1032" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1032" t="inlineStr">
         <is>
           <t>USD</t>
@@ -63514,7 +66298,11 @@
           <t>78.209.499-8</t>
         </is>
       </c>
-      <c r="K1034" t="inlineStr"/>
+      <c r="K1034" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1034" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-mensuales/articulos-de-aseo-e-higiene/feb-2026.xlsx
+++ b/docs/oc-mensuales/articulos-de-aseo-e-higiene/feb-2026.xlsx
@@ -562,7 +562,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1196,7 +1200,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1257,7 +1265,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1383,7 +1395,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3037,7 +3053,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4309,7 +4329,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5715,7 +5739,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6914,7 +6942,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L102" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7617,7 +7649,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L113" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8442,7 +8478,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr"/>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L126" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9535,7 +9575,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L143" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13172,7 +13216,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr"/>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L200" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13818,7 +13866,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K210" t="inlineStr"/>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L210" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15029,7 +15081,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K229" t="inlineStr"/>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L229" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15984,7 +16040,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K244" t="inlineStr"/>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L244" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16171,7 +16231,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K247" t="inlineStr"/>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L247" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16687,7 +16751,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K255" t="inlineStr"/>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L255" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17573,7 +17641,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K269" t="inlineStr"/>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L269" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17699,7 +17771,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K271" t="inlineStr"/>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L271" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18081,7 +18157,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K277" t="inlineStr"/>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L277" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19548,7 +19628,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K300" t="inlineStr"/>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L300" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20958,7 +21042,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K322" t="inlineStr"/>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L322" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21470,7 +21558,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K330" t="inlineStr"/>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L330" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21531,7 +21623,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K331" t="inlineStr"/>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L331" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21657,7 +21753,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K333" t="inlineStr"/>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L333" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21783,7 +21883,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K335" t="inlineStr"/>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L335" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21909,7 +22013,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K337" t="inlineStr"/>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L337" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22226,7 +22334,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K342" t="inlineStr"/>
+      <c r="K342" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L342" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22352,7 +22464,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K344" t="inlineStr"/>
+      <c r="K344" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L344" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22478,7 +22594,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K346" t="inlineStr"/>
+      <c r="K346" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L346" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24392,7 +24512,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K376" t="inlineStr"/>
+      <c r="K376" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L376" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24778,7 +24902,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K382" t="inlineStr"/>
+      <c r="K382" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L382" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24969,7 +25097,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K385" t="inlineStr"/>
+      <c r="K385" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L385" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25416,7 +25548,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K392" t="inlineStr"/>
+      <c r="K392" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L392" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25672,7 +25808,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K396" t="inlineStr"/>
+      <c r="K396" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L396" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26245,7 +26385,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K405" t="inlineStr"/>
+      <c r="K405" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L405" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26566,7 +26710,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K410" t="inlineStr"/>
+      <c r="K410" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L410" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26627,7 +26775,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K411" t="inlineStr"/>
+      <c r="K411" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L411" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27261,7 +27413,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K421" t="inlineStr"/>
+      <c r="K421" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L421" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27838,7 +27994,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K430" t="inlineStr"/>
+      <c r="K430" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L430" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28996,7 +29156,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K448" t="inlineStr"/>
+      <c r="K448" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L448" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29374,7 +29538,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K454" t="inlineStr"/>
+      <c r="K454" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L454" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33304,7 +33472,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K516" t="inlineStr"/>
+      <c r="K516" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L516" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34137,7 +34309,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K529" t="inlineStr"/>
+      <c r="K529" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L529" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34645,7 +34821,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K537" t="inlineStr"/>
+      <c r="K537" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L537" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35409,7 +35589,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K549" t="inlineStr"/>
+      <c r="K549" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L549" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35856,7 +36040,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K556" t="inlineStr"/>
+      <c r="K556" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L556" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36364,7 +36552,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K564" t="inlineStr"/>
+      <c r="K564" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L564" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36986,7 +37178,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K574" t="inlineStr"/>
+      <c r="K574" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L574" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37803,7 +37999,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K587" t="inlineStr"/>
+      <c r="K587" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L587" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38120,7 +38320,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K592" t="inlineStr"/>
+      <c r="K592" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L592" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38181,7 +38385,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K593" t="inlineStr"/>
+      <c r="K593" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L593" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38368,7 +38576,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K596" t="inlineStr"/>
+      <c r="K596" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L596" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38620,7 +38832,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K600" t="inlineStr"/>
+      <c r="K600" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L600" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40201,7 +40417,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K625" t="inlineStr"/>
+      <c r="K625" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L625" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40896,7 +41116,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K636" t="inlineStr"/>
+      <c r="K636" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L636" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41660,7 +41884,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K648" t="inlineStr"/>
+      <c r="K648" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L648" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45053,7 +45281,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K701" t="inlineStr"/>
+      <c r="K701" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L701" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45634,7 +45866,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K710" t="inlineStr"/>
+      <c r="K710" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L710" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46516,7 +46752,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K724" t="inlineStr"/>
+      <c r="K724" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L724" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46642,7 +46882,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K726" t="inlineStr"/>
+      <c r="K726" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L726" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46955,7 +47199,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K731" t="inlineStr"/>
+      <c r="K731" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L731" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47601,7 +47849,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K741" t="inlineStr"/>
+      <c r="K741" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L741" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48109,7 +48361,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K749" t="inlineStr"/>
+      <c r="K749" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L749" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48170,7 +48426,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K750" t="inlineStr"/>
+      <c r="K750" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L750" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49328,7 +49588,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K768" t="inlineStr"/>
+      <c r="K768" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L768" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50283,7 +50547,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K783" t="inlineStr"/>
+      <c r="K783" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L783" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50470,7 +50738,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K786" t="inlineStr"/>
+      <c r="K786" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L786" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51368,7 +51640,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K800" t="inlineStr"/>
+      <c r="K800" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L800" t="inlineStr">
         <is>
           <t>USD</t>
@@ -53038,7 +53314,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K826" t="inlineStr"/>
+      <c r="K826" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L826" t="inlineStr">
         <is>
           <t>USD</t>
@@ -53099,7 +53379,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K827" t="inlineStr"/>
+      <c r="K827" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L827" t="inlineStr">
         <is>
           <t>USD</t>
@@ -53725,7 +54009,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K837" t="inlineStr"/>
+      <c r="K837" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L837" t="inlineStr">
         <is>
           <t>USD</t>
@@ -54046,7 +54334,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K842" t="inlineStr"/>
+      <c r="K842" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L842" t="inlineStr">
         <is>
           <t>USD</t>
@@ -56346,7 +56638,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K878" t="inlineStr"/>
+      <c r="K878" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L878" t="inlineStr">
         <is>
           <t>USD</t>
@@ -56992,7 +57288,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K888" t="inlineStr"/>
+      <c r="K888" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L888" t="inlineStr">
         <is>
           <t>USD</t>
@@ -57508,7 +57808,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K896" t="inlineStr"/>
+      <c r="K896" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L896" t="inlineStr">
         <is>
           <t>USD</t>
@@ -57959,7 +58263,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K903" t="inlineStr"/>
+      <c r="K903" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L903" t="inlineStr">
         <is>
           <t>USD</t>
@@ -59694,7 +60002,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K930" t="inlineStr"/>
+      <c r="K930" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L930" t="inlineStr">
         <is>
           <t>USD</t>
@@ -59950,7 +60262,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K934" t="inlineStr"/>
+      <c r="K934" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L934" t="inlineStr">
         <is>
           <t>USD</t>
@@ -60271,7 +60587,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K939" t="inlineStr"/>
+      <c r="K939" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L939" t="inlineStr">
         <is>
           <t>USD</t>
@@ -60332,7 +60652,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K940" t="inlineStr"/>
+      <c r="K940" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L940" t="inlineStr">
         <is>
           <t>USD</t>
@@ -60775,7 +61099,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K947" t="inlineStr"/>
+      <c r="K947" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L947" t="inlineStr">
         <is>
           <t>USD</t>
@@ -61283,7 +61611,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K955" t="inlineStr"/>
+      <c r="K955" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L955" t="inlineStr">
         <is>
           <t>USD</t>
@@ -61409,7 +61741,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K957" t="inlineStr"/>
+      <c r="K957" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L957" t="inlineStr">
         <is>
           <t>USD</t>
@@ -61535,7 +61871,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K959" t="inlineStr"/>
+      <c r="K959" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L959" t="inlineStr">
         <is>
           <t>USD</t>
@@ -61986,7 +62326,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K966" t="inlineStr"/>
+      <c r="K966" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L966" t="inlineStr">
         <is>
           <t>USD</t>
@@ -62112,7 +62456,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K968" t="inlineStr"/>
+      <c r="K968" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L968" t="inlineStr">
         <is>
           <t>USD</t>
@@ -62498,7 +62846,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K974" t="inlineStr"/>
+      <c r="K974" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L974" t="inlineStr">
         <is>
           <t>USD</t>
@@ -63010,7 +63362,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K982" t="inlineStr"/>
+      <c r="K982" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L982" t="inlineStr">
         <is>
           <t>USD</t>
@@ -63136,7 +63492,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K984" t="inlineStr"/>
+      <c r="K984" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L984" t="inlineStr">
         <is>
           <t>USD</t>
@@ -63445,7 +63805,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K989" t="inlineStr"/>
+      <c r="K989" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L989" t="inlineStr">
         <is>
           <t>USD</t>
@@ -63697,7 +64061,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K993" t="inlineStr"/>
+      <c r="K993" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L993" t="inlineStr">
         <is>
           <t>USD</t>
@@ -65156,7 +65524,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K1016" t="inlineStr"/>
+      <c r="K1016" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1016" t="inlineStr">
         <is>
           <t>USD</t>
@@ -65794,7 +66166,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K1026" t="inlineStr"/>
+      <c r="K1026" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1026" t="inlineStr">
         <is>
           <t>USD</t>
@@ -65985,7 +66361,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K1029" t="inlineStr"/>
+      <c r="K1029" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1029" t="inlineStr">
         <is>
           <t>USD</t>
@@ -66237,7 +66617,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K1033" t="inlineStr"/>
+      <c r="K1033" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1033" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-mensuales/articulos-de-aseo-e-higiene/feb-2026.xlsx
+++ b/docs/oc-mensuales/articulos-de-aseo-e-higiene/feb-2026.xlsx
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -7621,7 +7621,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -8836,7 +8836,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -10437,7 +10437,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -28937,7 +28937,7 @@
       </c>
       <c r="E445" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F445" t="inlineStr">
@@ -34980,7 +34980,7 @@
       </c>
       <c r="E540" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F540" t="inlineStr">
@@ -43961,7 +43961,7 @@
       </c>
       <c r="E681" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F681" t="inlineStr">
@@ -53603,7 +53603,7 @@
       </c>
       <c r="E831" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F831" t="inlineStr">
@@ -54046,7 +54046,7 @@
       </c>
       <c r="E838" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F838" t="inlineStr">
@@ -59909,7 +59909,7 @@
       </c>
       <c r="E929" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F929" t="inlineStr">
